--- a/data/calibrations/recalage parc immobilier_new2.xlsx
+++ b/data/calibrations/recalage parc immobilier_new2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\ThreeME\data\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C9022-4A11-483C-8116-D71CA11A1A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C48172D-4BE4-4AD8-AEA9-FE5107050659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{F3B8202A-200E-4C94-BB50-F6C7EC74A6D2}"/>
   </bookViews>
@@ -1286,25 +1286,25 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>9.4433779213816977E-3</c:v>
+                  <c:v>1.0738327829237906E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.9867428906788351E-2</c:v>
+                  <c:v>5.4934817726399347E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.21371213265621286</c:v>
+                  <c:v>0.23333606550825939</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.34871528906019389</c:v>
+                  <c:v>0.31508176392545656</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.20195684024110336</c:v>
+                  <c:v>0.21264127283360726</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.8955651376382042E-2</c:v>
+                  <c:v>0.10406030936528178</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.7349279719025374E-2</c:v>
+                  <c:v>6.9207442653207857E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4918,145 +4918,145 @@
         <v>91</v>
       </c>
       <c r="B2">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C2">
-        <v>7966.4202385211802</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D2">
-        <v>8186.3743000000004</v>
+        <v>8022.1280880000004</v>
       </c>
       <c r="E2">
-        <v>9701.1703209999996</v>
+        <v>9534.2584409999999</v>
       </c>
       <c r="F2">
-        <v>10407.805619999999</v>
+        <v>10282.47286</v>
       </c>
       <c r="G2">
-        <v>10623.29257</v>
+        <v>10539.521699999999</v>
       </c>
       <c r="H2">
-        <v>8737.1823260000001</v>
+        <v>8556.5195359999998</v>
       </c>
       <c r="I2">
-        <v>8818.4625849999902</v>
+        <v>8591.9026649999996</v>
       </c>
       <c r="J2">
-        <v>9940.1322770000006</v>
+        <v>9694.266243</v>
       </c>
       <c r="K2">
-        <v>11282.96738</v>
+        <v>11036.826069999999</v>
       </c>
       <c r="L2">
-        <v>11424.569079999999</v>
+        <v>11182.380649999999</v>
       </c>
       <c r="M2">
-        <v>10506.44162</v>
+        <v>10264.94281</v>
       </c>
       <c r="N2">
-        <v>7837.733682</v>
+        <v>7599.993982</v>
       </c>
       <c r="O2">
-        <v>7159.1341110000003</v>
+        <v>6964.345609</v>
       </c>
       <c r="P2">
-        <v>8568.6068030000006</v>
+        <v>8403.7953550000002</v>
       </c>
       <c r="Q2">
-        <v>13270.076129999999</v>
+        <v>13144.305909999999</v>
       </c>
       <c r="R2">
-        <v>15282.092049999999</v>
+        <v>15161.38853</v>
       </c>
       <c r="S2">
-        <v>18046.60497</v>
+        <v>17946.218349999999</v>
       </c>
       <c r="T2">
-        <v>18825.771110000001</v>
+        <v>18728.08167</v>
       </c>
       <c r="U2">
-        <v>19502.961340000002</v>
+        <v>19415.861369999999</v>
       </c>
       <c r="V2">
-        <v>18275.81955</v>
+        <v>18183.457490000001</v>
       </c>
       <c r="W2">
-        <v>18115.709439999999</v>
+        <v>18039.45348</v>
       </c>
       <c r="X2">
-        <v>15743.35771</v>
+        <v>15656.5465</v>
       </c>
       <c r="Y2">
-        <v>14246.24509</v>
+        <v>14130.364299999999</v>
       </c>
       <c r="Z2">
-        <v>13552.2907</v>
+        <v>13417.90353</v>
       </c>
       <c r="AA2">
-        <v>13218.9871</v>
+        <v>13074.0507</v>
       </c>
       <c r="AB2">
-        <v>13110.4583</v>
+        <v>12959.426810000001</v>
       </c>
       <c r="AC2">
-        <v>13134.945610000001</v>
+        <v>12979.83195</v>
       </c>
       <c r="AD2">
-        <v>13237.48307</v>
+        <v>13078.9267</v>
       </c>
       <c r="AE2">
-        <v>13418.69291</v>
+        <v>13257.40092</v>
       </c>
       <c r="AF2">
-        <v>13660.693370000001</v>
+        <v>13498.208140000001</v>
       </c>
       <c r="AG2">
-        <v>13919.72378</v>
+        <v>13753.788420000001</v>
       </c>
       <c r="AH2">
-        <v>14205.07834</v>
+        <v>14033.910760000001</v>
       </c>
       <c r="AI2">
-        <v>14531.615959999999</v>
+        <v>14353.43714</v>
       </c>
       <c r="AJ2">
-        <v>14886.400100000001</v>
+        <v>14699.895409999999</v>
       </c>
       <c r="AK2">
-        <v>15281.61925</v>
+        <v>15086.16142</v>
       </c>
       <c r="AL2">
-        <v>15710.10277</v>
+        <v>15505.019060000001</v>
       </c>
       <c r="AM2">
-        <v>16214.782349999999</v>
+        <v>15999.621789999999</v>
       </c>
       <c r="AN2">
-        <v>16891.312089999999</v>
+        <v>16665.72034</v>
       </c>
       <c r="AO2">
-        <v>17662.433219999999</v>
+        <v>17426.102620000001</v>
       </c>
       <c r="AP2">
-        <v>18489.230490000002</v>
+        <v>18241.8377</v>
       </c>
       <c r="AQ2">
-        <v>19347.078539999999</v>
+        <v>19089.019749999999</v>
       </c>
       <c r="AR2">
-        <v>20240.183840000002</v>
+        <v>19972.513449999999</v>
       </c>
       <c r="AS2">
-        <v>21201.51326</v>
+        <v>20922.164100000002</v>
       </c>
       <c r="AT2">
-        <v>22205.29621</v>
+        <v>21912.999599999999</v>
       </c>
       <c r="AU2">
-        <v>23227.682059999999</v>
+        <v>22921.297999999999</v>
       </c>
       <c r="AV2">
-        <v>24250.91748</v>
+        <v>23929.476879999998</v>
       </c>
     </row>
     <row r="3" spans="1:48" x14ac:dyDescent="0.25">
@@ -5064,145 +5064,145 @@
         <v>92</v>
       </c>
       <c r="B3">
-        <v>401167.83705106698</v>
+        <v>409662.49706947699</v>
       </c>
       <c r="C3">
-        <v>407608.716436335</v>
+        <v>416239.76096901699</v>
       </c>
       <c r="D3">
-        <v>414153.0062</v>
+        <v>422922.625</v>
       </c>
       <c r="E3">
-        <v>512305.85320000001</v>
+        <v>521176.73670000001</v>
       </c>
       <c r="F3">
-        <v>554575.11</v>
+        <v>565935.13100000005</v>
       </c>
       <c r="G3">
-        <v>560405.52729999996</v>
+        <v>574293.12410000002</v>
       </c>
       <c r="H3">
-        <v>444416.26209999999</v>
+        <v>451320.11180000001</v>
       </c>
       <c r="I3">
-        <v>442715.61219999997</v>
+        <v>446202.5465</v>
       </c>
       <c r="J3">
-        <v>495132.52679999999</v>
+        <v>497037.24320000003</v>
       </c>
       <c r="K3">
-        <v>566430.42610000004</v>
+        <v>567902.00769999996</v>
       </c>
       <c r="L3">
-        <v>568014.10129999998</v>
+        <v>569861.89119999995</v>
       </c>
       <c r="M3">
-        <v>511188.31060000003</v>
+        <v>513672.21470000001</v>
       </c>
       <c r="N3">
-        <v>368053.46590000001</v>
+        <v>372000.83409999998</v>
       </c>
       <c r="O3">
-        <v>348236.66960000002</v>
+        <v>354667.6606</v>
       </c>
       <c r="P3">
-        <v>426497.20899999997</v>
+        <v>434004.98619999998</v>
       </c>
       <c r="Q3">
-        <v>690615.42890000006</v>
+        <v>697667.215499999</v>
       </c>
       <c r="R3">
-        <v>785402.55009999999</v>
+        <v>792035.46510000003</v>
       </c>
       <c r="S3">
-        <v>934616.52959999896</v>
+        <v>940486.50419999997</v>
       </c>
       <c r="T3">
-        <v>955481.72589999996</v>
+        <v>961472.50540000002</v>
       </c>
       <c r="U3">
-        <v>982805.72879999899</v>
+        <v>988911.54599999997</v>
       </c>
       <c r="V3">
-        <v>896948.24430000002</v>
+        <v>904143.78159999999</v>
       </c>
       <c r="W3">
-        <v>881197.14859999996</v>
+        <v>889542.007099999</v>
       </c>
       <c r="X3">
-        <v>734085.11399999994</v>
+        <v>744561.22499999998</v>
       </c>
       <c r="Y3">
-        <v>653316.59360000002</v>
+        <v>663382.41949999996</v>
       </c>
       <c r="Z3">
-        <v>608290.81059999997</v>
+        <v>618191.6067</v>
       </c>
       <c r="AA3">
-        <v>583884.41229999997</v>
+        <v>593769.80379999999</v>
       </c>
       <c r="AB3">
-        <v>571661.55359999998</v>
+        <v>581603.42700000003</v>
       </c>
       <c r="AC3">
-        <v>565958.94350000005</v>
+        <v>575983.20189999999</v>
       </c>
       <c r="AD3">
-        <v>563431.33970000001</v>
+        <v>573545.51170000003</v>
       </c>
       <c r="AE3">
-        <v>563980.05530000001</v>
+        <v>574210.49659999995</v>
       </c>
       <c r="AF3">
-        <v>566626.56810000003</v>
+        <v>577060.00930000003</v>
       </c>
       <c r="AG3">
-        <v>569258.03989999997</v>
+        <v>579794.37109999999</v>
       </c>
       <c r="AH3">
-        <v>572364.064799999</v>
+        <v>582927.1091</v>
       </c>
       <c r="AI3">
-        <v>576543.44409999996</v>
+        <v>587059.32819999999</v>
       </c>
       <c r="AJ3">
-        <v>581360.15879999998</v>
+        <v>591766.48569999996</v>
       </c>
       <c r="AK3">
-        <v>587521.48419999995</v>
+        <v>597761.40930000006</v>
       </c>
       <c r="AL3">
-        <v>594634.60580000002</v>
+        <v>604654.68770000001</v>
       </c>
       <c r="AM3">
-        <v>604290.47259999998</v>
+        <v>614034.51760000002</v>
       </c>
       <c r="AN3">
-        <v>619564.71</v>
+        <v>628973.19869999995</v>
       </c>
       <c r="AO3">
-        <v>637528.91940000001</v>
+        <v>646551.14099999995</v>
       </c>
       <c r="AP3">
-        <v>656697.86060000001</v>
+        <v>665288.28769999999</v>
       </c>
       <c r="AQ3">
-        <v>676087.93330000003</v>
+        <v>684237.81660000002</v>
       </c>
       <c r="AR3">
-        <v>695735.86340000003</v>
+        <v>703460.607699999</v>
       </c>
       <c r="AS3">
-        <v>716651.86880000005</v>
+        <v>723863.65469999996</v>
       </c>
       <c r="AT3">
-        <v>737926.69050000003</v>
+        <v>744570.852699999</v>
       </c>
       <c r="AU3">
-        <v>758262.57929999998</v>
+        <v>764309.21699999995</v>
       </c>
       <c r="AV3">
-        <v>777253.88749999995</v>
+        <v>782682.72560000001</v>
       </c>
     </row>
     <row r="4" spans="1:48" x14ac:dyDescent="0.25">
@@ -5365,136 +5365,136 @@
         <v>188893454</v>
       </c>
       <c r="E5">
-        <v>192890472.5</v>
+        <v>191063764.30000001</v>
       </c>
       <c r="F5">
-        <v>195972600.59999999</v>
+        <v>192370890.30000001</v>
       </c>
       <c r="G5">
-        <v>198367042.5</v>
+        <v>193041127.30000001</v>
       </c>
       <c r="H5">
-        <v>201726129.59999999</v>
+        <v>194680942.30000001</v>
       </c>
       <c r="I5">
-        <v>204743452.80000001</v>
+        <v>196011318.5</v>
       </c>
       <c r="J5">
-        <v>206557692.40000001</v>
+        <v>196206590.80000001</v>
       </c>
       <c r="K5">
-        <v>206969909.5</v>
+        <v>195081039.30000001</v>
       </c>
       <c r="L5">
-        <v>207129634.5</v>
+        <v>193724931.90000001</v>
       </c>
       <c r="M5">
-        <v>208073401.19999999</v>
+        <v>193110902.69999999</v>
       </c>
       <c r="N5">
-        <v>210932186.90000001</v>
+        <v>194281637.40000001</v>
       </c>
       <c r="O5">
-        <v>214522650.30000001</v>
+        <v>196119853.19999999</v>
       </c>
       <c r="P5">
-        <v>217170466.30000001</v>
+        <v>197106337.90000001</v>
       </c>
       <c r="Q5">
-        <v>216580420.40000001</v>
+        <v>195170429.80000001</v>
       </c>
       <c r="R5">
-        <v>214655988.19999999</v>
+        <v>192061154.90000001</v>
       </c>
       <c r="S5">
-        <v>211106274.90000001</v>
+        <v>187527040.90000001</v>
       </c>
       <c r="T5">
-        <v>207181677.30000001</v>
+        <v>182694963.80000001</v>
       </c>
       <c r="U5">
-        <v>202945756.69999999</v>
+        <v>177622740.59999999</v>
       </c>
       <c r="V5">
-        <v>199334272</v>
+        <v>173128570.40000001</v>
       </c>
       <c r="W5">
-        <v>195776468.09999999</v>
+        <v>168708415.90000001</v>
       </c>
       <c r="X5">
-        <v>193276944.40000001</v>
+        <v>165233441.90000001</v>
       </c>
       <c r="Y5">
-        <v>191476407.69999999</v>
+        <v>162385010.80000001</v>
       </c>
       <c r="Z5">
-        <v>190150777.80000001</v>
+        <v>159966826.69999999</v>
       </c>
       <c r="AA5">
-        <v>189160520.5</v>
+        <v>157858983.59999999</v>
       </c>
       <c r="AB5">
-        <v>188415820.09999999</v>
+        <v>155986406.5</v>
       </c>
       <c r="AC5">
-        <v>187856236.69999999</v>
+        <v>154300128.09999999</v>
       </c>
       <c r="AD5">
-        <v>187440999.90000001</v>
+        <v>152766882.5</v>
       </c>
       <c r="AE5">
-        <v>187122099.90000001</v>
+        <v>151348094.59999999</v>
       </c>
       <c r="AF5">
-        <v>186860221</v>
+        <v>150012718.09999999</v>
       </c>
       <c r="AG5">
-        <v>186637195.69999999</v>
+        <v>148747010</v>
       </c>
       <c r="AH5">
-        <v>186434191.19999999</v>
+        <v>147536256.80000001</v>
       </c>
       <c r="AI5">
-        <v>186224165.69999999</v>
+        <v>146359767</v>
       </c>
       <c r="AJ5">
-        <v>185995090.90000001</v>
+        <v>145209000.5</v>
       </c>
       <c r="AK5">
-        <v>185740775.5</v>
+        <v>144079638.30000001</v>
       </c>
       <c r="AL5">
-        <v>185457902.80000001</v>
+        <v>142969788.59999999</v>
       </c>
       <c r="AM5">
-        <v>185120273.19999999</v>
+        <v>141859845.19999999</v>
       </c>
       <c r="AN5">
-        <v>184650019.30000001</v>
+        <v>140690651.30000001</v>
       </c>
       <c r="AO5">
-        <v>184017026.30000001</v>
+        <v>139440226.30000001</v>
       </c>
       <c r="AP5">
-        <v>183212143.90000001</v>
+        <v>138102586</v>
       </c>
       <c r="AQ5">
-        <v>182237357.69999999</v>
+        <v>136679600.90000001</v>
       </c>
       <c r="AR5">
-        <v>181091455.69999999</v>
+        <v>135170501.09999999</v>
       </c>
       <c r="AS5">
-        <v>179758154.80000001</v>
+        <v>133564048.5</v>
       </c>
       <c r="AT5">
-        <v>178234987.90000001</v>
+        <v>131858746.8</v>
       </c>
       <c r="AU5">
-        <v>176528509.5</v>
+        <v>130059504.59999999</v>
       </c>
       <c r="AV5">
-        <v>174649944.5</v>
+        <v>128174374.3</v>
       </c>
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
@@ -5511,136 +5511,136 @@
         <v>412154138</v>
       </c>
       <c r="E6">
-        <v>397810191.5</v>
+        <v>399760841.10000002</v>
       </c>
       <c r="F6">
-        <v>383408628.10000002</v>
+        <v>387113174.30000001</v>
       </c>
       <c r="G6">
-        <v>369492117.69999999</v>
+        <v>374756494.19999999</v>
       </c>
       <c r="H6">
-        <v>358775875.69999999</v>
+        <v>365465593.80000001</v>
       </c>
       <c r="I6">
-        <v>348504845.80000001</v>
+        <v>356468435</v>
       </c>
       <c r="J6">
-        <v>337377244.30000001</v>
+        <v>346439416.80000001</v>
       </c>
       <c r="K6">
-        <v>325402099.39999998</v>
+        <v>335377600.10000002</v>
       </c>
       <c r="L6">
-        <v>314251454.89999998</v>
+        <v>325017050.10000002</v>
       </c>
       <c r="M6">
-        <v>305196594.69999999</v>
+        <v>316704904.30000001</v>
       </c>
       <c r="N6">
-        <v>299519536.30000001</v>
+        <v>311816568.69999999</v>
       </c>
       <c r="O6">
-        <v>295425133</v>
+        <v>308486200.69999999</v>
       </c>
       <c r="P6">
-        <v>290688668.80000001</v>
+        <v>304380859.89999998</v>
       </c>
       <c r="Q6">
-        <v>282984711.30000001</v>
+        <v>296998277.30000001</v>
       </c>
       <c r="R6">
-        <v>274616948.10000002</v>
+        <v>288783148.60000002</v>
       </c>
       <c r="S6">
-        <v>265312031.80000001</v>
+        <v>279421242.80000001</v>
       </c>
       <c r="T6">
-        <v>256230283.40000001</v>
+        <v>270171193.69999999</v>
       </c>
       <c r="U6">
-        <v>247438946.80000001</v>
+        <v>261102769.5</v>
       </c>
       <c r="V6">
-        <v>239767898</v>
+        <v>253135044.5</v>
       </c>
       <c r="W6">
-        <v>232663714.30000001</v>
+        <v>245672049.19999999</v>
       </c>
       <c r="X6">
-        <v>226960634.5</v>
+        <v>239656956.5</v>
       </c>
       <c r="Y6">
-        <v>222323468.5</v>
+        <v>234732631.09999999</v>
       </c>
       <c r="Z6">
-        <v>218442793</v>
+        <v>230586477.40000001</v>
       </c>
       <c r="AA6">
-        <v>215151039.5</v>
+        <v>227042044.59999999</v>
       </c>
       <c r="AB6">
-        <v>212330268.80000001</v>
+        <v>223975151.80000001</v>
       </c>
       <c r="AC6">
-        <v>209894794.80000001</v>
+        <v>221295672.5</v>
       </c>
       <c r="AD6">
-        <v>207782914.19999999</v>
+        <v>218939165.59999999</v>
       </c>
       <c r="AE6">
-        <v>205934939.69999999</v>
+        <v>216842366.59999999</v>
       </c>
       <c r="AF6">
-        <v>204301903.30000001</v>
+        <v>214953289.09999999</v>
       </c>
       <c r="AG6">
-        <v>202852072.09999999</v>
+        <v>213239045.59999999</v>
       </c>
       <c r="AH6">
-        <v>201557206.09999999</v>
+        <v>211670280.09999999</v>
       </c>
       <c r="AI6">
-        <v>200386544.09999999</v>
+        <v>210214313.59999999</v>
       </c>
       <c r="AJ6">
-        <v>199319999</v>
+        <v>208850362.19999999</v>
       </c>
       <c r="AK6">
-        <v>198342689.30000001</v>
+        <v>207563307.80000001</v>
       </c>
       <c r="AL6">
-        <v>197442787</v>
+        <v>206341195.59999999</v>
       </c>
       <c r="AM6">
-        <v>196588075.40000001</v>
+        <v>205148979.59999999</v>
       </c>
       <c r="AN6">
-        <v>195699653.09999999</v>
+        <v>203899053.90000001</v>
       </c>
       <c r="AO6">
-        <v>194742508.09999999</v>
+        <v>202552822.30000001</v>
       </c>
       <c r="AP6">
-        <v>193702934.19999999</v>
+        <v>201095257.30000001</v>
       </c>
       <c r="AQ6">
-        <v>192578174.30000001</v>
+        <v>199523140.09999999</v>
       </c>
       <c r="AR6">
-        <v>191361962.5</v>
+        <v>197829166.80000001</v>
       </c>
       <c r="AS6">
-        <v>190034268.80000001</v>
+        <v>195992691.69999999</v>
       </c>
       <c r="AT6">
-        <v>188589427.80000001</v>
+        <v>194008575.09999999</v>
       </c>
       <c r="AU6">
-        <v>187029944.5</v>
+        <v>191880709.40000001</v>
       </c>
       <c r="AV6">
-        <v>185361965.80000001</v>
+        <v>189617282.80000001</v>
       </c>
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.25">
@@ -5657,136 +5657,136 @@
         <v>786713699</v>
       </c>
       <c r="E7">
-        <v>765151720.10000002</v>
+        <v>767697315.20000005</v>
       </c>
       <c r="F7">
-        <v>742848404.10000002</v>
+        <v>747867086.29999995</v>
       </c>
       <c r="G7">
-        <v>721013825.5</v>
+        <v>728430631.79999995</v>
       </c>
       <c r="H7">
-        <v>704493791.79999995</v>
+        <v>714280416.60000002</v>
       </c>
       <c r="I7">
-        <v>688605379.20000005</v>
+        <v>700681344.79999995</v>
       </c>
       <c r="J7">
-        <v>671106976.79999995</v>
+        <v>685365464.70000005</v>
       </c>
       <c r="K7">
-        <v>651745399</v>
+        <v>668066588.89999998</v>
       </c>
       <c r="L7">
-        <v>633284211.29999995</v>
+        <v>651608861.20000005</v>
       </c>
       <c r="M7">
-        <v>617987009</v>
+        <v>638329540.5</v>
       </c>
       <c r="N7">
-        <v>608496979.39999998</v>
+        <v>630965417.79999995</v>
       </c>
       <c r="O7">
-        <v>601344786.70000005</v>
+        <v>625921224.89999998</v>
       </c>
       <c r="P7">
-        <v>592570777.39999998</v>
+        <v>619119672.39999998</v>
       </c>
       <c r="Q7">
-        <v>577386690.70000005</v>
+        <v>605555013.79999995</v>
       </c>
       <c r="R7">
-        <v>560460876.60000002</v>
+        <v>590111798.29999995</v>
       </c>
       <c r="S7">
-        <v>541087069.79999995</v>
+        <v>572016337.29999995</v>
       </c>
       <c r="T7">
-        <v>521982952</v>
+        <v>554130371.39999998</v>
       </c>
       <c r="U7">
-        <v>503259298.69999999</v>
+        <v>536554113.60000002</v>
       </c>
       <c r="V7">
-        <v>486896215.10000002</v>
+        <v>521401326</v>
       </c>
       <c r="W7">
-        <v>471602051.19999999</v>
+        <v>507283507.69999999</v>
       </c>
       <c r="X7">
-        <v>459368250.60000002</v>
+        <v>496368012.30000001</v>
       </c>
       <c r="Y7">
-        <v>449260693.19999999</v>
+        <v>487667698.19999999</v>
       </c>
       <c r="Z7">
-        <v>440571105</v>
+        <v>480434061.60000002</v>
       </c>
       <c r="AA7">
-        <v>432933383.5</v>
+        <v>474272532.80000001</v>
       </c>
       <c r="AB7">
-        <v>426110209</v>
+        <v>468927421.19999999</v>
       </c>
       <c r="AC7">
-        <v>419944555.89999998</v>
+        <v>464229969.80000001</v>
       </c>
       <c r="AD7">
-        <v>414332636.30000001</v>
+        <v>460069777.5</v>
       </c>
       <c r="AE7">
-        <v>409171232.69999999</v>
+        <v>456335672.80000001</v>
       </c>
       <c r="AF7">
-        <v>404377610.10000002</v>
+        <v>452938025.19999999</v>
       </c>
       <c r="AG7">
-        <v>399905830.39999998</v>
+        <v>449829058.60000002</v>
       </c>
       <c r="AH7">
-        <v>395711729.69999999</v>
+        <v>446962486.89999998</v>
       </c>
       <c r="AI7">
-        <v>391742511.39999998</v>
+        <v>444281461.39999998</v>
       </c>
       <c r="AJ7">
-        <v>387964893.5</v>
+        <v>441750901</v>
       </c>
       <c r="AK7">
-        <v>384351383.39999998</v>
+        <v>439342184.10000002</v>
       </c>
       <c r="AL7">
-        <v>380880749</v>
+        <v>437033668.30000001</v>
       </c>
       <c r="AM7">
-        <v>377495346.89999998</v>
+        <v>434760738.60000002</v>
       </c>
       <c r="AN7">
-        <v>374056814.69999999</v>
+        <v>432362753.89999998</v>
       </c>
       <c r="AO7">
-        <v>370505300.30000001</v>
+        <v>429770246.60000002</v>
       </c>
       <c r="AP7">
-        <v>366818009.80000001</v>
+        <v>426956960.5</v>
       </c>
       <c r="AQ7">
-        <v>362992183.60000002</v>
+        <v>423919605.19999999</v>
       </c>
       <c r="AR7">
-        <v>359019611.80000001</v>
+        <v>420647544</v>
       </c>
       <c r="AS7">
-        <v>354868235.80000001</v>
+        <v>417104610.5</v>
       </c>
       <c r="AT7">
-        <v>350530562.39999998</v>
+        <v>413282945.39999998</v>
       </c>
       <c r="AU7">
-        <v>346015578.39999998</v>
+        <v>409193793.10000002</v>
       </c>
       <c r="AV7">
-        <v>341338922</v>
+        <v>404856226</v>
       </c>
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
@@ -5803,136 +5803,136 @@
         <v>661409532</v>
       </c>
       <c r="E8">
-        <v>687654837.10000002</v>
+        <v>679048358.89999998</v>
       </c>
       <c r="F8">
-        <v>713532820.89999998</v>
+        <v>696700866.10000002</v>
       </c>
       <c r="G8">
-        <v>739315723.89999998</v>
+        <v>714621712</v>
       </c>
       <c r="H8">
-        <v>762734330.20000005</v>
+        <v>730411692.70000005</v>
       </c>
       <c r="I8">
-        <v>786229123</v>
+        <v>746557353</v>
       </c>
       <c r="J8">
-        <v>811239684.89999998</v>
+        <v>764544554.29999995</v>
       </c>
       <c r="K8">
-        <v>837175973.20000005</v>
+        <v>783836993.60000002</v>
       </c>
       <c r="L8">
-        <v>861943251.70000005</v>
+        <v>802262679.70000005</v>
       </c>
       <c r="M8">
-        <v>883954354.89999998</v>
+        <v>818139898</v>
       </c>
       <c r="N8">
-        <v>905015713</v>
+        <v>832553063.70000005</v>
       </c>
       <c r="O8">
-        <v>922669857.89999998</v>
+        <v>843827707.5</v>
       </c>
       <c r="P8">
-        <v>939570313.70000005</v>
+        <v>854827711.60000002</v>
       </c>
       <c r="Q8">
-        <v>954214492.89999998</v>
+        <v>864860588.5</v>
       </c>
       <c r="R8">
-        <v>967737841.20000005</v>
+        <v>874399705.39999998</v>
       </c>
       <c r="S8">
-        <v>978321861.20000005</v>
+        <v>881924858.20000005</v>
       </c>
       <c r="T8">
-        <v>987909184.5</v>
+        <v>888834801.10000002</v>
       </c>
       <c r="U8">
-        <v>997504979.79999995</v>
+        <v>895923864.10000002</v>
       </c>
       <c r="V8">
-        <v>1007994349</v>
+        <v>903812785.70000005</v>
       </c>
       <c r="W8">
-        <v>1017585804</v>
+        <v>911054906.70000005</v>
       </c>
       <c r="X8">
-        <v>1028999862</v>
+        <v>919764352.10000002</v>
       </c>
       <c r="Y8">
-        <v>1040499213</v>
+        <v>928564849.39999998</v>
       </c>
       <c r="Z8">
-        <v>1051302774</v>
+        <v>936777301.5</v>
       </c>
       <c r="AA8">
-        <v>1060908389</v>
+        <v>943974916.70000005</v>
       </c>
       <c r="AB8">
-        <v>1069080762</v>
+        <v>949957663.60000002</v>
       </c>
       <c r="AC8">
-        <v>1076236121</v>
+        <v>955091050</v>
       </c>
       <c r="AD8">
-        <v>1082301808</v>
+        <v>959313661.10000002</v>
       </c>
       <c r="AE8">
-        <v>1087275644</v>
+        <v>962625380.20000005</v>
       </c>
       <c r="AF8">
-        <v>1091191650</v>
+        <v>965053388.39999998</v>
       </c>
       <c r="AG8">
-        <v>1094258440</v>
+        <v>966782855.5</v>
       </c>
       <c r="AH8">
-        <v>1096332749</v>
+        <v>967684023.39999998</v>
       </c>
       <c r="AI8">
-        <v>1097366928</v>
+        <v>967712032.20000005</v>
       </c>
       <c r="AJ8">
-        <v>1097499553</v>
+        <v>966987369.20000005</v>
       </c>
       <c r="AK8">
-        <v>1096654345</v>
+        <v>965436890.20000005</v>
       </c>
       <c r="AL8">
-        <v>1094742933</v>
+        <v>962974895.10000002</v>
       </c>
       <c r="AM8">
-        <v>1091527088</v>
+        <v>959384018.20000005</v>
       </c>
       <c r="AN8">
-        <v>1086924151</v>
+        <v>954602116.10000002</v>
       </c>
       <c r="AO8">
-        <v>1080929260</v>
+        <v>948626135.10000002</v>
       </c>
       <c r="AP8">
-        <v>1073637930</v>
+        <v>941540570</v>
       </c>
       <c r="AQ8">
-        <v>1064998723</v>
+        <v>933290105.70000005</v>
       </c>
       <c r="AR8">
-        <v>1055054746</v>
+        <v>923908440.89999998</v>
       </c>
       <c r="AS8">
-        <v>1043871202</v>
+        <v>913454289.39999998</v>
       </c>
       <c r="AT8">
-        <v>1031465975</v>
+        <v>901938423.29999995</v>
       </c>
       <c r="AU8">
-        <v>1017914166</v>
+        <v>889421485.29999995</v>
       </c>
       <c r="AV8">
-        <v>1004778040</v>
+        <v>877456259.39999998</v>
       </c>
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
@@ -5949,136 +5949,136 @@
         <v>300942006</v>
       </c>
       <c r="E9">
-        <v>325989961.60000002</v>
+        <v>329969297.60000002</v>
       </c>
       <c r="F9">
-        <v>352084282.69999999</v>
+        <v>359742700</v>
       </c>
       <c r="G9">
-        <v>378165535</v>
+        <v>389215747.30000001</v>
       </c>
       <c r="H9">
-        <v>398508244.89999998</v>
+        <v>413578731.80000001</v>
       </c>
       <c r="I9">
-        <v>418161329</v>
+        <v>437576984.80000001</v>
       </c>
       <c r="J9">
-        <v>439605844.10000002</v>
+        <v>463484353.60000002</v>
       </c>
       <c r="K9">
-        <v>463289674.5</v>
+        <v>491584419.10000002</v>
       </c>
       <c r="L9">
-        <v>486295724.80000001</v>
+        <v>518896396.89999998</v>
       </c>
       <c r="M9">
-        <v>506208653.5</v>
+        <v>542965479.89999998</v>
       </c>
       <c r="N9">
-        <v>521190493.5</v>
+        <v>562545207</v>
       </c>
       <c r="O9">
-        <v>533918566.89999998</v>
+        <v>579549240.79999995</v>
       </c>
       <c r="P9">
-        <v>548554139</v>
+        <v>598050840</v>
       </c>
       <c r="Q9">
-        <v>569962988.5</v>
+        <v>622216441.10000002</v>
       </c>
       <c r="R9">
-        <v>593083596.79999995</v>
+        <v>647542988.20000005</v>
       </c>
       <c r="S9">
-        <v>618801146.70000005</v>
+        <v>674637351.79999995</v>
       </c>
       <c r="T9">
-        <v>643886642</v>
+        <v>700801501.20000005</v>
       </c>
       <c r="U9">
-        <v>669133668.60000002</v>
+        <v>727035789</v>
       </c>
       <c r="V9">
-        <v>691805364.20000005</v>
+        <v>750844533.10000002</v>
       </c>
       <c r="W9">
-        <v>713277230.70000005</v>
+        <v>773240083.60000002</v>
       </c>
       <c r="X9">
-        <v>731393965.60000002</v>
+        <v>792622111.70000005</v>
       </c>
       <c r="Y9">
-        <v>747295973.10000002</v>
+        <v>809830746</v>
       </c>
       <c r="Z9">
-        <v>761456560</v>
+        <v>825198761.29999995</v>
       </c>
       <c r="AA9">
-        <v>774184494</v>
+        <v>838945678.5</v>
       </c>
       <c r="AB9">
-        <v>785688750.5</v>
+        <v>851238700.39999998</v>
       </c>
       <c r="AC9">
-        <v>796358985</v>
+        <v>862516434.39999998</v>
       </c>
       <c r="AD9">
-        <v>806257380.39999998</v>
+        <v>872830197</v>
       </c>
       <c r="AE9">
-        <v>815474550.79999995</v>
+        <v>882268575</v>
       </c>
       <c r="AF9">
-        <v>824093578.89999998</v>
+        <v>890919190.89999998</v>
       </c>
       <c r="AG9">
-        <v>832245008</v>
+        <v>898942313.29999995</v>
       </c>
       <c r="AH9">
-        <v>839875616</v>
+        <v>906275752.20000005</v>
       </c>
       <c r="AI9">
-        <v>846991650.79999995</v>
+        <v>912926951.70000005</v>
       </c>
       <c r="AJ9">
-        <v>853699904.5</v>
+        <v>919023514.70000005</v>
       </c>
       <c r="AK9">
-        <v>859996262.70000005</v>
+        <v>924559699.70000005</v>
       </c>
       <c r="AL9">
-        <v>865854066.79999995</v>
+        <v>929507596.10000002</v>
       </c>
       <c r="AM9">
-        <v>871182104</v>
+        <v>933760540.10000002</v>
       </c>
       <c r="AN9">
-        <v>876081590</v>
+        <v>937414261.39999998</v>
       </c>
       <c r="AO9">
-        <v>880601013.79999995</v>
+        <v>940523536.89999998</v>
       </c>
       <c r="AP9">
-        <v>884824590.60000002</v>
+        <v>943188400.10000002</v>
       </c>
       <c r="AQ9">
-        <v>888664784.29999995</v>
+        <v>945329009.5</v>
       </c>
       <c r="AR9">
-        <v>892114531.79999995</v>
+        <v>946953211.5</v>
       </c>
       <c r="AS9">
-        <v>895227624.79999995</v>
+        <v>948125065</v>
       </c>
       <c r="AT9">
-        <v>897950275.10000002</v>
+        <v>948800220.89999998</v>
       </c>
       <c r="AU9">
-        <v>900230340.70000005</v>
+        <v>948942569.60000002</v>
       </c>
       <c r="AV9">
-        <v>902023811.29999995</v>
+        <v>948524907.5</v>
       </c>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
@@ -6095,136 +6095,136 @@
         <v>42391824</v>
       </c>
       <c r="E10">
-        <v>46675187.380000003</v>
+        <v>48327797.350000001</v>
       </c>
       <c r="F10">
-        <v>51852903</v>
+        <v>55246987.710000001</v>
       </c>
       <c r="G10">
-        <v>57105090.280000001</v>
+        <v>62334992.270000003</v>
       </c>
       <c r="H10">
-        <v>61438669.100000001</v>
+        <v>67923206.430000007</v>
       </c>
       <c r="I10">
-        <v>65905159.450000003</v>
+        <v>73311926.799999997</v>
       </c>
       <c r="J10">
-        <v>70879847.420000002</v>
+        <v>79019560.629999995</v>
       </c>
       <c r="K10">
-        <v>76909945.150000006</v>
+        <v>85686810.739999995</v>
       </c>
       <c r="L10">
-        <v>83440128.719999999</v>
+        <v>92822209.859999999</v>
       </c>
       <c r="M10">
-        <v>89967966.540000007</v>
+        <v>99963264.049999997</v>
       </c>
       <c r="N10">
-        <v>95086621.840000004</v>
+        <v>105740186.90000001</v>
       </c>
       <c r="O10">
-        <v>101255214.59999999</v>
+        <v>112677970.8</v>
       </c>
       <c r="P10">
-        <v>109252701.8</v>
+        <v>121504490.40000001</v>
       </c>
       <c r="Q10">
-        <v>122754386.59999999</v>
+        <v>135904659.30000001</v>
       </c>
       <c r="R10">
-        <v>138389682.09999999</v>
+        <v>152452455</v>
       </c>
       <c r="S10">
-        <v>157681669.19999999</v>
+        <v>172687406.19999999</v>
       </c>
       <c r="T10">
-        <v>177480391</v>
+        <v>193401590.19999999</v>
       </c>
       <c r="U10">
-        <v>198119730</v>
+        <v>214939148.69999999</v>
       </c>
       <c r="V10">
-        <v>216665518.69999999</v>
+        <v>234342017</v>
       </c>
       <c r="W10">
-        <v>234894833.30000001</v>
+        <v>253437374.90000001</v>
       </c>
       <c r="X10">
-        <v>249458384.19999999</v>
+        <v>268849791.60000002</v>
       </c>
       <c r="Y10">
-        <v>262264822.5</v>
+        <v>282461709.69999999</v>
       </c>
       <c r="Z10">
-        <v>274294531</v>
+        <v>295272047.19999999</v>
       </c>
       <c r="AA10">
-        <v>286069775.69999999</v>
+        <v>307818166.30000001</v>
       </c>
       <c r="AB10">
-        <v>297877315.89999998</v>
+        <v>320393191.69999999</v>
       </c>
       <c r="AC10">
-        <v>309894515.10000002</v>
+        <v>333175640.5</v>
       </c>
       <c r="AD10">
-        <v>322161959.39999998</v>
+        <v>346205150.19999999</v>
       </c>
       <c r="AE10">
-        <v>334719381.60000002</v>
+        <v>359520810.19999999</v>
       </c>
       <c r="AF10">
-        <v>347588943.30000001</v>
+        <v>373145498.39999998</v>
       </c>
       <c r="AG10">
-        <v>360771926.5</v>
+        <v>387074438.5</v>
       </c>
       <c r="AH10">
-        <v>374237309.69999999</v>
+        <v>401272037.60000002</v>
       </c>
       <c r="AI10">
-        <v>387980423</v>
+        <v>415729484.19999999</v>
       </c>
       <c r="AJ10">
-        <v>402043237</v>
+        <v>430484962.89999998</v>
       </c>
       <c r="AK10">
-        <v>416460554.39999998</v>
+        <v>445569973</v>
       </c>
       <c r="AL10">
-        <v>431248936.5</v>
+        <v>460997655.80000001</v>
       </c>
       <c r="AM10">
-        <v>446384187.39999998</v>
+        <v>476739775.39999998</v>
       </c>
       <c r="AN10">
-        <v>461907435.69999999</v>
+        <v>492831911.89999998</v>
       </c>
       <c r="AO10">
-        <v>477841510.10000002</v>
+        <v>509291827.89999998</v>
       </c>
       <c r="AP10">
-        <v>494244814.60000002</v>
+        <v>526173269.69999999</v>
       </c>
       <c r="AQ10">
-        <v>511053956.10000002</v>
+        <v>543409107.60000002</v>
       </c>
       <c r="AR10">
-        <v>528250077.89999998</v>
+        <v>560977095.70000005</v>
       </c>
       <c r="AS10">
-        <v>545856327.5</v>
+        <v>578895385.29999995</v>
       </c>
       <c r="AT10">
-        <v>563809309.79999995</v>
+        <v>597096521</v>
       </c>
       <c r="AU10">
-        <v>582035150.70000005</v>
+        <v>615503794.5</v>
       </c>
       <c r="AV10">
-        <v>600452183.60000002</v>
+        <v>634033487</v>
       </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
@@ -6241,136 +6241,136 @@
         <v>661127</v>
       </c>
       <c r="E11">
-        <v>1570695.689</v>
+        <v>1875691.4240000001</v>
       </c>
       <c r="F11">
-        <v>2873115.656</v>
+        <v>3531050.3420000002</v>
       </c>
       <c r="G11">
-        <v>4198104.9280000003</v>
+        <v>5256734.8899999997</v>
       </c>
       <c r="H11">
-        <v>5322697.4009999996</v>
+        <v>6659155</v>
       </c>
       <c r="I11">
-        <v>6453008.0240000002</v>
+        <v>7994934.3710000003</v>
       </c>
       <c r="J11">
-        <v>7700498.6380000003</v>
+        <v>9407847.8210000005</v>
       </c>
       <c r="K11">
-        <v>9105911.9820000008</v>
+        <v>10965461.109999999</v>
       </c>
       <c r="L11">
-        <v>10653992.07</v>
+        <v>12666268.359999999</v>
       </c>
       <c r="M11">
-        <v>12281020.18</v>
+        <v>14455010.630000001</v>
       </c>
       <c r="N11">
-        <v>13746915.1</v>
+        <v>16086364.380000001</v>
       </c>
       <c r="O11">
-        <v>15522057.939999999</v>
+        <v>18076069.41</v>
       </c>
       <c r="P11">
-        <v>17875445.68</v>
+        <v>20692600.420000002</v>
       </c>
       <c r="Q11">
-        <v>21583434.899999999</v>
+        <v>24761715.600000001</v>
       </c>
       <c r="R11">
-        <v>26206806.670000002</v>
+        <v>29800489.16</v>
       </c>
       <c r="S11">
-        <v>31919517.649999999</v>
+        <v>36015334.119999997</v>
       </c>
       <c r="T11">
-        <v>38386446.810000002</v>
+        <v>43023155.509999998</v>
       </c>
       <c r="U11">
-        <v>45380808.899999999</v>
+        <v>50604764.049999997</v>
       </c>
       <c r="V11">
-        <v>52060903.799999997</v>
+        <v>57860244.409999996</v>
       </c>
       <c r="W11">
-        <v>58611420.700000003</v>
+        <v>65015184.780000001</v>
       </c>
       <c r="X11">
-        <v>64086054.079999998</v>
+        <v>71049428.959999904</v>
       </c>
       <c r="Y11">
-        <v>68731331.760000005</v>
+        <v>76209264.299999997</v>
       </c>
       <c r="Z11">
-        <v>73265484.659999996</v>
+        <v>81248549.340000004</v>
       </c>
       <c r="AA11">
-        <v>77877083.909999996</v>
+        <v>86372363.579999998</v>
       </c>
       <c r="AB11">
-        <v>82681046.400000006</v>
+        <v>91705637.030000001</v>
       </c>
       <c r="AC11">
-        <v>87779009.049999997</v>
+        <v>97355321.959999904</v>
       </c>
       <c r="AD11">
-        <v>93205348.900000006</v>
+        <v>103358213.5</v>
       </c>
       <c r="AE11">
-        <v>98988492.760000005</v>
+        <v>109745441.7</v>
       </c>
       <c r="AF11">
-        <v>105150518.09999999</v>
+        <v>116542314.7</v>
       </c>
       <c r="AG11">
-        <v>111714451.5</v>
+        <v>123770202.8</v>
       </c>
       <c r="AH11">
-        <v>118669206.8</v>
+        <v>131417171.40000001</v>
       </c>
       <c r="AI11">
-        <v>126020292.3</v>
+        <v>139488505.09999999</v>
       </c>
       <c r="AJ11">
-        <v>133815216.09999999</v>
+        <v>148031783.09999999</v>
       </c>
       <c r="AK11">
-        <v>142092802.19999999</v>
+        <v>157087119.09999999</v>
       </c>
       <c r="AL11">
-        <v>150883559.69999999</v>
+        <v>166686135.09999999</v>
       </c>
       <c r="AM11">
-        <v>160177259.69999999</v>
+        <v>176820438.09999999</v>
       </c>
       <c r="AN11">
-        <v>169995846</v>
+        <v>187514761.40000001</v>
       </c>
       <c r="AO11">
-        <v>180375121.80000001</v>
+        <v>198806945.59999999</v>
       </c>
       <c r="AP11">
-        <v>191394264.59999999</v>
+        <v>210777644.19999999</v>
       </c>
       <c r="AQ11">
-        <v>203046487.59999999</v>
+        <v>223421097</v>
       </c>
       <c r="AR11">
-        <v>215361341.80000001</v>
+        <v>236767767.5</v>
       </c>
       <c r="AS11">
-        <v>228397276.59999999</v>
+        <v>250877000.09999999</v>
       </c>
       <c r="AT11">
-        <v>242155747.69999999</v>
+        <v>265750853.40000001</v>
       </c>
       <c r="AU11">
-        <v>256655335.69999999</v>
+        <v>281407169.5</v>
       </c>
       <c r="AV11">
-        <v>271886812.39999998</v>
+        <v>297835611</v>
       </c>
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
@@ -6378,145 +6378,145 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C12">
-        <v>7966.4202385211802</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D12">
-        <v>8186.3743000000004</v>
+        <v>8022.1280880000004</v>
       </c>
       <c r="E12">
-        <v>9701.1703209999996</v>
+        <v>9534.2584409999999</v>
       </c>
       <c r="F12">
-        <v>10407.805619999999</v>
+        <v>10282.47286</v>
       </c>
       <c r="G12">
-        <v>10623.29257</v>
+        <v>10539.521699999999</v>
       </c>
       <c r="H12">
-        <v>8737.1823260000001</v>
+        <v>8556.5195359999998</v>
       </c>
       <c r="I12">
-        <v>8818.4625849999902</v>
+        <v>8591.9026649999996</v>
       </c>
       <c r="J12">
-        <v>9940.1322770000006</v>
+        <v>9694.266243</v>
       </c>
       <c r="K12">
-        <v>11282.96738</v>
+        <v>11036.826069999999</v>
       </c>
       <c r="L12">
-        <v>11424.569079999999</v>
+        <v>11182.380649999999</v>
       </c>
       <c r="M12">
-        <v>10506.44162</v>
+        <v>10264.94281</v>
       </c>
       <c r="N12">
-        <v>7837.733682</v>
+        <v>7599.993982</v>
       </c>
       <c r="O12">
-        <v>7159.1341110000003</v>
+        <v>6964.345609</v>
       </c>
       <c r="P12">
-        <v>8568.6068030000006</v>
+        <v>8403.7953550000002</v>
       </c>
       <c r="Q12">
-        <v>13270.076129999999</v>
+        <v>13144.305909999999</v>
       </c>
       <c r="R12">
-        <v>15282.475899999999</v>
+        <v>15161.77334</v>
       </c>
       <c r="S12">
-        <v>18046.88349</v>
+        <v>17946.497889999999</v>
       </c>
       <c r="T12">
-        <v>18829.531660000001</v>
+        <v>18731.853050000002</v>
       </c>
       <c r="U12">
-        <v>19429.48156</v>
+        <v>19341.830549999999</v>
       </c>
       <c r="V12">
-        <v>20279.491099999999</v>
+        <v>20201.412240000001</v>
       </c>
       <c r="W12">
-        <v>23720.276249999999</v>
+        <v>23671.50894</v>
       </c>
       <c r="X12">
-        <v>26689.909650000001</v>
+        <v>26658.756870000001</v>
       </c>
       <c r="Y12">
-        <v>28247.954610000001</v>
+        <v>28231.747480000002</v>
       </c>
       <c r="Z12">
-        <v>28850.194960000001</v>
+        <v>28838.489580000001</v>
       </c>
       <c r="AA12">
-        <v>28864.591349999999</v>
+        <v>28844.901470000001</v>
       </c>
       <c r="AB12">
-        <v>29415.639640000001</v>
+        <v>29375.17958</v>
       </c>
       <c r="AC12">
-        <v>30604.34504</v>
+        <v>30539.323659999998</v>
       </c>
       <c r="AD12">
-        <v>30894.227859999999</v>
+        <v>30808.928349999998</v>
       </c>
       <c r="AE12">
-        <v>30755.587609999999</v>
+        <v>30656.745190000001</v>
       </c>
       <c r="AF12">
-        <v>30705.280340000001</v>
+        <v>30597.126479999999</v>
       </c>
       <c r="AG12">
-        <v>30636.998920000002</v>
+        <v>30516.56769</v>
       </c>
       <c r="AH12">
-        <v>30373.837309999999</v>
+        <v>30239.176869999999</v>
       </c>
       <c r="AI12">
-        <v>30157.484110000001</v>
+        <v>30010.63667</v>
       </c>
       <c r="AJ12">
-        <v>30003.9159</v>
+        <v>29841.224429999998</v>
       </c>
       <c r="AK12">
-        <v>30031.489730000001</v>
+        <v>29851.401290000002</v>
       </c>
       <c r="AL12">
-        <v>31062.437430000002</v>
+        <v>30855.025710000002</v>
       </c>
       <c r="AM12">
-        <v>31924.517660000001</v>
+        <v>31687.6518</v>
       </c>
       <c r="AN12">
-        <v>32189.328130000002</v>
+        <v>31941.42613</v>
       </c>
       <c r="AO12">
-        <v>32259.308069999999</v>
+        <v>32001.414089999998</v>
       </c>
       <c r="AP12">
-        <v>32240.896260000001</v>
+        <v>31971.433939999999</v>
       </c>
       <c r="AQ12">
-        <v>32166.560890000001</v>
+        <v>31884.963589999999</v>
       </c>
       <c r="AR12">
-        <v>32261.434379999999</v>
+        <v>31959.815060000001</v>
       </c>
       <c r="AS12">
-        <v>32982.10353</v>
+        <v>32639.899410000002</v>
       </c>
       <c r="AT12">
-        <v>33868.678979999997</v>
+        <v>33476.382610000001</v>
       </c>
       <c r="AU12">
-        <v>34809.153890000001</v>
+        <v>34363.599699999999</v>
       </c>
       <c r="AV12">
-        <v>35733.996279999999</v>
+        <v>35235.453079999999</v>
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
@@ -6524,145 +6524,145 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>401167.83705106698</v>
+        <v>409662.49706947699</v>
       </c>
       <c r="C13">
-        <v>407608.716436335</v>
+        <v>416239.76096901699</v>
       </c>
       <c r="D13">
-        <v>414153.0062</v>
+        <v>422922.625</v>
       </c>
       <c r="E13">
-        <v>512305.85320000001</v>
+        <v>521176.73670000001</v>
       </c>
       <c r="F13">
-        <v>554575.11</v>
+        <v>565935.13100000005</v>
       </c>
       <c r="G13">
-        <v>560405.52729999996</v>
+        <v>574293.12410000002</v>
       </c>
       <c r="H13">
-        <v>444416.26209999999</v>
+        <v>451320.11180000001</v>
       </c>
       <c r="I13">
-        <v>442715.61219999997</v>
+        <v>446202.5465</v>
       </c>
       <c r="J13">
-        <v>495132.52679999999</v>
+        <v>497037.24320000003</v>
       </c>
       <c r="K13">
-        <v>566430.42610000004</v>
+        <v>567902.00769999996</v>
       </c>
       <c r="L13">
-        <v>568014.10129999998</v>
+        <v>569861.89119999995</v>
       </c>
       <c r="M13">
-        <v>511188.31060000003</v>
+        <v>513672.21470000001</v>
       </c>
       <c r="N13">
-        <v>368053.46590000001</v>
+        <v>372000.83409999998</v>
       </c>
       <c r="O13">
-        <v>348236.66960000002</v>
+        <v>354667.6606</v>
       </c>
       <c r="P13">
-        <v>426497.20899999997</v>
+        <v>434004.98619999998</v>
       </c>
       <c r="Q13">
-        <v>690615.42890000006</v>
+        <v>697667.215499999</v>
       </c>
       <c r="R13">
-        <v>785415.02399999998</v>
+        <v>792047.933499999</v>
       </c>
       <c r="S13">
-        <v>934592.26170000003</v>
+        <v>940462.86750000005</v>
       </c>
       <c r="T13">
-        <v>955620.32929999998</v>
+        <v>961610.02439999999</v>
       </c>
       <c r="U13">
-        <v>979229.13309999998</v>
+        <v>985316.62390000001</v>
       </c>
       <c r="V13">
-        <v>1014744.6360000001</v>
+        <v>1020709.091</v>
       </c>
       <c r="W13">
-        <v>1193173.8419999999</v>
+        <v>1197882.4339999999</v>
       </c>
       <c r="X13">
-        <v>1332072.335</v>
+        <v>1335691.2620000001</v>
       </c>
       <c r="Y13">
-        <v>1404018.2860000001</v>
+        <v>1407025.5889999999</v>
       </c>
       <c r="Z13">
-        <v>1421944.5959999999</v>
+        <v>1424603.203</v>
       </c>
       <c r="AA13">
-        <v>1401412.7919999999</v>
+        <v>1403935.7409999999</v>
       </c>
       <c r="AB13">
-        <v>1401736.696</v>
+        <v>1403626.469</v>
       </c>
       <c r="AC13">
-        <v>1429635.8940000001</v>
+        <v>1430514.25</v>
       </c>
       <c r="AD13">
-        <v>1413913.1159999999</v>
+        <v>1414407.3940000001</v>
       </c>
       <c r="AE13">
-        <v>1382074.5789999999</v>
+        <v>1382487.2139999999</v>
       </c>
       <c r="AF13">
-        <v>1354679.2609999999</v>
+        <v>1355139.851</v>
       </c>
       <c r="AG13">
-        <v>1325121.216</v>
+        <v>1325594.0349999999</v>
       </c>
       <c r="AH13">
-        <v>1287251.2209999999</v>
+        <v>1287741.6040000001</v>
       </c>
       <c r="AI13">
-        <v>1252540.1710000001</v>
+        <v>1253045.0689999999</v>
       </c>
       <c r="AJ13">
-        <v>1220795.298</v>
+        <v>1221121.4140000001</v>
       </c>
       <c r="AK13">
-        <v>1196867.888</v>
+        <v>1196967.8910000001</v>
       </c>
       <c r="AL13">
-        <v>1212023.419</v>
+        <v>1211290.5290000001</v>
       </c>
       <c r="AM13">
-        <v>1217311.118</v>
+        <v>1215950.1740000001</v>
       </c>
       <c r="AN13">
-        <v>1202160.824</v>
+        <v>1200623.5220000001</v>
       </c>
       <c r="AO13">
-        <v>1179790.0020000001</v>
+        <v>1178141.1040000001</v>
       </c>
       <c r="AP13">
-        <v>1154429.621</v>
+        <v>1152627.179</v>
       </c>
       <c r="AQ13">
-        <v>1127613.6680000001</v>
+        <v>1125609.189</v>
       </c>
       <c r="AR13">
-        <v>1106694.0919999999</v>
+        <v>1104295.0789999999</v>
       </c>
       <c r="AS13">
-        <v>1105707.0530000001</v>
+        <v>1102397.713</v>
       </c>
       <c r="AT13">
-        <v>1109420.1240000001</v>
+        <v>1104996.548</v>
       </c>
       <c r="AU13">
-        <v>1114467.3470000001</v>
+        <v>1108857.9920000001</v>
       </c>
       <c r="AV13">
-        <v>1118471.6839999999</v>
+        <v>1111710.304</v>
       </c>
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
@@ -6825,136 +6825,136 @@
         <v>188893454</v>
       </c>
       <c r="E15">
-        <v>192890472.5</v>
+        <v>191063764.30000001</v>
       </c>
       <c r="F15">
-        <v>195972600.59999999</v>
+        <v>192370890.30000001</v>
       </c>
       <c r="G15">
-        <v>198367042.5</v>
+        <v>193041127.30000001</v>
       </c>
       <c r="H15">
-        <v>201726129.59999999</v>
+        <v>194680942.30000001</v>
       </c>
       <c r="I15">
-        <v>204743452.80000001</v>
+        <v>196011318.5</v>
       </c>
       <c r="J15">
-        <v>206557692.40000001</v>
+        <v>196206590.80000001</v>
       </c>
       <c r="K15">
-        <v>206969909.5</v>
+        <v>195081039.30000001</v>
       </c>
       <c r="L15">
-        <v>207129634.5</v>
+        <v>193724931.90000001</v>
       </c>
       <c r="M15">
-        <v>208073401.19999999</v>
+        <v>193110902.69999999</v>
       </c>
       <c r="N15">
-        <v>210932186.90000001</v>
+        <v>194281637.40000001</v>
       </c>
       <c r="O15">
-        <v>214522650.30000001</v>
+        <v>196119853.19999999</v>
       </c>
       <c r="P15">
-        <v>217170466.30000001</v>
+        <v>197106337.90000001</v>
       </c>
       <c r="Q15">
-        <v>216580420.40000001</v>
+        <v>195170429.80000001</v>
       </c>
       <c r="R15">
-        <v>214655876.19999999</v>
+        <v>192061051.5</v>
       </c>
       <c r="S15">
-        <v>211106389.40000001</v>
+        <v>187527128.69999999</v>
       </c>
       <c r="T15">
-        <v>207180855.5</v>
+        <v>182694217</v>
       </c>
       <c r="U15">
-        <v>203017593.30000001</v>
+        <v>177686812</v>
       </c>
       <c r="V15">
-        <v>198698802</v>
+        <v>172578667.09999999</v>
       </c>
       <c r="W15">
-        <v>193171923.80000001</v>
+        <v>166461552.59999999</v>
       </c>
       <c r="X15">
-        <v>186916466.40000001</v>
+        <v>159774581.90000001</v>
       </c>
       <c r="Y15">
-        <v>180653841.80000001</v>
+        <v>153155052.5</v>
       </c>
       <c r="Z15">
-        <v>174731054.59999999</v>
+        <v>146908139.90000001</v>
       </c>
       <c r="AA15">
-        <v>169232227.59999999</v>
+        <v>141107559.5</v>
       </c>
       <c r="AB15">
-        <v>163676595.30000001</v>
+        <v>135352093</v>
       </c>
       <c r="AC15">
-        <v>157856281.69999999</v>
+        <v>129469458.09999999</v>
       </c>
       <c r="AD15">
-        <v>152275698.19999999</v>
+        <v>123870877.59999999</v>
       </c>
       <c r="AE15">
-        <v>147116623.69999999</v>
+        <v>118698841.40000001</v>
       </c>
       <c r="AF15">
-        <v>142362695.59999999</v>
+        <v>113933920.2</v>
       </c>
       <c r="AG15">
-        <v>137976998.69999999</v>
+        <v>109541565.5</v>
       </c>
       <c r="AH15">
-        <v>133955395.40000001</v>
+        <v>105512758.90000001</v>
       </c>
       <c r="AI15">
-        <v>130281469.7</v>
+        <v>101828331.5</v>
       </c>
       <c r="AJ15">
-        <v>126942918.3</v>
+        <v>98475130.920000002</v>
       </c>
       <c r="AK15">
-        <v>123830164.3</v>
+        <v>95363559.989999995</v>
       </c>
       <c r="AL15">
-        <v>120580810.5</v>
+        <v>92208896.260000005</v>
       </c>
       <c r="AM15">
-        <v>117261649.40000001</v>
+        <v>89062822.159999996</v>
       </c>
       <c r="AN15">
-        <v>114096236.90000001</v>
+        <v>86088461.730000004</v>
       </c>
       <c r="AO15">
-        <v>111146652</v>
+        <v>83329673.129999995</v>
       </c>
       <c r="AP15">
-        <v>108430956</v>
+        <v>80796765.760000005</v>
       </c>
       <c r="AQ15">
-        <v>105952748.40000001</v>
+        <v>78488220.269999996</v>
       </c>
       <c r="AR15">
-        <v>103627942.7</v>
+        <v>76338797.379999995</v>
       </c>
       <c r="AS15">
-        <v>101213263.40000001</v>
+        <v>74167575.200000003</v>
       </c>
       <c r="AT15">
-        <v>98646736.450000003</v>
+        <v>71926823.560000002</v>
       </c>
       <c r="AU15">
-        <v>95928670</v>
+        <v>69614350.920000002</v>
       </c>
       <c r="AV15">
-        <v>93087655.730000004</v>
+        <v>67248186.879999995</v>
       </c>
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
@@ -6971,136 +6971,136 @@
         <v>412154138</v>
       </c>
       <c r="E16">
-        <v>397810191.5</v>
+        <v>399760841.10000002</v>
       </c>
       <c r="F16">
-        <v>383408628.10000002</v>
+        <v>387113174.30000001</v>
       </c>
       <c r="G16">
-        <v>369492117.69999999</v>
+        <v>374756494.19999999</v>
       </c>
       <c r="H16">
-        <v>358775875.69999999</v>
+        <v>365465593.80000001</v>
       </c>
       <c r="I16">
-        <v>348504845.80000001</v>
+        <v>356468435</v>
       </c>
       <c r="J16">
-        <v>337377244.30000001</v>
+        <v>346439416.80000001</v>
       </c>
       <c r="K16">
-        <v>325402099.39999998</v>
+        <v>335377600.10000002</v>
       </c>
       <c r="L16">
-        <v>314251454.89999998</v>
+        <v>325017050.10000002</v>
       </c>
       <c r="M16">
-        <v>305196594.69999999</v>
+        <v>316704904.30000001</v>
       </c>
       <c r="N16">
-        <v>299519536.30000001</v>
+        <v>311816568.69999999</v>
       </c>
       <c r="O16">
-        <v>295425133</v>
+        <v>308486200.69999999</v>
       </c>
       <c r="P16">
-        <v>290688668.80000001</v>
+        <v>304380859.89999998</v>
       </c>
       <c r="Q16">
-        <v>282984711.30000001</v>
+        <v>296998277.30000001</v>
       </c>
       <c r="R16">
-        <v>274616891.60000002</v>
+        <v>288783084.89999998</v>
       </c>
       <c r="S16">
-        <v>265312456.59999999</v>
+        <v>279421683.5</v>
       </c>
       <c r="T16">
-        <v>256230092.59999999</v>
+        <v>270170955.19999999</v>
       </c>
       <c r="U16">
-        <v>247485132.90000001</v>
+        <v>261154462</v>
       </c>
       <c r="V16">
-        <v>239037612.90000001</v>
+        <v>252346472.59999999</v>
       </c>
       <c r="W16">
-        <v>229914887.40000001</v>
+        <v>242686590.19999999</v>
       </c>
       <c r="X16">
-        <v>220560384.40000001</v>
+        <v>232661896.09999999</v>
       </c>
       <c r="Y16">
-        <v>211685226.69999999</v>
+        <v>223041210.19999999</v>
       </c>
       <c r="Z16">
-        <v>203558189.19999999</v>
+        <v>214127153</v>
       </c>
       <c r="AA16">
-        <v>196207766.90000001</v>
+        <v>205966927.5</v>
       </c>
       <c r="AB16">
-        <v>189203486.09999999</v>
+        <v>198103163.69999999</v>
       </c>
       <c r="AC16">
-        <v>182305303.19999999</v>
+        <v>190290827.09999999</v>
       </c>
       <c r="AD16">
-        <v>175847176.19999999</v>
+        <v>182912421</v>
       </c>
       <c r="AE16">
-        <v>169947358.5</v>
+        <v>176105037.69999999</v>
       </c>
       <c r="AF16">
-        <v>164560594.30000001</v>
+        <v>169828995.5</v>
       </c>
       <c r="AG16">
-        <v>159645168.80000001</v>
+        <v>164046634.69999999</v>
       </c>
       <c r="AH16">
-        <v>155183592.90000001</v>
+        <v>158744164.30000001</v>
       </c>
       <c r="AI16">
-        <v>151138260.09999999</v>
+        <v>153886020.30000001</v>
       </c>
       <c r="AJ16">
-        <v>147478045.80000001</v>
+        <v>149444885.69999999</v>
       </c>
       <c r="AK16">
-        <v>144116280.69999999</v>
+        <v>145329183.30000001</v>
       </c>
       <c r="AL16">
-        <v>140787264.09999999</v>
+        <v>141253755.19999999</v>
       </c>
       <c r="AM16">
-        <v>137510047.09999999</v>
+        <v>137246758.30000001</v>
       </c>
       <c r="AN16">
-        <v>134383891.5</v>
+        <v>133415596.90000001</v>
       </c>
       <c r="AO16">
-        <v>131426722.7</v>
+        <v>129782762</v>
       </c>
       <c r="AP16">
-        <v>128641935.59999999</v>
+        <v>126353832.3</v>
       </c>
       <c r="AQ16">
-        <v>126031123.8</v>
+        <v>123130508.8</v>
       </c>
       <c r="AR16">
-        <v>123539030.8</v>
+        <v>120055359.40000001</v>
       </c>
       <c r="AS16">
-        <v>121004518</v>
+        <v>116960849.90000001</v>
       </c>
       <c r="AT16">
-        <v>118385364.7</v>
+        <v>113804709.7</v>
       </c>
       <c r="AU16">
-        <v>115680849.09999999</v>
+        <v>110587532.90000001</v>
       </c>
       <c r="AV16">
-        <v>112908064.40000001</v>
+        <v>107327783.3</v>
       </c>
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.25">
@@ -7117,136 +7117,136 @@
         <v>786713699</v>
       </c>
       <c r="E17">
-        <v>765151720.10000002</v>
+        <v>767697315.20000005</v>
       </c>
       <c r="F17">
-        <v>742848404.10000002</v>
+        <v>747867086.29999995</v>
       </c>
       <c r="G17">
-        <v>721013825.5</v>
+        <v>728430631.79999995</v>
       </c>
       <c r="H17">
-        <v>704493791.79999995</v>
+        <v>714280416.60000002</v>
       </c>
       <c r="I17">
-        <v>688605379.20000005</v>
+        <v>700681344.79999995</v>
       </c>
       <c r="J17">
-        <v>671106976.79999995</v>
+        <v>685365464.70000005</v>
       </c>
       <c r="K17">
-        <v>651745399</v>
+        <v>668066588.89999998</v>
       </c>
       <c r="L17">
-        <v>633284211.29999995</v>
+        <v>651608861.20000005</v>
       </c>
       <c r="M17">
-        <v>617987009</v>
+        <v>638329540.5</v>
       </c>
       <c r="N17">
-        <v>608496979.39999998</v>
+        <v>630965417.79999995</v>
       </c>
       <c r="O17">
-        <v>601344786.70000005</v>
+        <v>625921224.89999998</v>
       </c>
       <c r="P17">
-        <v>592570777.39999998</v>
+        <v>619119672.39999998</v>
       </c>
       <c r="Q17">
-        <v>577386690.70000005</v>
+        <v>605555013.79999995</v>
       </c>
       <c r="R17">
-        <v>560460677.10000002</v>
+        <v>590111586.29999995</v>
       </c>
       <c r="S17">
-        <v>541087654.60000002</v>
+        <v>572016937.29999995</v>
       </c>
       <c r="T17">
-        <v>521981536.69999999</v>
+        <v>554128849.20000005</v>
       </c>
       <c r="U17">
-        <v>503358252.5</v>
+        <v>536660753.80000001</v>
       </c>
       <c r="V17">
-        <v>485133574.80000001</v>
+        <v>519528075.5</v>
       </c>
       <c r="W17">
-        <v>465023657.80000001</v>
+        <v>500271972.5</v>
       </c>
       <c r="X17">
-        <v>444033855.89999998</v>
+        <v>479963611.80000001</v>
       </c>
       <c r="Y17">
-        <v>423703636.39999998</v>
+        <v>460246646.10000002</v>
       </c>
       <c r="Z17">
-        <v>404765350.80000001</v>
+        <v>441913255.10000002</v>
       </c>
       <c r="AA17">
-        <v>387435816.30000001</v>
+        <v>425205797.10000002</v>
       </c>
       <c r="AB17">
-        <v>370921220</v>
+        <v>409257736.69999999</v>
       </c>
       <c r="AC17">
-        <v>354737150.60000002</v>
+        <v>393535077.80000001</v>
       </c>
       <c r="AD17">
-        <v>339595437.5</v>
+        <v>378829195.39999998</v>
       </c>
       <c r="AE17">
-        <v>325723033.19999999</v>
+        <v>365395585.5</v>
       </c>
       <c r="AF17">
-        <v>313003552</v>
+        <v>353112527.10000002</v>
       </c>
       <c r="AG17">
-        <v>301344810.10000002</v>
+        <v>341887450.10000002</v>
       </c>
       <c r="AH17">
-        <v>290719125.89999998</v>
+        <v>331698358.5</v>
       </c>
       <c r="AI17">
-        <v>281032347.60000002</v>
+        <v>322447572.5</v>
       </c>
       <c r="AJ17">
-        <v>272202936.10000002</v>
+        <v>314056210.10000002</v>
       </c>
       <c r="AK17">
-        <v>264047186.59999999</v>
+        <v>306320308.89999998</v>
       </c>
       <c r="AL17">
-        <v>256014575.30000001</v>
+        <v>298601342.80000001</v>
       </c>
       <c r="AM17">
-        <v>248168520.40000001</v>
+        <v>290982459.69999999</v>
       </c>
       <c r="AN17">
-        <v>240746377.40000001</v>
+        <v>283740232.39999998</v>
       </c>
       <c r="AO17">
-        <v>233791414</v>
+        <v>276935749.39999998</v>
       </c>
       <c r="AP17">
-        <v>227303380.59999999</v>
+        <v>270579260.30000001</v>
       </c>
       <c r="AQ17">
-        <v>221271931.19999999</v>
+        <v>264667323.40000001</v>
       </c>
       <c r="AR17">
-        <v>215579632.19999999</v>
+        <v>259067774.80000001</v>
       </c>
       <c r="AS17">
-        <v>209912485.30000001</v>
+        <v>253407458.30000001</v>
       </c>
       <c r="AT17">
-        <v>204191122.59999999</v>
+        <v>247593672.19999999</v>
       </c>
       <c r="AU17">
-        <v>198410761.09999999</v>
+        <v>241623100.19999999</v>
       </c>
       <c r="AV17">
-        <v>192599948.80000001</v>
+        <v>235532646.80000001</v>
       </c>
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.25">
@@ -7263,136 +7263,136 @@
         <v>661409532</v>
       </c>
       <c r="E18">
-        <v>687654837.10000002</v>
+        <v>679048358.89999998</v>
       </c>
       <c r="F18">
-        <v>713532820.89999998</v>
+        <v>696700866.10000002</v>
       </c>
       <c r="G18">
-        <v>739315723.89999998</v>
+        <v>714621712</v>
       </c>
       <c r="H18">
-        <v>762734330.20000005</v>
+        <v>730411692.70000005</v>
       </c>
       <c r="I18">
-        <v>786229123</v>
+        <v>746557353</v>
       </c>
       <c r="J18">
-        <v>811239684.89999998</v>
+        <v>764544554.29999995</v>
       </c>
       <c r="K18">
-        <v>837175973.20000005</v>
+        <v>783836993.60000002</v>
       </c>
       <c r="L18">
-        <v>861943251.70000005</v>
+        <v>802262679.70000005</v>
       </c>
       <c r="M18">
-        <v>883954354.89999998</v>
+        <v>818139898</v>
       </c>
       <c r="N18">
-        <v>905015713</v>
+        <v>832553063.70000005</v>
       </c>
       <c r="O18">
-        <v>922669857.89999998</v>
+        <v>843827707.5</v>
       </c>
       <c r="P18">
-        <v>939570313.70000005</v>
+        <v>854827711.60000002</v>
       </c>
       <c r="Q18">
-        <v>954214492.89999998</v>
+        <v>864860588.5</v>
       </c>
       <c r="R18">
-        <v>967737555.20000005</v>
+        <v>874399468.5</v>
       </c>
       <c r="S18">
-        <v>978321526.60000002</v>
+        <v>881924485.70000005</v>
       </c>
       <c r="T18">
-        <v>987905171.5</v>
+        <v>888831347.39999998</v>
       </c>
       <c r="U18">
-        <v>997456936.79999995</v>
+        <v>895867669.5</v>
       </c>
       <c r="V18">
-        <v>1004236597</v>
+        <v>900701833.70000005</v>
       </c>
       <c r="W18">
-        <v>1004509973</v>
+        <v>900272406.89999998</v>
       </c>
       <c r="X18">
-        <v>998747365.89999998</v>
+        <v>894825721.39999998</v>
       </c>
       <c r="Y18">
-        <v>988036919.20000005</v>
+        <v>885127029.39999998</v>
       </c>
       <c r="Z18">
-        <v>974126707.39999998</v>
+        <v>872625186</v>
       </c>
       <c r="AA18">
-        <v>958505187</v>
+        <v>858602650.10000002</v>
       </c>
       <c r="AB18">
-        <v>941678004.10000002</v>
+        <v>843595041</v>
       </c>
       <c r="AC18">
-        <v>924102107.20000005</v>
+        <v>828020761.79999995</v>
       </c>
       <c r="AD18">
-        <v>906189712</v>
+        <v>812135594.10000002</v>
       </c>
       <c r="AE18">
-        <v>888106582.29999995</v>
+        <v>796048063.20000005</v>
       </c>
       <c r="AF18">
-        <v>869720439.60000002</v>
+        <v>779636564.39999998</v>
       </c>
       <c r="AG18">
-        <v>851340085.29999995</v>
+        <v>763177487.60000002</v>
       </c>
       <c r="AH18">
-        <v>833097458.20000005</v>
+        <v>746787903.10000002</v>
       </c>
       <c r="AI18">
-        <v>814836141.60000002</v>
+        <v>730330053.20000005</v>
       </c>
       <c r="AJ18">
-        <v>796613593</v>
+        <v>713857595.79999995</v>
       </c>
       <c r="AK18">
-        <v>778393129.89999998</v>
+        <v>697351381.70000005</v>
       </c>
       <c r="AL18">
-        <v>759660527.79999995</v>
+        <v>680418280.79999995</v>
       </c>
       <c r="AM18">
-        <v>740977352.20000005</v>
+        <v>663542775.29999995</v>
       </c>
       <c r="AN18">
-        <v>722470747.20000005</v>
+        <v>646814866</v>
       </c>
       <c r="AO18">
-        <v>704221419.29999995</v>
+        <v>630296933.79999995</v>
       </c>
       <c r="AP18">
-        <v>686341532.60000002</v>
+        <v>614088552.29999995</v>
       </c>
       <c r="AQ18">
-        <v>668766704.5</v>
+        <v>598129205.79999995</v>
       </c>
       <c r="AR18">
-        <v>651473648.70000005</v>
+        <v>582409783.10000002</v>
       </c>
       <c r="AS18">
-        <v>634389174</v>
+        <v>566900615.70000005</v>
       </c>
       <c r="AT18">
-        <v>617469296.5</v>
+        <v>551567542.89999998</v>
       </c>
       <c r="AU18">
-        <v>600664259.79999995</v>
+        <v>536362614.39999998</v>
       </c>
       <c r="AV18">
-        <v>584569229</v>
+        <v>521881024.89999998</v>
       </c>
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.25">
@@ -7409,136 +7409,136 @@
         <v>300942006</v>
       </c>
       <c r="E19">
-        <v>325989961.60000002</v>
+        <v>329969297.60000002</v>
       </c>
       <c r="F19">
-        <v>352084282.69999999</v>
+        <v>359742700</v>
       </c>
       <c r="G19">
-        <v>378165535</v>
+        <v>389215747.30000001</v>
       </c>
       <c r="H19">
-        <v>398508244.89999998</v>
+        <v>413578731.80000001</v>
       </c>
       <c r="I19">
-        <v>418161329</v>
+        <v>437576984.80000001</v>
       </c>
       <c r="J19">
-        <v>439605844.10000002</v>
+        <v>463484353.60000002</v>
       </c>
       <c r="K19">
-        <v>463289674.5</v>
+        <v>491584419.10000002</v>
       </c>
       <c r="L19">
-        <v>486295724.80000001</v>
+        <v>518896396.89999998</v>
       </c>
       <c r="M19">
-        <v>506208653.5</v>
+        <v>542965479.89999998</v>
       </c>
       <c r="N19">
-        <v>521190493.5</v>
+        <v>562545207</v>
       </c>
       <c r="O19">
-        <v>533918566.89999998</v>
+        <v>579549240.79999995</v>
       </c>
       <c r="P19">
-        <v>548554139</v>
+        <v>598050840</v>
       </c>
       <c r="Q19">
-        <v>569962988.5</v>
+        <v>622216441.10000002</v>
       </c>
       <c r="R19">
-        <v>593083780.29999995</v>
+        <v>647543118.89999998</v>
       </c>
       <c r="S19">
-        <v>618800343.29999995</v>
+        <v>674636551.39999998</v>
       </c>
       <c r="T19">
-        <v>643887675.10000002</v>
+        <v>700801880.70000005</v>
       </c>
       <c r="U19">
-        <v>669030140.89999998</v>
+        <v>726936793</v>
       </c>
       <c r="V19">
-        <v>693271044</v>
+        <v>751663155.10000002</v>
       </c>
       <c r="W19">
-        <v>718644500.79999995</v>
+        <v>776362385.5</v>
       </c>
       <c r="X19">
-        <v>743440895.79999995</v>
+        <v>799537069.10000002</v>
       </c>
       <c r="Y19">
-        <v>765809004.29999995</v>
+        <v>819629072</v>
       </c>
       <c r="Z19">
-        <v>784936397.79999995</v>
+        <v>836138223.29999995</v>
       </c>
       <c r="AA19">
-        <v>800598287.60000002</v>
+        <v>849058815.70000005</v>
       </c>
       <c r="AB19">
-        <v>813833776.29999995</v>
+        <v>859434286.60000002</v>
       </c>
       <c r="AC19">
-        <v>825602040.70000005</v>
+        <v>868279705.60000002</v>
       </c>
       <c r="AD19">
-        <v>835116764.39999998</v>
+        <v>874939394</v>
       </c>
       <c r="AE19">
-        <v>842286085.29999995</v>
+        <v>879358884.20000005</v>
       </c>
       <c r="AF19">
-        <v>847263048.10000002</v>
+        <v>881667531</v>
       </c>
       <c r="AG19">
-        <v>850284027.79999995</v>
+        <v>882126278.5</v>
       </c>
       <c r="AH19">
-        <v>851457975.39999998</v>
+        <v>880853466.29999995</v>
       </c>
       <c r="AI19">
-        <v>850887991.39999998</v>
+        <v>877930855.39999998</v>
       </c>
       <c r="AJ19">
-        <v>848745109.20000005</v>
+        <v>873527961.5</v>
       </c>
       <c r="AK19">
-        <v>845241077.39999998</v>
+        <v>867836070.39999998</v>
       </c>
       <c r="AL19">
-        <v>840724444.10000002</v>
+        <v>861118809.5</v>
       </c>
       <c r="AM19">
-        <v>835417950.10000002</v>
+        <v>853658442.39999998</v>
       </c>
       <c r="AN19">
-        <v>829284447.89999998</v>
+        <v>845463548.20000005</v>
       </c>
       <c r="AO19">
-        <v>822390459.39999998</v>
+        <v>836612090.89999998</v>
       </c>
       <c r="AP19">
-        <v>814885739.20000005</v>
+        <v>827259694.20000005</v>
       </c>
       <c r="AQ19">
-        <v>806772899.20000005</v>
+        <v>817401512.79999995</v>
       </c>
       <c r="AR19">
-        <v>798181183</v>
+        <v>807152103.89999998</v>
       </c>
       <c r="AS19">
-        <v>789375700.20000005</v>
+        <v>796743751</v>
       </c>
       <c r="AT19">
-        <v>780396774.5</v>
+        <v>786210002</v>
       </c>
       <c r="AU19">
-        <v>771234567.10000002</v>
+        <v>775539858.39999998</v>
       </c>
       <c r="AV19">
-        <v>761856915.5</v>
+        <v>764703966.70000005</v>
       </c>
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.25">
@@ -7555,136 +7555,136 @@
         <v>42391824</v>
       </c>
       <c r="E20">
-        <v>46675187.380000003</v>
+        <v>48327797.350000001</v>
       </c>
       <c r="F20">
-        <v>51852903</v>
+        <v>55246987.710000001</v>
       </c>
       <c r="G20">
-        <v>57105090.280000001</v>
+        <v>62334992.270000003</v>
       </c>
       <c r="H20">
-        <v>61438669.100000001</v>
+        <v>67923206.430000007</v>
       </c>
       <c r="I20">
-        <v>65905159.450000003</v>
+        <v>73311926.799999997</v>
       </c>
       <c r="J20">
-        <v>70879847.420000002</v>
+        <v>79019560.629999995</v>
       </c>
       <c r="K20">
-        <v>76909945.150000006</v>
+        <v>85686810.739999995</v>
       </c>
       <c r="L20">
-        <v>83440128.719999999</v>
+        <v>92822209.859999999</v>
       </c>
       <c r="M20">
-        <v>89967966.540000007</v>
+        <v>99963264.049999997</v>
       </c>
       <c r="N20">
-        <v>95086621.840000004</v>
+        <v>105740186.90000001</v>
       </c>
       <c r="O20">
-        <v>101255214.59999999</v>
+        <v>112677970.8</v>
       </c>
       <c r="P20">
-        <v>109252701.8</v>
+        <v>121504490.40000001</v>
       </c>
       <c r="Q20">
-        <v>122754386.59999999</v>
+        <v>135904659.30000001</v>
       </c>
       <c r="R20">
-        <v>138390050.09999999</v>
+        <v>152452830.5</v>
       </c>
       <c r="S20">
-        <v>157681680.40000001</v>
+        <v>172687440.69999999</v>
       </c>
       <c r="T20">
-        <v>177484527</v>
+        <v>193405807.69999999</v>
       </c>
       <c r="U20">
-        <v>198068345.30000001</v>
+        <v>214886830</v>
       </c>
       <c r="V20">
-        <v>219769329.59999999</v>
+        <v>237463429.69999999</v>
       </c>
       <c r="W20">
-        <v>246202082.59999999</v>
+        <v>264763817.90000001</v>
       </c>
       <c r="X20">
-        <v>276304875</v>
+        <v>295675963.89999998</v>
       </c>
       <c r="Y20">
-        <v>308395932</v>
+        <v>328490762</v>
       </c>
       <c r="Z20">
-        <v>340829313.30000001</v>
+        <v>361530428.60000002</v>
       </c>
       <c r="AA20">
-        <v>372311452.89999998</v>
+        <v>393488703</v>
       </c>
       <c r="AB20">
-        <v>402980957.89999998</v>
+        <v>424496444.19999999</v>
       </c>
       <c r="AC20">
-        <v>433464297.19999999</v>
+        <v>455171469.69999999</v>
       </c>
       <c r="AD20">
-        <v>462831342.5</v>
+        <v>484600855.89999998</v>
       </c>
       <c r="AE20">
-        <v>490782430</v>
+        <v>512505967</v>
       </c>
       <c r="AF20">
-        <v>517417766.60000002</v>
+        <v>538999074.20000005</v>
       </c>
       <c r="AG20">
-        <v>542688165.29999995</v>
+        <v>564039337.10000002</v>
       </c>
       <c r="AH20">
-        <v>566404534.60000002</v>
+        <v>587450691.60000002</v>
       </c>
       <c r="AI20">
-        <v>588639343.20000005</v>
+        <v>609312687.89999998</v>
       </c>
       <c r="AJ20">
-        <v>609490239.60000002</v>
+        <v>629725186.29999995</v>
       </c>
       <c r="AK20">
-        <v>629087559</v>
+        <v>648822708.60000002</v>
       </c>
       <c r="AL20">
-        <v>648008774.70000005</v>
+        <v>667159796.10000002</v>
       </c>
       <c r="AM20">
-        <v>666158699.70000005</v>
+        <v>684650189.5</v>
       </c>
       <c r="AN20">
-        <v>683235684.89999998</v>
+        <v>701012471.29999995</v>
       </c>
       <c r="AO20">
-        <v>699161365.5</v>
+        <v>716178462.39999998</v>
       </c>
       <c r="AP20">
-        <v>713991787</v>
+        <v>730211112.79999995</v>
       </c>
       <c r="AQ20">
-        <v>727716266</v>
+        <v>743106025.20000005</v>
       </c>
       <c r="AR20">
-        <v>740454726.39999998</v>
+        <v>754983354.79999995</v>
       </c>
       <c r="AS20">
-        <v>752495153.79999995</v>
+        <v>766118794</v>
       </c>
       <c r="AT20">
-        <v>763881541.10000002</v>
+        <v>776555671.20000005</v>
       </c>
       <c r="AU20">
-        <v>774636020.60000002</v>
+        <v>786318129.89999998</v>
       </c>
       <c r="AV20">
-        <v>784753130.79999995</v>
+        <v>795405131.20000005</v>
       </c>
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.25">
@@ -7701,136 +7701,136 @@
         <v>661127</v>
       </c>
       <c r="E21">
-        <v>1570695.689</v>
+        <v>1875691.4240000001</v>
       </c>
       <c r="F21">
-        <v>2873115.656</v>
+        <v>3531050.3420000002</v>
       </c>
       <c r="G21">
-        <v>4198104.9280000003</v>
+        <v>5256734.8899999997</v>
       </c>
       <c r="H21">
-        <v>5322697.4009999996</v>
+        <v>6659155</v>
       </c>
       <c r="I21">
-        <v>6453008.0240000002</v>
+        <v>7994934.3710000003</v>
       </c>
       <c r="J21">
-        <v>7700498.6380000003</v>
+        <v>9407847.8210000005</v>
       </c>
       <c r="K21">
-        <v>9105911.9820000008</v>
+        <v>10965461.109999999</v>
       </c>
       <c r="L21">
-        <v>10653992.07</v>
+        <v>12666268.359999999</v>
       </c>
       <c r="M21">
-        <v>12281020.18</v>
+        <v>14455010.630000001</v>
       </c>
       <c r="N21">
-        <v>13746915.1</v>
+        <v>16086364.380000001</v>
       </c>
       <c r="O21">
-        <v>15522057.939999999</v>
+        <v>18076069.41</v>
       </c>
       <c r="P21">
-        <v>17875445.68</v>
+        <v>20692600.420000002</v>
       </c>
       <c r="Q21">
-        <v>21583434.899999999</v>
+        <v>24761715.600000001</v>
       </c>
       <c r="R21">
-        <v>26206909.239999998</v>
+        <v>29800599.010000002</v>
       </c>
       <c r="S21">
-        <v>31919520.420000002</v>
+        <v>36015344.049999997</v>
       </c>
       <c r="T21">
-        <v>38387718.490000002</v>
+        <v>43024519.789999999</v>
       </c>
       <c r="U21">
-        <v>45366787.770000003</v>
+        <v>50589869.229999997</v>
       </c>
       <c r="V21">
-        <v>53147431.5</v>
+        <v>59012758.100000001</v>
       </c>
       <c r="W21">
-        <v>63216470.549999997</v>
+        <v>69864770.239999995</v>
       </c>
       <c r="X21">
-        <v>76012462.049999997</v>
+        <v>83577461.25</v>
       </c>
       <c r="Y21">
-        <v>90907750.920000002</v>
+        <v>99502539.25</v>
       </c>
       <c r="Z21">
-        <v>107386259.8</v>
+        <v>117090886.90000001</v>
       </c>
       <c r="AA21">
-        <v>124970507.09999999</v>
+        <v>135830792.40000001</v>
       </c>
       <c r="AB21">
-        <v>143594681.80000001</v>
+        <v>155649956.40000001</v>
       </c>
       <c r="AC21">
-        <v>163750567.09999999</v>
+        <v>177050447.59999999</v>
       </c>
       <c r="AD21">
-        <v>185047498.19999999</v>
+        <v>199615291</v>
       </c>
       <c r="AE21">
-        <v>207127448.5</v>
+        <v>222977182.5</v>
       </c>
       <c r="AF21">
-        <v>230035468.09999999</v>
+        <v>247184951.90000001</v>
       </c>
       <c r="AG21">
-        <v>253704466.5</v>
+        <v>272164968.89999998</v>
       </c>
       <c r="AH21">
-        <v>277808510.19999999</v>
+        <v>297579249.89999998</v>
       </c>
       <c r="AI21">
-        <v>302330865.5</v>
+        <v>323410898.30000001</v>
       </c>
       <c r="AJ21">
-        <v>327331303.69999999</v>
+        <v>349717175.60000002</v>
       </c>
       <c r="AK21">
-        <v>352831256.19999999</v>
+        <v>376523441.30000001</v>
       </c>
       <c r="AL21">
-        <v>379499288.39999998</v>
+        <v>404514804.19999999</v>
       </c>
       <c r="AM21">
-        <v>407285498.10000002</v>
+        <v>433636269.69999999</v>
       </c>
       <c r="AN21">
-        <v>435657465</v>
+        <v>463339674.19999999</v>
       </c>
       <c r="AO21">
-        <v>464420535.60000002</v>
+        <v>493422896.80000001</v>
       </c>
       <c r="AP21">
-        <v>493507810.30000001</v>
+        <v>523813923.60000002</v>
       </c>
       <c r="AQ21">
-        <v>522812458.69999999</v>
+        <v>554401335.39999998</v>
       </c>
       <c r="AR21">
-        <v>552409385.70000005</v>
+        <v>585258376.10000002</v>
       </c>
       <c r="AS21">
-        <v>582673611.20000005</v>
+        <v>616764862</v>
       </c>
       <c r="AT21">
-        <v>613655165.29999995</v>
+        <v>648967579.70000005</v>
       </c>
       <c r="AU21">
-        <v>645395286</v>
+        <v>681904826.79999995</v>
       </c>
       <c r="AV21">
-        <v>677892315.60000002</v>
+        <v>715572061.5</v>
       </c>
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.25">
@@ -7993,136 +7993,136 @@
         <v>1.2911593599999999E-3</v>
       </c>
       <c r="E23">
-        <v>1.3028745799999999E-3</v>
+        <v>1.3028729499999999E-3</v>
       </c>
       <c r="F23">
-        <v>1.3155393E-3</v>
+        <v>1.3155347700000001E-3</v>
       </c>
       <c r="G23">
-        <v>1.3464105499999999E-3</v>
+        <v>1.34640178E-3</v>
       </c>
       <c r="H23">
-        <v>1.3905160500000001E-3</v>
+        <v>1.3905015600000001E-3</v>
       </c>
       <c r="I23">
-        <v>1.4271793999999999E-3</v>
+        <v>1.42715892E-3</v>
       </c>
       <c r="J23">
-        <v>1.46040057E-3</v>
+        <v>1.4603745200000001E-3</v>
       </c>
       <c r="K23">
-        <v>1.4916140500000001E-3</v>
+        <v>1.49158047E-3</v>
       </c>
       <c r="L23">
-        <v>1.5395514500000001E-3</v>
+        <v>1.53950871E-3</v>
       </c>
       <c r="M23">
-        <v>1.60647999E-3</v>
+        <v>1.60642882E-3</v>
       </c>
       <c r="N23">
-        <v>1.65767489E-3</v>
+        <v>1.65761834E-3</v>
       </c>
       <c r="O23">
-        <v>1.6920494899999999E-3</v>
+        <v>1.6919922899999999E-3</v>
       </c>
       <c r="P23">
-        <v>1.72094993E-3</v>
+        <v>1.7208971999999999E-3</v>
       </c>
       <c r="Q23">
-        <v>1.7501776999999999E-3</v>
+        <v>1.7501238599999999E-3</v>
       </c>
       <c r="R23">
-        <v>1.80625362E-3</v>
+        <v>1.8061857999999999E-3</v>
       </c>
       <c r="S23">
-        <v>1.86407782E-3</v>
+        <v>1.86400184E-3</v>
       </c>
       <c r="T23">
-        <v>1.9006929100000001E-3</v>
+        <v>1.9006078099999999E-3</v>
       </c>
       <c r="U23">
-        <v>1.9377242600000001E-3</v>
+        <v>1.93764604E-3</v>
       </c>
       <c r="V23">
-        <v>1.9754522900000001E-3</v>
+        <v>1.9753656399999998E-3</v>
       </c>
       <c r="W23">
-        <v>2.0140372099999998E-3</v>
+        <v>2.0139419899999999E-3</v>
       </c>
       <c r="X23">
-        <v>2.0530272899999999E-3</v>
+        <v>2.0529106399999998E-3</v>
       </c>
       <c r="Y23">
-        <v>2.0926577699999999E-3</v>
+        <v>2.0925295400000001E-3</v>
       </c>
       <c r="Z23">
-        <v>2.13284596E-3</v>
+        <v>2.13271887E-3</v>
       </c>
       <c r="AA23">
-        <v>2.1735626899999998E-3</v>
+        <v>2.1734357500000001E-3</v>
       </c>
       <c r="AB23">
-        <v>2.2148148599999999E-3</v>
+        <v>2.2146820299999998E-3</v>
       </c>
       <c r="AC23">
-        <v>2.25678823E-3</v>
+        <v>2.2566464500000001E-3</v>
       </c>
       <c r="AD23">
-        <v>2.2992333900000001E-3</v>
+        <v>2.2990805299999998E-3</v>
       </c>
       <c r="AE23">
-        <v>2.3421989000000001E-3</v>
+        <v>2.3420339599999999E-3</v>
       </c>
       <c r="AF23">
-        <v>2.3857233300000002E-3</v>
+        <v>2.3855458900000001E-3</v>
       </c>
       <c r="AG23">
-        <v>2.4298093400000002E-3</v>
+        <v>2.4296191699999998E-3</v>
       </c>
       <c r="AH23">
-        <v>2.4744738099999998E-3</v>
+        <v>2.4742689099999998E-3</v>
       </c>
       <c r="AI23">
-        <v>2.51966933E-3</v>
+        <v>2.5194487199999998E-3</v>
       </c>
       <c r="AJ23">
-        <v>2.56539399E-3</v>
+        <v>2.5651586500000001E-3</v>
       </c>
       <c r="AK23">
-        <v>2.6116032699999999E-3</v>
+        <v>2.61135254E-3</v>
       </c>
       <c r="AL23">
-        <v>2.6582423600000002E-3</v>
+        <v>2.6579753900000001E-3</v>
       </c>
       <c r="AM23">
-        <v>2.70494572E-3</v>
+        <v>2.7046623499999999E-3</v>
       </c>
       <c r="AN23">
-        <v>2.7521255199999999E-3</v>
+        <v>2.7518254800000001E-3</v>
       </c>
       <c r="AO23">
-        <v>2.7995899899999998E-3</v>
+        <v>2.79927313E-3</v>
       </c>
       <c r="AP23">
-        <v>2.8471470800000001E-3</v>
+        <v>2.8468134999999999E-3</v>
       </c>
       <c r="AQ23">
-        <v>2.8946728300000002E-3</v>
+        <v>2.8943218500000001E-3</v>
       </c>
       <c r="AR23">
-        <v>2.9421091499999999E-3</v>
+        <v>2.94173847E-3</v>
       </c>
       <c r="AS23">
-        <v>2.98933828E-3</v>
+        <v>2.9889469299999999E-3</v>
       </c>
       <c r="AT23">
-        <v>3.0362111900000001E-3</v>
+        <v>3.0357977700000002E-3</v>
       </c>
       <c r="AU23">
-        <v>3.0825664400000001E-3</v>
+        <v>3.0821303099999998E-3</v>
       </c>
       <c r="AV23">
-        <v>3.1438063800000001E-3</v>
+        <v>3.1433496099999999E-3</v>
       </c>
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.25">
@@ -8142,133 +8142,133 @@
         <v>26830545.620000001</v>
       </c>
       <c r="F24">
-        <v>27046288.920000002</v>
+        <v>27046525.010000002</v>
       </c>
       <c r="G24">
-        <v>27260657.16</v>
+        <v>27260839.120000001</v>
       </c>
       <c r="H24">
-        <v>27476744.850000001</v>
+        <v>27476582.300000001</v>
       </c>
       <c r="I24">
-        <v>27710473.059999999</v>
+        <v>27709685.489999998</v>
       </c>
       <c r="J24">
-        <v>27947234.129999999</v>
+        <v>27945548.02</v>
       </c>
       <c r="K24">
-        <v>28179281.850000001</v>
+        <v>28176470.940000001</v>
       </c>
       <c r="L24">
-        <v>28405732.41</v>
+        <v>28401582.449999999</v>
       </c>
       <c r="M24">
-        <v>28636629.899999999</v>
+        <v>28630909.760000002</v>
       </c>
       <c r="N24">
-        <v>32255275.699999999</v>
+        <v>32247762.359999999</v>
       </c>
       <c r="O24">
-        <v>32594526.719999999</v>
+        <v>32584977.359999999</v>
       </c>
       <c r="P24">
-        <v>32945817.579999998</v>
+        <v>32933946.640000001</v>
       </c>
       <c r="Q24">
-        <v>31696940.440000001</v>
+        <v>31682655.68</v>
       </c>
       <c r="R24">
-        <v>31564343.690000001</v>
+        <v>31547745.18</v>
       </c>
       <c r="S24">
-        <v>30961012.75</v>
+        <v>30944923.84</v>
       </c>
       <c r="T24">
-        <v>30701681.010000002</v>
+        <v>30686352.600000001</v>
       </c>
       <c r="U24">
-        <v>32586206.079999998</v>
+        <v>32571783.539999999</v>
       </c>
       <c r="V24">
-        <v>32585854.98</v>
+        <v>32572430.210000001</v>
       </c>
       <c r="W24">
-        <v>31720141.32</v>
+        <v>31707757.940000001</v>
       </c>
       <c r="X24">
-        <v>30954653.260000002</v>
+        <v>30943359.699999999</v>
       </c>
       <c r="Y24">
-        <v>30127535.550000001</v>
+        <v>30117426.469999999</v>
       </c>
       <c r="Z24">
-        <v>29455510.870000001</v>
+        <v>29446721.379999999</v>
       </c>
       <c r="AA24">
-        <v>28631687.75</v>
+        <v>28624395.59</v>
       </c>
       <c r="AB24">
-        <v>27740985.289999999</v>
+        <v>27735377.859999999</v>
       </c>
       <c r="AC24">
-        <v>27634130.43</v>
+        <v>27630402.800000001</v>
       </c>
       <c r="AD24">
-        <v>27387132.239999998</v>
+        <v>27385486.300000001</v>
       </c>
       <c r="AE24">
-        <v>27087129.239999998</v>
+        <v>27087770.300000001</v>
       </c>
       <c r="AF24">
-        <v>26778406.66</v>
+        <v>26781542.43</v>
       </c>
       <c r="AG24">
-        <v>26737962.149999999</v>
+        <v>26743799.440000001</v>
       </c>
       <c r="AH24">
-        <v>26368198.460000001</v>
+        <v>26376943.41</v>
       </c>
       <c r="AI24">
-        <v>25847639.91</v>
+        <v>25859495.629999999</v>
       </c>
       <c r="AJ24">
-        <v>25596685.32</v>
+        <v>25611851.710000001</v>
       </c>
       <c r="AK24">
-        <v>25290446.210000001</v>
+        <v>25309117.550000001</v>
       </c>
       <c r="AL24">
-        <v>24879843.98</v>
+        <v>24902205.93</v>
       </c>
       <c r="AM24">
-        <v>23989238.350000001</v>
+        <v>24015468.140000001</v>
       </c>
       <c r="AN24">
-        <v>22884777.77</v>
+        <v>22915036.469999999</v>
       </c>
       <c r="AO24">
-        <v>21756461.16</v>
+        <v>21790873.57</v>
       </c>
       <c r="AP24">
-        <v>20898312.34</v>
+        <v>20936973.539999999</v>
       </c>
       <c r="AQ24">
-        <v>19825835.23</v>
+        <v>19868814.699999999</v>
       </c>
       <c r="AR24">
-        <v>18782728.84</v>
+        <v>18830069.670000002</v>
       </c>
       <c r="AS24">
-        <v>17870085.699999999</v>
+        <v>17921799.100000001</v>
       </c>
       <c r="AT24">
-        <v>16841986.199999999</v>
+        <v>16898061.02</v>
       </c>
       <c r="AU24">
-        <v>15797526.35</v>
+        <v>15857929.74</v>
       </c>
       <c r="AV24">
-        <v>16211376.16</v>
+        <v>16282524.08</v>
       </c>
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.25">
@@ -8276,145 +8276,145 @@
         <v>103</v>
       </c>
       <c r="B25">
-        <v>40116783.705106698</v>
+        <v>40966249.706947699</v>
       </c>
       <c r="C25">
-        <v>40760871.6436335</v>
+        <v>41623976.0969017</v>
       </c>
       <c r="D25">
-        <v>41415300.619999997</v>
+        <v>42292262.5</v>
       </c>
       <c r="E25">
-        <v>51230585.32</v>
+        <v>52117673.670000002</v>
       </c>
       <c r="F25">
-        <v>55457511</v>
+        <v>56593513.100000001</v>
       </c>
       <c r="G25">
-        <v>56040552.729999997</v>
+        <v>57429312.409999996</v>
       </c>
       <c r="H25">
-        <v>44441626.210000001</v>
+        <v>45132011.18</v>
       </c>
       <c r="I25">
-        <v>44271561.219999999</v>
+        <v>44620254.649999999</v>
       </c>
       <c r="J25">
-        <v>49513252.68</v>
+        <v>49703724.32</v>
       </c>
       <c r="K25">
-        <v>56643042.609999999</v>
+        <v>56790200.770000003</v>
       </c>
       <c r="L25">
-        <v>56801410.130000003</v>
+        <v>56986189.119999997</v>
       </c>
       <c r="M25">
-        <v>51118831.060000002</v>
+        <v>51367221.469999999</v>
       </c>
       <c r="N25">
-        <v>36805346.590000004</v>
+        <v>37200083.409999996</v>
       </c>
       <c r="O25">
-        <v>34823666.960000001</v>
+        <v>35466766.060000002</v>
       </c>
       <c r="P25">
-        <v>42649720.899999999</v>
+        <v>43400498.619999997</v>
       </c>
       <c r="Q25">
-        <v>69061542.890000001</v>
+        <v>69766721.549999997</v>
       </c>
       <c r="R25">
-        <v>78540255.010000005</v>
+        <v>79203546.510000005</v>
       </c>
       <c r="S25">
-        <v>93461652.959999904</v>
+        <v>94048650.420000002</v>
       </c>
       <c r="T25">
-        <v>95548172.590000004</v>
+        <v>96147250.540000007</v>
       </c>
       <c r="U25">
-        <v>98280572.879999995</v>
+        <v>98891154.599999994</v>
       </c>
       <c r="V25">
-        <v>89694824.430000007</v>
+        <v>90414378.159999996</v>
       </c>
       <c r="W25">
-        <v>88119714.859999999</v>
+        <v>88954200.709999904</v>
       </c>
       <c r="X25">
-        <v>73408511.400000006</v>
+        <v>74456122.5</v>
       </c>
       <c r="Y25">
-        <v>65331659.359999999</v>
+        <v>66338241.950000003</v>
       </c>
       <c r="Z25">
-        <v>60829081.060000002</v>
+        <v>61819160.670000002</v>
       </c>
       <c r="AA25">
-        <v>58388441.229999997</v>
+        <v>59376980.380000003</v>
       </c>
       <c r="AB25">
-        <v>57166155.359999999</v>
+        <v>58160342.700000003</v>
       </c>
       <c r="AC25">
-        <v>56595894.350000001</v>
+        <v>57598320.189999998</v>
       </c>
       <c r="AD25">
-        <v>56343133.969999999</v>
+        <v>57354551.170000002</v>
       </c>
       <c r="AE25">
-        <v>56398005.530000001</v>
+        <v>57421049.659999996</v>
       </c>
       <c r="AF25">
-        <v>56662656.810000002</v>
+        <v>57706000.93</v>
       </c>
       <c r="AG25">
-        <v>56925803.990000002</v>
+        <v>57979437.109999999</v>
       </c>
       <c r="AH25">
-        <v>57236406.479999997</v>
+        <v>58292710.909999996</v>
       </c>
       <c r="AI25">
-        <v>57654344.409999996</v>
+        <v>58705932.82</v>
       </c>
       <c r="AJ25">
-        <v>58136015.880000003</v>
+        <v>59176648.57</v>
       </c>
       <c r="AK25">
-        <v>58752148.420000002</v>
+        <v>59776140.93</v>
       </c>
       <c r="AL25">
-        <v>59463460.579999998</v>
+        <v>60465468.770000003</v>
       </c>
       <c r="AM25">
-        <v>60429047.259999998</v>
+        <v>61403451.759999998</v>
       </c>
       <c r="AN25">
-        <v>61956471</v>
+        <v>62897319.869999997</v>
       </c>
       <c r="AO25">
-        <v>63752891.939999998</v>
+        <v>64655114.100000001</v>
       </c>
       <c r="AP25">
-        <v>65669786.060000002</v>
+        <v>66528828.770000003</v>
       </c>
       <c r="AQ25">
-        <v>67608793.329999998</v>
+        <v>68423781.659999996</v>
       </c>
       <c r="AR25">
-        <v>69573586.340000004</v>
+        <v>70346060.769999996</v>
       </c>
       <c r="AS25">
-        <v>71665186.879999995</v>
+        <v>72386365.469999999</v>
       </c>
       <c r="AT25">
-        <v>73792669.049999997</v>
+        <v>74457085.269999996</v>
       </c>
       <c r="AU25">
-        <v>75826257.930000007</v>
+        <v>76430921.700000003</v>
       </c>
       <c r="AV25">
-        <v>77725388.75</v>
+        <v>78268272.560000002</v>
       </c>
     </row>
     <row r="26" spans="1:48" x14ac:dyDescent="0.25">
@@ -8422,145 +8422,145 @@
         <v>104</v>
       </c>
       <c r="B26">
-        <v>1.9161062080326401E-4</v>
+        <v>1.8387279230377499E-4</v>
       </c>
       <c r="C26">
-        <v>1.95442833219329E-4</v>
+        <v>1.8755024814985001E-4</v>
       </c>
       <c r="D26">
-        <v>1.9766545599999999E-4</v>
+        <v>1.8968311500000001E-4</v>
       </c>
       <c r="E26">
-        <v>1.5610889700000001E-4</v>
+        <v>1.5081159800000001E-4</v>
       </c>
       <c r="F26">
-        <v>1.5471472200000001E-4</v>
+        <v>1.4978342699999999E-4</v>
       </c>
       <c r="G26">
-        <v>1.59234078E-4</v>
+        <v>1.5415817900000001E-4</v>
       </c>
       <c r="H26">
-        <v>1.6907519899999999E-4</v>
+        <v>1.6304628599999999E-4</v>
       </c>
       <c r="I26">
-        <v>1.6881448099999999E-4</v>
+        <v>1.63044928E-4</v>
       </c>
       <c r="J26">
-        <v>1.78970502E-4</v>
+        <v>1.73750141E-4</v>
       </c>
       <c r="K26">
-        <v>1.74352275E-4</v>
+        <v>1.7001224899999999E-4</v>
       </c>
       <c r="L26">
-        <v>1.6876091299999999E-4</v>
+        <v>1.6454941100000001E-4</v>
       </c>
       <c r="M26">
-        <v>1.60227519E-4</v>
+        <v>1.5569669900000001E-4</v>
       </c>
       <c r="N26">
-        <v>1.65005841E-4</v>
+        <v>1.58028434E-4</v>
       </c>
       <c r="O26">
-        <v>1.4191521899999999E-4</v>
+        <v>1.3493923300000001E-4</v>
       </c>
       <c r="P26">
-        <v>1.45420176E-4</v>
+        <v>1.3959396800000001E-4</v>
       </c>
       <c r="Q26" s="39">
-        <v>1.24541545E-4</v>
+        <v>1.2172555899999999E-4</v>
       </c>
       <c r="R26">
-        <v>1.3977872000000001E-4</v>
+        <v>1.37259531E-4</v>
       </c>
       <c r="S26" s="39">
-        <v>1.22013721E-4</v>
+        <v>1.20393424E-4</v>
       </c>
       <c r="T26">
-        <v>1.3663790700000001E-4</v>
+        <v>1.3491041000000001E-4</v>
       </c>
       <c r="U26">
-        <v>1.38133949E-4</v>
+        <v>1.36521588E-4</v>
       </c>
       <c r="V26">
-        <v>1.66893853E-4</v>
+        <v>1.64544103E-4</v>
       </c>
       <c r="W26">
-        <v>1.6730965000000001E-4</v>
+        <v>1.6488285600000001E-4</v>
       </c>
       <c r="X26">
-        <v>2.14462293E-4</v>
+        <v>2.10278832E-4</v>
       </c>
       <c r="Y26">
-        <v>2.1806035900000001E-4</v>
+        <v>2.1300480499999999E-4</v>
       </c>
       <c r="Z26">
-        <v>2.2279295500000001E-4</v>
+        <v>2.17050885E-4</v>
       </c>
       <c r="AA26">
-        <v>2.26397328E-4</v>
+        <v>2.2018719400000001E-4</v>
       </c>
       <c r="AB26">
-        <v>2.2933951399999999E-4</v>
+        <v>2.2282239400000001E-4</v>
       </c>
       <c r="AC26">
-        <v>2.3208301200000001E-4</v>
+        <v>2.2535087699999999E-4</v>
       </c>
       <c r="AD26">
-        <v>2.3494403200000001E-4</v>
+        <v>2.28036423E-4</v>
       </c>
       <c r="AE26">
-        <v>2.3792850099999999E-4</v>
+        <v>2.30880505E-4</v>
       </c>
       <c r="AF26">
-        <v>2.4108811899999999E-4</v>
+        <v>2.33913422E-4</v>
       </c>
       <c r="AG26">
-        <v>2.4452397299999998E-4</v>
+        <v>2.3721838500000001E-4</v>
       </c>
       <c r="AH26">
-        <v>2.4818256800000001E-4</v>
+        <v>2.40748981E-4</v>
       </c>
       <c r="AI26">
-        <v>2.52047198E-4</v>
+        <v>2.4449721599999999E-4</v>
       </c>
       <c r="AJ26">
-        <v>2.5606157999999999E-4</v>
+        <v>2.4840702800000002E-4</v>
       </c>
       <c r="AK26">
-        <v>2.60103156E-4</v>
+        <v>2.5237764100000001E-4</v>
       </c>
       <c r="AL26">
-        <v>2.6419758600000002E-4</v>
+        <v>2.5642766599999998E-4</v>
       </c>
       <c r="AM26">
-        <v>2.6832761899999997E-4</v>
+        <v>2.60565511E-4</v>
       </c>
       <c r="AN26">
-        <v>2.7263192699999999E-4</v>
+        <v>2.64967098E-4</v>
       </c>
       <c r="AO26">
-        <v>2.77045208E-4</v>
+        <v>2.6952396400000003E-4</v>
       </c>
       <c r="AP26">
-        <v>2.8154851100000003E-4</v>
+        <v>2.7419448099999999E-4</v>
       </c>
       <c r="AQ26">
-        <v>2.8616216300000001E-4</v>
+        <v>2.7898223800000002E-4</v>
       </c>
       <c r="AR26">
-        <v>2.9091764399999999E-4</v>
+        <v>2.83918008E-4</v>
       </c>
       <c r="AS26">
-        <v>2.9584117700000003E-4</v>
+        <v>2.8903459900000002E-4</v>
       </c>
       <c r="AT26">
-        <v>3.00914664E-4</v>
+        <v>2.9430375300000002E-4</v>
       </c>
       <c r="AU26">
-        <v>3.0632768499999998E-4</v>
+        <v>2.99895611E-4</v>
       </c>
       <c r="AV26">
-        <v>3.1200766999999998E-4</v>
+        <v>3.05736617E-4</v>
       </c>
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
@@ -8568,145 +8568,145 @@
         <v>91</v>
       </c>
       <c r="B27">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C27">
-        <v>7966.4202385211802</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D27">
-        <v>8186.3743000000004</v>
+        <v>8022.1280880000004</v>
       </c>
       <c r="E27">
-        <v>9701.1703209999996</v>
+        <v>9534.2584409999999</v>
       </c>
       <c r="F27">
-        <v>10407.805619999999</v>
+        <v>10282.47286</v>
       </c>
       <c r="G27">
-        <v>10623.29257</v>
+        <v>10539.521699999999</v>
       </c>
       <c r="H27">
-        <v>8737.1823260000001</v>
+        <v>8556.5195359999998</v>
       </c>
       <c r="I27">
-        <v>8818.4625849999902</v>
+        <v>8591.9026649999996</v>
       </c>
       <c r="J27">
-        <v>9940.1322770000006</v>
+        <v>9694.266243</v>
       </c>
       <c r="K27">
-        <v>11282.96738</v>
+        <v>11036.826069999999</v>
       </c>
       <c r="L27">
-        <v>11424.569079999999</v>
+        <v>11182.380649999999</v>
       </c>
       <c r="M27">
-        <v>10506.44162</v>
+        <v>10264.94281</v>
       </c>
       <c r="N27">
-        <v>7837.733682</v>
+        <v>7599.993982</v>
       </c>
       <c r="O27">
-        <v>7159.1341110000003</v>
+        <v>6964.345609</v>
       </c>
       <c r="P27">
-        <v>8568.6068030000006</v>
+        <v>8403.7953550000002</v>
       </c>
       <c r="Q27">
-        <v>13270.076129999999</v>
+        <v>13144.305909999999</v>
       </c>
       <c r="R27">
-        <v>15282.092049999999</v>
+        <v>15161.38853</v>
       </c>
       <c r="S27">
-        <v>18046.60497</v>
+        <v>17946.218349999999</v>
       </c>
       <c r="T27">
-        <v>18825.771110000001</v>
+        <v>18728.08167</v>
       </c>
       <c r="U27">
-        <v>19502.961340000002</v>
+        <v>19415.861369999999</v>
       </c>
       <c r="V27">
-        <v>18275.81955</v>
+        <v>18183.457490000001</v>
       </c>
       <c r="W27">
-        <v>18115.709439999999</v>
+        <v>18039.45348</v>
       </c>
       <c r="X27">
-        <v>15743.35771</v>
+        <v>15656.5465</v>
       </c>
       <c r="Y27">
-        <v>14246.24509</v>
+        <v>14130.364299999999</v>
       </c>
       <c r="Z27">
-        <v>13552.2907</v>
+        <v>13417.90353</v>
       </c>
       <c r="AA27">
-        <v>13218.9871</v>
+        <v>13074.0507</v>
       </c>
       <c r="AB27">
-        <v>13110.4583</v>
+        <v>12959.426810000001</v>
       </c>
       <c r="AC27">
-        <v>13134.945610000001</v>
+        <v>12979.83195</v>
       </c>
       <c r="AD27">
-        <v>13237.48307</v>
+        <v>13078.9267</v>
       </c>
       <c r="AE27">
-        <v>13418.69291</v>
+        <v>13257.40092</v>
       </c>
       <c r="AF27">
-        <v>13660.693370000001</v>
+        <v>13498.208140000001</v>
       </c>
       <c r="AG27">
-        <v>13919.72378</v>
+        <v>13753.788420000001</v>
       </c>
       <c r="AH27">
-        <v>14205.07834</v>
+        <v>14033.910760000001</v>
       </c>
       <c r="AI27">
-        <v>14531.615959999999</v>
+        <v>14353.43714</v>
       </c>
       <c r="AJ27">
-        <v>14886.400100000001</v>
+        <v>14699.895409999999</v>
       </c>
       <c r="AK27">
-        <v>15281.61925</v>
+        <v>15086.16142</v>
       </c>
       <c r="AL27">
-        <v>15710.10277</v>
+        <v>15505.019060000001</v>
       </c>
       <c r="AM27">
-        <v>16214.782349999999</v>
+        <v>15999.621789999999</v>
       </c>
       <c r="AN27">
-        <v>16891.312089999999</v>
+        <v>16665.72034</v>
       </c>
       <c r="AO27">
-        <v>17662.433219999999</v>
+        <v>17426.102620000001</v>
       </c>
       <c r="AP27">
-        <v>18489.230490000002</v>
+        <v>18241.8377</v>
       </c>
       <c r="AQ27">
-        <v>19347.078539999999</v>
+        <v>19089.019749999999</v>
       </c>
       <c r="AR27">
-        <v>20240.183840000002</v>
+        <v>19972.513449999999</v>
       </c>
       <c r="AS27">
-        <v>21201.51326</v>
+        <v>20922.164100000002</v>
       </c>
       <c r="AT27">
-        <v>22205.29621</v>
+        <v>21912.999599999999</v>
       </c>
       <c r="AU27">
-        <v>23227.682059999999</v>
+        <v>22921.297999999999</v>
       </c>
       <c r="AV27">
-        <v>24250.91748</v>
+        <v>23929.476879999998</v>
       </c>
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
@@ -8714,145 +8714,145 @@
         <v>105</v>
       </c>
       <c r="B28">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C28">
-        <v>7966.4202385211902</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D28">
-        <v>8186.3742824293804</v>
+        <v>8022.1280913976798</v>
       </c>
       <c r="E28">
-        <v>9701.1703209695897</v>
+        <v>9534.25844921522</v>
       </c>
       <c r="F28">
-        <v>10407.8056041769</v>
+        <v>10282.4728900873</v>
       </c>
       <c r="G28">
-        <v>10623.2925565719</v>
+        <v>10539.521694347701</v>
       </c>
       <c r="H28">
-        <v>8737.18232133936</v>
+        <v>8556.5195376094707</v>
       </c>
       <c r="I28">
-        <v>8818.4625882105793</v>
+        <v>8591.9026735474708</v>
       </c>
       <c r="J28">
-        <v>9940.1322562618698</v>
+        <v>9694.2662199945498</v>
       </c>
       <c r="K28">
-        <v>11282.9673936618</v>
+        <v>11036.8260767556</v>
       </c>
       <c r="L28">
-        <v>11424.5690587727</v>
+        <v>11182.380641377</v>
       </c>
       <c r="M28">
-        <v>10506.441609973899</v>
+        <v>10264.942820730799</v>
       </c>
       <c r="N28">
-        <v>7837.7336658944196</v>
+        <v>7599.9939644666601</v>
       </c>
       <c r="O28">
-        <v>7159.1341260828003</v>
+        <v>6964.3456031981696</v>
       </c>
       <c r="P28">
-        <v>8568.60678276402</v>
+        <v>8403.7953766794599</v>
       </c>
       <c r="Q28">
-        <v>13270.076152507399</v>
+        <v>13144.3059301741</v>
       </c>
       <c r="R28">
-        <v>15282.0920452255</v>
+        <v>15161.388500953401</v>
       </c>
       <c r="S28">
-        <v>18046.604985106202</v>
+        <v>17946.2183772887</v>
       </c>
       <c r="T28">
-        <v>18825.771059611201</v>
+        <v>18728.081669962899</v>
       </c>
       <c r="U28">
-        <v>19502.961367640299</v>
+        <v>19415.861324889102</v>
       </c>
       <c r="V28">
-        <v>18275.819560279699</v>
+        <v>18183.457469638401</v>
       </c>
       <c r="W28">
-        <v>20542.2786513264</v>
+        <v>20466.022666262001</v>
       </c>
       <c r="X28">
-        <v>21027.357680560599</v>
+        <v>20940.546474548901</v>
       </c>
       <c r="Y28">
-        <v>19154.2450941073</v>
+        <v>19038.364290602502</v>
       </c>
       <c r="Z28">
-        <v>18323.290719291901</v>
+        <v>18188.903533380599</v>
       </c>
       <c r="AA28">
-        <v>17397.987080556999</v>
+        <v>17253.050698065199</v>
       </c>
       <c r="AB28">
-        <v>17255.458287510799</v>
+        <v>17104.426796274402</v>
       </c>
       <c r="AC28">
-        <v>17089.945627581699</v>
+        <v>16934.831968543302</v>
       </c>
       <c r="AD28">
-        <v>16996.483070427901</v>
+        <v>16837.926691577199</v>
       </c>
       <c r="AE28">
-        <v>17025.692915142601</v>
+        <v>16864.4009431308</v>
       </c>
       <c r="AF28">
-        <v>17355.693347865399</v>
+        <v>17193.2081474714</v>
       </c>
       <c r="AG28">
-        <v>17442.723757854001</v>
+        <v>17276.788434443199</v>
       </c>
       <c r="AH28">
-        <v>17588.078343298199</v>
+        <v>17416.910751309999</v>
       </c>
       <c r="AI28">
-        <v>17991.6159610674</v>
+        <v>17813.437137173001</v>
       </c>
       <c r="AJ28">
-        <v>18230.400081137799</v>
+        <v>18043.8953982741</v>
       </c>
       <c r="AK28">
-        <v>18501.6192258224</v>
+        <v>18306.161435996899</v>
       </c>
       <c r="AL28">
-        <v>19388.1027404421</v>
+        <v>19183.019030286901</v>
       </c>
       <c r="AM28">
-        <v>19724.782369714201</v>
+        <v>19509.621785008199</v>
       </c>
       <c r="AN28">
-        <v>20248.312078849602</v>
+        <v>20022.720317931598</v>
       </c>
       <c r="AO28">
-        <v>20880.4332081188</v>
+        <v>20644.1026451043</v>
       </c>
       <c r="AP28">
-        <v>21581.230482881499</v>
+        <v>21333.837676128001</v>
       </c>
       <c r="AQ28">
-        <v>22325.0785371327</v>
+        <v>22067.0197399301</v>
       </c>
       <c r="AR28">
-        <v>23113.183822663301</v>
+        <v>22845.513444465301</v>
       </c>
       <c r="AS28">
-        <v>23977.513236504099</v>
+        <v>23698.164116688899</v>
       </c>
       <c r="AT28">
-        <v>24893.296212843899</v>
+        <v>24600.999632401999</v>
       </c>
       <c r="AU28">
-        <v>25835.682053909699</v>
+        <v>25529.2979625146</v>
       </c>
       <c r="AV28">
-        <v>26783.917443731701</v>
+        <v>26462.476870928302</v>
       </c>
     </row>
     <row r="29" spans="1:48" x14ac:dyDescent="0.25">
@@ -8908,97 +8908,97 @@
         <v>93114.179950000005</v>
       </c>
       <c r="R29">
-        <v>94895.645269999906</v>
+        <v>94796.611229999995</v>
       </c>
       <c r="S29">
-        <v>97228.440010000006</v>
+        <v>96976.641740000006</v>
       </c>
       <c r="T29">
-        <v>97060.425289999999</v>
+        <v>96790.300220000005</v>
       </c>
       <c r="U29">
-        <v>100371.8621</v>
+        <v>100089.55839999999</v>
       </c>
       <c r="V29">
-        <v>98103.098870000002</v>
+        <v>97919.652749999994</v>
       </c>
       <c r="W29">
-        <v>96143.781140000006</v>
+        <v>95994.554470000003</v>
       </c>
       <c r="X29">
-        <v>91234.063829999999</v>
+        <v>91256.825169999996</v>
       </c>
       <c r="Y29">
-        <v>87788.583769999997</v>
+        <v>87867.219490000003</v>
       </c>
       <c r="Z29">
-        <v>85421.863200000007</v>
+        <v>85531.58971</v>
       </c>
       <c r="AA29">
-        <v>83302.922529999996</v>
+        <v>83428.545870000002</v>
       </c>
       <c r="AB29">
-        <v>81363.214080000005</v>
+        <v>81495.670440000002</v>
       </c>
       <c r="AC29">
-        <v>80785.516350000005</v>
+        <v>80924.307350000003</v>
       </c>
       <c r="AD29">
-        <v>80067.583790000004</v>
+        <v>80209.683650000006</v>
       </c>
       <c r="AE29">
-        <v>79340.444159999999</v>
+        <v>79483.797930000001</v>
       </c>
       <c r="AF29">
-        <v>78648.782609999995</v>
+        <v>78793.796220000004</v>
       </c>
       <c r="AG29">
-        <v>78371.820070000002</v>
+        <v>78518.025829999999</v>
       </c>
       <c r="AH29">
-        <v>77596.818100000004</v>
+        <v>77740.589040000006</v>
       </c>
       <c r="AI29">
-        <v>76612.548250000007</v>
+        <v>76750.739270000005</v>
       </c>
       <c r="AJ29">
-        <v>76058.902969999996</v>
+        <v>76191.302750000003</v>
       </c>
       <c r="AK29">
-        <v>75451.399579999998</v>
+        <v>75575.536309999996</v>
       </c>
       <c r="AL29">
-        <v>74704.634229999996</v>
+        <v>74818.172120000003</v>
       </c>
       <c r="AM29">
-        <v>73276.459319999994</v>
+        <v>73373.536240000001</v>
       </c>
       <c r="AN29">
-        <v>71644.952229999995</v>
+        <v>71718.321559999997</v>
       </c>
       <c r="AO29">
-        <v>70035.33094</v>
+        <v>70081.498399999997</v>
       </c>
       <c r="AP29">
-        <v>68868.939809999996</v>
+        <v>68887.414999999906</v>
       </c>
       <c r="AQ29">
-        <v>67374.600380000003</v>
+        <v>67363.900420000005</v>
       </c>
       <c r="AR29">
-        <v>65929.165729999906</v>
+        <v>65889.627739999996</v>
       </c>
       <c r="AS29">
-        <v>64713.467409999997</v>
+        <v>64642.703520000003</v>
       </c>
       <c r="AT29">
-        <v>63326.491549999999</v>
+        <v>63222.283519999997</v>
       </c>
       <c r="AU29">
-        <v>61890.662960000001</v>
+        <v>61752.993399999999</v>
       </c>
       <c r="AV29">
-        <v>62666.98128</v>
+        <v>62514.370239999997</v>
       </c>
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
@@ -9054,97 +9054,97 @@
         <v>93114.179950000005</v>
       </c>
       <c r="R30">
-        <v>94895.645269999906</v>
+        <v>94796.611229999995</v>
       </c>
       <c r="S30">
-        <v>97228.440010000006</v>
+        <v>96976.641740000006</v>
       </c>
       <c r="T30">
-        <v>97060.425289999999</v>
+        <v>96790.300220000005</v>
       </c>
       <c r="U30">
-        <v>100371.8621</v>
+        <v>100089.55839999999</v>
       </c>
       <c r="V30">
-        <v>98103.098870000002</v>
+        <v>97919.652749999994</v>
       </c>
       <c r="W30">
-        <v>96143.781140000006</v>
+        <v>95994.554470000003</v>
       </c>
       <c r="X30">
-        <v>91234.063829999999</v>
+        <v>91256.825169999996</v>
       </c>
       <c r="Y30">
-        <v>87788.583769999997</v>
+        <v>87867.219490000003</v>
       </c>
       <c r="Z30">
-        <v>85421.863200000007</v>
+        <v>85531.58971</v>
       </c>
       <c r="AA30">
-        <v>83302.922529999996</v>
+        <v>83428.545870000002</v>
       </c>
       <c r="AB30">
-        <v>81363.214080000005</v>
+        <v>81495.670440000002</v>
       </c>
       <c r="AC30">
-        <v>80785.516350000005</v>
+        <v>80924.307350000003</v>
       </c>
       <c r="AD30">
-        <v>80067.583790000004</v>
+        <v>80209.683650000006</v>
       </c>
       <c r="AE30">
-        <v>79340.444159999999</v>
+        <v>79483.797930000001</v>
       </c>
       <c r="AF30">
-        <v>78648.782609999995</v>
+        <v>78793.796220000004</v>
       </c>
       <c r="AG30">
-        <v>78371.820070000002</v>
+        <v>78518.025829999999</v>
       </c>
       <c r="AH30">
-        <v>77596.818100000004</v>
+        <v>77740.589040000006</v>
       </c>
       <c r="AI30">
-        <v>76612.548250000007</v>
+        <v>76750.739270000005</v>
       </c>
       <c r="AJ30">
-        <v>76058.902969999996</v>
+        <v>76191.302750000003</v>
       </c>
       <c r="AK30">
-        <v>75451.399579999998</v>
+        <v>75575.536309999996</v>
       </c>
       <c r="AL30">
-        <v>74704.634229999996</v>
+        <v>74818.172120000003</v>
       </c>
       <c r="AM30">
-        <v>73276.459319999994</v>
+        <v>73373.536240000001</v>
       </c>
       <c r="AN30">
-        <v>71644.952229999995</v>
+        <v>71718.321559999997</v>
       </c>
       <c r="AO30">
-        <v>70035.33094</v>
+        <v>70081.498399999997</v>
       </c>
       <c r="AP30">
-        <v>68868.939809999996</v>
+        <v>68887.414999999906</v>
       </c>
       <c r="AQ30">
-        <v>67374.600380000003</v>
+        <v>67363.900420000005</v>
       </c>
       <c r="AR30">
-        <v>65929.165729999906</v>
+        <v>65889.627739999996</v>
       </c>
       <c r="AS30">
-        <v>64713.467409999997</v>
+        <v>64642.703520000003</v>
       </c>
       <c r="AT30">
-        <v>63326.491549999999</v>
+        <v>63222.283519999997</v>
       </c>
       <c r="AU30">
-        <v>61890.662960000001</v>
+        <v>61752.993399999999</v>
       </c>
       <c r="AV30">
-        <v>62666.98128</v>
+        <v>62514.370239999997</v>
       </c>
     </row>
     <row r="31" spans="1:48" x14ac:dyDescent="0.25">
@@ -9158,139 +9158,139 @@
         <v>0.98039215686274495</v>
       </c>
       <c r="D31">
-        <v>0.99102938060000001</v>
+        <v>0.99102560019999997</v>
       </c>
       <c r="E31">
-        <v>0.69050082479999997</v>
+        <v>0.69078412690000002</v>
       </c>
       <c r="F31">
-        <v>0.69826689620000004</v>
+        <v>0.69892559340000004</v>
       </c>
       <c r="G31">
-        <v>0.75048792389999996</v>
+        <v>0.75154929049999997</v>
       </c>
       <c r="H31">
-        <v>0.74196917399999995</v>
+        <v>0.74208622400000002</v>
       </c>
       <c r="I31">
-        <v>0.75691974169999998</v>
+        <v>0.75657658559999996</v>
       </c>
       <c r="J31">
-        <v>0.79354190309999995</v>
+        <v>0.79288026609999995</v>
       </c>
       <c r="K31">
-        <v>0.83577822859999995</v>
+        <v>0.83514108129999998</v>
       </c>
       <c r="L31">
-        <v>0.86124936870000002</v>
+        <v>0.86073636919999996</v>
       </c>
       <c r="M31">
-        <v>0.88263335970000001</v>
+        <v>0.8822819864</v>
       </c>
       <c r="N31">
-        <v>0.94055030360000003</v>
+        <v>0.94015974010000003</v>
       </c>
       <c r="O31">
-        <v>0.94600954900000001</v>
+        <v>0.94605744410000003</v>
       </c>
       <c r="P31">
-        <v>0.977273536</v>
+        <v>0.97746895359999997</v>
       </c>
       <c r="Q31">
-        <v>0.97951600270000005</v>
+        <v>0.98005794950000003</v>
       </c>
       <c r="R31">
-        <v>1.0054763529999999</v>
+        <v>1.0070424200000001</v>
       </c>
       <c r="S31">
-        <v>0.99588708189999997</v>
+        <v>0.99926356699999996</v>
       </c>
       <c r="T31">
-        <v>1.024166669</v>
+        <v>1.0278075840000001</v>
       </c>
       <c r="U31">
-        <v>1.046295988</v>
+        <v>1.0501284310000001</v>
       </c>
       <c r="V31">
-        <v>1.1003200980000001</v>
+        <v>1.103139154</v>
       </c>
       <c r="W31">
-        <v>1.1184047290000001</v>
+        <v>1.121119451</v>
       </c>
       <c r="X31">
-        <v>1.189038646</v>
+        <v>1.1896875739999999</v>
       </c>
       <c r="Y31">
-        <v>1.21609576</v>
+        <v>1.215700614</v>
       </c>
       <c r="Z31">
-        <v>1.2422566180000001</v>
+        <v>1.2412101179999999</v>
       </c>
       <c r="AA31">
-        <v>1.2659353520000001</v>
+        <v>1.2645214309999999</v>
       </c>
       <c r="AB31">
-        <v>1.288197644</v>
+        <v>1.286596058</v>
       </c>
       <c r="AC31">
-        <v>1.312294372</v>
+        <v>1.310557059</v>
       </c>
       <c r="AD31">
-        <v>1.336047811</v>
+        <v>1.3342317610000001</v>
       </c>
       <c r="AE31">
-        <v>1.359690176</v>
+        <v>1.3578438260000001</v>
       </c>
       <c r="AF31">
-        <v>1.3834758540000001</v>
+        <v>1.3816194230000001</v>
       </c>
       <c r="AG31">
-        <v>1.4086093340000001</v>
+        <v>1.406737141</v>
       </c>
       <c r="AH31">
-        <v>1.433065773</v>
+        <v>1.4312195190000001</v>
       </c>
       <c r="AI31">
-        <v>1.457255988</v>
+        <v>1.4554796350000001</v>
       </c>
       <c r="AJ31">
-        <v>1.4826721940000001</v>
+        <v>1.4809754550000001</v>
       </c>
       <c r="AK31">
-        <v>1.5079763610000001</v>
+        <v>1.5064149250000001</v>
       </c>
       <c r="AL31">
-        <v>1.532990232</v>
+        <v>1.531619407</v>
       </c>
       <c r="AM31">
-        <v>1.5556991760000001</v>
+        <v>1.554652836</v>
       </c>
       <c r="AN31">
-        <v>1.5768145259999999</v>
+        <v>1.5762818030000001</v>
       </c>
       <c r="AO31">
-        <v>1.597250244</v>
+        <v>1.5973554400000001</v>
       </c>
       <c r="AP31">
-        <v>1.61855478</v>
+        <v>1.6193542869999999</v>
       </c>
       <c r="AQ31">
-        <v>1.638451471</v>
+        <v>1.6400456919999999</v>
       </c>
       <c r="AR31">
-        <v>1.658135664</v>
+        <v>1.6605913240000001</v>
       </c>
       <c r="AS31">
-        <v>1.678096703</v>
+        <v>1.681494654</v>
       </c>
       <c r="AT31">
-        <v>1.6969332420000001</v>
+        <v>1.701385484</v>
       </c>
       <c r="AU31">
-        <v>1.7155968290000001</v>
+        <v>1.7211622680000001</v>
       </c>
       <c r="AV31">
-        <v>1.748859795</v>
+        <v>1.755212668</v>
       </c>
     </row>
     <row r="32" spans="1:48" x14ac:dyDescent="0.25">
@@ -9304,139 +9304,139 @@
         <v>87412.254258101195</v>
       </c>
       <c r="D32">
-        <v>89779.333647315201</v>
+        <v>89778.991173318398</v>
       </c>
       <c r="E32">
-        <v>65354.7058355599</v>
+        <v>65381.519888118703</v>
       </c>
       <c r="F32">
-        <v>66867.940471114707</v>
+        <v>66931.019109666493</v>
       </c>
       <c r="G32">
-        <v>68548.696147868293</v>
+        <v>68645.640141566197</v>
       </c>
       <c r="H32">
-        <v>68886.365404837401</v>
+        <v>68897.232634033993</v>
       </c>
       <c r="I32">
-        <v>70634.4399765407</v>
+        <v>70602.417243333097</v>
       </c>
       <c r="J32">
-        <v>73394.269231097598</v>
+        <v>73333.074776310095</v>
       </c>
       <c r="K32">
-        <v>75887.442260401396</v>
+        <v>75829.590216299795</v>
       </c>
       <c r="L32">
-        <v>77696.839428836596</v>
+        <v>77650.559639002095</v>
       </c>
       <c r="M32">
-        <v>78958.807762078606</v>
+        <v>78927.374532706002</v>
       </c>
       <c r="N32">
-        <v>84605.181421196103</v>
+        <v>84570.049120831594</v>
       </c>
       <c r="O32">
-        <v>85951.091500545197</v>
+        <v>85955.443080428202</v>
       </c>
       <c r="P32">
-        <v>89736.422568822207</v>
+        <v>89754.366446032596</v>
       </c>
       <c r="Q32">
-        <v>91206.829339312404</v>
+        <v>91257.292271170998</v>
       </c>
       <c r="R32">
-        <v>95415.3273216612</v>
+        <v>95464.208780858302</v>
       </c>
       <c r="S32">
-        <v>96828.547399248098</v>
+        <v>96905.2249407934</v>
       </c>
       <c r="T32">
-        <v>99406.052460982595</v>
+        <v>99481.804623752803</v>
       </c>
       <c r="U32">
-        <v>105018.676623319</v>
+        <v>105106.890922074</v>
       </c>
       <c r="V32">
-        <v>107944.811362742</v>
+        <v>108019.002894608</v>
       </c>
       <c r="W32">
-        <v>107527.65949091699</v>
+        <v>107621.36220639601</v>
       </c>
       <c r="X32">
-        <v>108480.8277255</v>
+        <v>108567.110947439</v>
       </c>
       <c r="Y32">
-        <v>106759.324499101</v>
+        <v>106820.23268446499</v>
       </c>
       <c r="Z32">
-        <v>106115.87488208999</v>
+        <v>106162.67455667599</v>
       </c>
       <c r="AA32">
-        <v>105456.114555644</v>
+        <v>105497.184209781</v>
       </c>
       <c r="AB32">
-        <v>104811.900686123</v>
+        <v>104852.008332171</v>
       </c>
       <c r="AC32">
-        <v>106014.378445219</v>
+        <v>106055.922242228</v>
       </c>
       <c r="AD32">
-        <v>106974.120054688</v>
+        <v>107018.30746559201</v>
       </c>
       <c r="AE32">
-        <v>107878.42248382801</v>
+        <v>107926.584286282</v>
       </c>
       <c r="AF32">
-        <v>108808.69168742999</v>
+        <v>108863.039269456</v>
       </c>
       <c r="AG32">
-        <v>110395.27727317</v>
+        <v>110454.223173058</v>
       </c>
       <c r="AH32">
-        <v>111201.344112816</v>
+        <v>111263.848452605</v>
       </c>
       <c r="AI32">
-        <v>111644.094693251</v>
+        <v>111709.13797867901</v>
       </c>
       <c r="AJ32">
-        <v>112770.420539763</v>
+        <v>112837.449257224</v>
       </c>
       <c r="AK32">
-        <v>113778.926971005</v>
+        <v>113848.115862263</v>
       </c>
       <c r="AL32">
-        <v>114521.474559722</v>
+        <v>114592.964415258</v>
       </c>
       <c r="AM32">
-        <v>113996.12738432099</v>
+        <v>114070.376202864</v>
       </c>
       <c r="AN32">
-        <v>112970.80139084</v>
+        <v>113048.28521673</v>
       </c>
       <c r="AO32">
-        <v>111863.949432535</v>
+        <v>111945.062712591</v>
       </c>
       <c r="AP32">
-        <v>111468.151723007</v>
+        <v>111553.130800598</v>
       </c>
       <c r="AQ32">
-        <v>110390.01310064799</v>
+        <v>110479.874680138</v>
       </c>
       <c r="AR32">
-        <v>109319.50099467899</v>
+        <v>109415.744166633</v>
       </c>
       <c r="AS32">
-        <v>108595.45630041799</v>
+        <v>108696.360388987</v>
       </c>
       <c r="AT32">
-        <v>107460.82861042699</v>
+        <v>107565.47544626</v>
       </c>
       <c r="AU32">
-        <v>106179.42511888299</v>
+        <v>106286.922176133</v>
       </c>
       <c r="AV32">
-        <v>109595.764034609</v>
+        <v>109726.01457729</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
@@ -9599,136 +9599,136 @@
         <v>1.2911593599999999E-3</v>
       </c>
       <c r="E34">
-        <v>1.3028745799999999E-3</v>
+        <v>1.3028729499999999E-3</v>
       </c>
       <c r="F34">
-        <v>1.3155393E-3</v>
+        <v>1.3155347700000001E-3</v>
       </c>
       <c r="G34">
-        <v>1.3464105499999999E-3</v>
+        <v>1.34640178E-3</v>
       </c>
       <c r="H34">
-        <v>1.3905160500000001E-3</v>
+        <v>1.3905015600000001E-3</v>
       </c>
       <c r="I34">
-        <v>1.4271793999999999E-3</v>
+        <v>1.42715892E-3</v>
       </c>
       <c r="J34">
-        <v>1.46040057E-3</v>
+        <v>1.4603745200000001E-3</v>
       </c>
       <c r="K34">
-        <v>1.4916140500000001E-3</v>
+        <v>1.49158047E-3</v>
       </c>
       <c r="L34">
-        <v>1.5395514500000001E-3</v>
+        <v>1.53950871E-3</v>
       </c>
       <c r="M34">
-        <v>1.60647999E-3</v>
+        <v>1.60642882E-3</v>
       </c>
       <c r="N34">
-        <v>1.65767489E-3</v>
+        <v>1.65761834E-3</v>
       </c>
       <c r="O34">
-        <v>1.6920494899999999E-3</v>
+        <v>1.6919922899999999E-3</v>
       </c>
       <c r="P34">
-        <v>1.72094993E-3</v>
+        <v>1.7208971999999999E-3</v>
       </c>
       <c r="Q34">
-        <v>1.7501776999999999E-3</v>
+        <v>1.7501238599999999E-3</v>
       </c>
       <c r="R34">
-        <v>1.80627549E-3</v>
+        <v>1.8062075800000001E-3</v>
       </c>
       <c r="S34">
-        <v>1.86415645E-3</v>
+        <v>1.8640803500000001E-3</v>
       </c>
       <c r="T34">
-        <v>1.9008500599999999E-3</v>
+        <v>1.9007646999999999E-3</v>
       </c>
       <c r="U34">
-        <v>1.93808006E-3</v>
+        <v>1.9380019400000001E-3</v>
       </c>
       <c r="V34">
-        <v>1.9760371399999998E-3</v>
+        <v>1.9759222899999999E-3</v>
       </c>
       <c r="W34">
-        <v>2.0151191200000001E-3</v>
+        <v>2.0149587699999998E-3</v>
       </c>
       <c r="X34">
-        <v>2.05560279E-3</v>
+        <v>2.0553738500000002E-3</v>
       </c>
       <c r="Y34">
-        <v>2.0959761200000002E-3</v>
+        <v>2.0957212000000001E-3</v>
       </c>
       <c r="Z34">
-        <v>2.13692717E-3</v>
+        <v>2.1366450500000002E-3</v>
       </c>
       <c r="AA34">
-        <v>2.1789481599999998E-3</v>
+        <v>2.1786081400000002E-3</v>
       </c>
       <c r="AB34">
-        <v>2.2223869900000002E-3</v>
+        <v>2.2219491199999999E-3</v>
       </c>
       <c r="AC34">
-        <v>2.2677902000000001E-3</v>
+        <v>2.26723485E-3</v>
       </c>
       <c r="AD34">
-        <v>2.3126958600000001E-3</v>
+        <v>2.3120292899999999E-3</v>
       </c>
       <c r="AE34">
-        <v>2.35817721E-3</v>
+        <v>2.3573912500000002E-3</v>
       </c>
       <c r="AF34">
-        <v>2.4047185300000002E-3</v>
+        <v>2.4037985499999999E-3</v>
       </c>
       <c r="AG34">
-        <v>2.45223274E-3</v>
+        <v>2.4511692000000001E-3</v>
       </c>
       <c r="AH34">
-        <v>2.5005997999999999E-3</v>
+        <v>2.4993891199999998E-3</v>
       </c>
       <c r="AI34">
-        <v>2.54933777E-3</v>
+        <v>2.5479762700000002E-3</v>
       </c>
       <c r="AJ34">
-        <v>2.5987478499999998E-3</v>
+        <v>2.5972134200000002E-3</v>
       </c>
       <c r="AK34">
-        <v>2.6488481000000001E-3</v>
+        <v>2.64708379E-3</v>
       </c>
       <c r="AL34">
-        <v>2.6997084800000001E-3</v>
+        <v>2.6978770900000001E-3</v>
       </c>
       <c r="AM34">
-        <v>2.7515122999999999E-3</v>
+        <v>2.7494585099999999E-3</v>
       </c>
       <c r="AN34">
-        <v>2.8029628500000001E-3</v>
+        <v>2.8008562599999998E-3</v>
       </c>
       <c r="AO34">
-        <v>2.8548275399999999E-3</v>
+        <v>2.8525955299999999E-3</v>
       </c>
       <c r="AP34">
-        <v>2.9072272899999998E-3</v>
+        <v>2.90481832E-3</v>
       </c>
       <c r="AQ34">
-        <v>2.9597561800000002E-3</v>
+        <v>2.9571854199999998E-3</v>
       </c>
       <c r="AR34">
-        <v>3.0121305000000002E-3</v>
+        <v>3.0094180999999998E-3</v>
       </c>
       <c r="AS34">
-        <v>3.0650674900000001E-3</v>
+        <v>3.0622032299999998E-3</v>
       </c>
       <c r="AT34">
-        <v>3.1176914400000001E-3</v>
+        <v>3.1146679699999998E-3</v>
       </c>
       <c r="AU34">
-        <v>3.1695865900000001E-3</v>
+        <v>3.1664361400000002E-3</v>
       </c>
       <c r="AV34">
-        <v>3.2364934599999999E-3</v>
+        <v>3.23319497E-3</v>
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
@@ -9748,133 +9748,133 @@
         <v>26830545.620000001</v>
       </c>
       <c r="F35">
-        <v>27046288.920000002</v>
+        <v>27046525.010000002</v>
       </c>
       <c r="G35">
-        <v>27260657.16</v>
+        <v>27260839.120000001</v>
       </c>
       <c r="H35">
-        <v>27476744.850000001</v>
+        <v>27476582.300000001</v>
       </c>
       <c r="I35">
-        <v>27710473.059999999</v>
+        <v>27709685.489999998</v>
       </c>
       <c r="J35">
-        <v>27947234.129999999</v>
+        <v>27945548.02</v>
       </c>
       <c r="K35">
-        <v>28179281.850000001</v>
+        <v>28176470.940000001</v>
       </c>
       <c r="L35">
-        <v>28405732.41</v>
+        <v>28401582.449999999</v>
       </c>
       <c r="M35">
-        <v>28636629.899999999</v>
+        <v>28630909.760000002</v>
       </c>
       <c r="N35">
-        <v>32255275.699999999</v>
+        <v>32247762.359999999</v>
       </c>
       <c r="O35">
-        <v>32594526.719999999</v>
+        <v>32584977.359999999</v>
       </c>
       <c r="P35">
-        <v>32945817.579999998</v>
+        <v>32933946.640000001</v>
       </c>
       <c r="Q35">
-        <v>31696940.440000001</v>
+        <v>31682655.68</v>
       </c>
       <c r="R35">
-        <v>31564343.690000001</v>
+        <v>31547745.18</v>
       </c>
       <c r="S35">
-        <v>30961012.039999999</v>
+        <v>30944923.140000001</v>
       </c>
       <c r="T35">
-        <v>30701682.940000001</v>
+        <v>30686354.489999998</v>
       </c>
       <c r="U35">
-        <v>32586201.219999999</v>
+        <v>32571778.699999999</v>
       </c>
       <c r="V35">
-        <v>31356190.010000002</v>
+        <v>31342760.73</v>
       </c>
       <c r="W35">
-        <v>29216192.780000001</v>
+        <v>29203820.859999999</v>
       </c>
       <c r="X35">
-        <v>27130986.390000001</v>
+        <v>27119753.34</v>
       </c>
       <c r="Y35">
-        <v>24937910.989999998</v>
+        <v>24927885.510000002</v>
       </c>
       <c r="Z35">
-        <v>22865413.52</v>
+        <v>22856623.68</v>
       </c>
       <c r="AA35">
-        <v>20616898.719999999</v>
+        <v>20609384.82</v>
       </c>
       <c r="AB35">
-        <v>18283846.039999999</v>
+        <v>18277693.460000001</v>
       </c>
       <c r="AC35">
-        <v>17552232.34</v>
+        <v>17547595.82</v>
       </c>
       <c r="AD35">
-        <v>16673395.199999999</v>
+        <v>16670423.42</v>
       </c>
       <c r="AE35">
-        <v>15739081.619999999</v>
+        <v>15737857.18</v>
       </c>
       <c r="AF35">
-        <v>14795672.369999999</v>
+        <v>14796245.77</v>
       </c>
       <c r="AG35">
-        <v>14113127.33</v>
+        <v>14115544.199999999</v>
       </c>
       <c r="AH35">
-        <v>13109770.609999999</v>
+        <v>13114094.869999999</v>
       </c>
       <c r="AI35">
-        <v>11963416.970000001</v>
+        <v>11969720.17</v>
       </c>
       <c r="AJ35">
-        <v>11080646.699999999</v>
+        <v>11088992.449999999</v>
       </c>
       <c r="AK35">
-        <v>10147307.460000001</v>
+        <v>10157775.59</v>
       </c>
       <c r="AL35">
-        <v>9117452.1510000005</v>
+        <v>9130128.4839999899</v>
       </c>
       <c r="AM35">
-        <v>8874804.8460000008</v>
+        <v>8889752.2420000006</v>
       </c>
       <c r="AN35">
-        <v>8447436.477</v>
+        <v>8464720.1809999999</v>
       </c>
       <c r="AO35">
-        <v>8018341.5559999999</v>
+        <v>8037942.9890000001</v>
       </c>
       <c r="AP35">
-        <v>7862757.176</v>
+        <v>7884653.0630000001</v>
       </c>
       <c r="AQ35">
-        <v>7524139.8470000001</v>
+        <v>7548314.3839999996</v>
       </c>
       <c r="AR35">
-        <v>7231025.9510000004</v>
+        <v>7257466.5669999998</v>
       </c>
       <c r="AS35">
-        <v>7075271.5520000001</v>
+        <v>7103976.7019999996</v>
       </c>
       <c r="AT35">
-        <v>6825129.8099999996</v>
+        <v>6856095.6890000002</v>
       </c>
       <c r="AU35">
-        <v>6571838.4199999999</v>
+        <v>6605047.2850000001</v>
       </c>
       <c r="AV35">
-        <v>6946907.1799999997</v>
+        <v>6985862.7029999997</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
@@ -9882,145 +9882,145 @@
         <v>38</v>
       </c>
       <c r="B36">
-        <v>40116783.705106698</v>
+        <v>40966249.706947699</v>
       </c>
       <c r="C36">
-        <v>40760871.6436335</v>
+        <v>41623976.0969017</v>
       </c>
       <c r="D36">
-        <v>41415300.619999997</v>
+        <v>42292262.5</v>
       </c>
       <c r="E36">
-        <v>51230585.32</v>
+        <v>52117673.670000002</v>
       </c>
       <c r="F36">
-        <v>55457511</v>
+        <v>56593513.100000001</v>
       </c>
       <c r="G36">
-        <v>56040552.729999997</v>
+        <v>57429312.409999996</v>
       </c>
       <c r="H36">
-        <v>44441626.210000001</v>
+        <v>45132011.18</v>
       </c>
       <c r="I36">
-        <v>44271561.219999999</v>
+        <v>44620254.649999999</v>
       </c>
       <c r="J36">
-        <v>49513252.68</v>
+        <v>49703724.32</v>
       </c>
       <c r="K36">
-        <v>56643042.609999999</v>
+        <v>56790200.770000003</v>
       </c>
       <c r="L36">
-        <v>56801410.130000003</v>
+        <v>56986189.119999997</v>
       </c>
       <c r="M36">
-        <v>51118831.060000002</v>
+        <v>51367221.469999999</v>
       </c>
       <c r="N36">
-        <v>36805346.590000004</v>
+        <v>37200083.409999996</v>
       </c>
       <c r="O36">
-        <v>34823666.960000001</v>
+        <v>35466766.060000002</v>
       </c>
       <c r="P36">
-        <v>42649720.899999999</v>
+        <v>43400498.619999997</v>
       </c>
       <c r="Q36">
-        <v>69061542.890000001</v>
+        <v>69766721.549999997</v>
       </c>
       <c r="R36">
-        <v>78541502.400000006</v>
+        <v>79204793.349999994</v>
       </c>
       <c r="S36">
-        <v>93459226.170000002</v>
+        <v>94046286.75</v>
       </c>
       <c r="T36">
-        <v>95562032.930000007</v>
+        <v>96161002.439999998</v>
       </c>
       <c r="U36">
-        <v>97922913.310000002</v>
+        <v>98531662.390000001</v>
       </c>
       <c r="V36">
-        <v>101474463.59999999</v>
+        <v>102070909.09999999</v>
       </c>
       <c r="W36">
-        <v>119317384.2</v>
+        <v>119788243.40000001</v>
       </c>
       <c r="X36">
-        <v>133207233.5</v>
+        <v>133569126.2</v>
       </c>
       <c r="Y36">
-        <v>140401828.59999999</v>
+        <v>140702558.90000001</v>
       </c>
       <c r="Z36">
-        <v>142194459.59999999</v>
+        <v>142460320.30000001</v>
       </c>
       <c r="AA36">
-        <v>140141279.19999999</v>
+        <v>140393574.09999999</v>
       </c>
       <c r="AB36">
-        <v>140173669.59999999</v>
+        <v>140362646.90000001</v>
       </c>
       <c r="AC36">
-        <v>142963589.40000001</v>
+        <v>143051425</v>
       </c>
       <c r="AD36">
-        <v>141391311.59999999</v>
+        <v>141440739.40000001</v>
       </c>
       <c r="AE36">
-        <v>138207457.90000001</v>
+        <v>138248721.40000001</v>
       </c>
       <c r="AF36">
-        <v>135467926.09999999</v>
+        <v>135513985.09999999</v>
       </c>
       <c r="AG36">
-        <v>132512121.59999999</v>
+        <v>132559403.5</v>
       </c>
       <c r="AH36">
-        <v>128725122.09999999</v>
+        <v>128774160.40000001</v>
       </c>
       <c r="AI36">
-        <v>125254017.09999999</v>
+        <v>125304506.90000001</v>
       </c>
       <c r="AJ36">
-        <v>122079529.8</v>
+        <v>122112141.40000001</v>
       </c>
       <c r="AK36">
-        <v>119686788.8</v>
+        <v>119696789.09999999</v>
       </c>
       <c r="AL36">
-        <v>121202341.90000001</v>
+        <v>121129052.90000001</v>
       </c>
       <c r="AM36">
-        <v>121731111.8</v>
+        <v>121595017.40000001</v>
       </c>
       <c r="AN36">
-        <v>120216082.40000001</v>
+        <v>120062352.2</v>
       </c>
       <c r="AO36">
-        <v>117979000.2</v>
+        <v>117814110.40000001</v>
       </c>
       <c r="AP36">
-        <v>115442962.09999999</v>
+        <v>115262717.90000001</v>
       </c>
       <c r="AQ36">
-        <v>112761366.8</v>
+        <v>112560918.90000001</v>
       </c>
       <c r="AR36">
-        <v>110669409.2</v>
+        <v>110429507.90000001</v>
       </c>
       <c r="AS36">
-        <v>110570705.3</v>
+        <v>110239771.3</v>
       </c>
       <c r="AT36">
-        <v>110942012.40000001</v>
+        <v>110499654.8</v>
       </c>
       <c r="AU36">
-        <v>111446734.7</v>
+        <v>110885799.2</v>
       </c>
       <c r="AV36">
-        <v>111847168.40000001</v>
+        <v>111171030.40000001</v>
       </c>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
@@ -10028,145 +10028,145 @@
         <v>39</v>
       </c>
       <c r="B37">
-        <v>1.9161062080326401E-4</v>
+        <v>1.8387279230377499E-4</v>
       </c>
       <c r="C37">
-        <v>1.95442833219329E-4</v>
+        <v>1.8755024814985001E-4</v>
       </c>
       <c r="D37">
-        <v>1.9766545599999999E-4</v>
+        <v>1.8968311500000001E-4</v>
       </c>
       <c r="E37">
-        <v>1.5610889700000001E-4</v>
+        <v>1.5081159800000001E-4</v>
       </c>
       <c r="F37">
-        <v>1.5471472200000001E-4</v>
+        <v>1.4978342699999999E-4</v>
       </c>
       <c r="G37">
-        <v>1.59234078E-4</v>
+        <v>1.5415817900000001E-4</v>
       </c>
       <c r="H37">
-        <v>1.6907519899999999E-4</v>
+        <v>1.6304628599999999E-4</v>
       </c>
       <c r="I37">
-        <v>1.6881448099999999E-4</v>
+        <v>1.63044928E-4</v>
       </c>
       <c r="J37">
-        <v>1.78970502E-4</v>
+        <v>1.73750141E-4</v>
       </c>
       <c r="K37">
-        <v>1.74352275E-4</v>
+        <v>1.7001224899999999E-4</v>
       </c>
       <c r="L37">
-        <v>1.6876091299999999E-4</v>
+        <v>1.6454941100000001E-4</v>
       </c>
       <c r="M37">
-        <v>1.60227519E-4</v>
+        <v>1.5569669900000001E-4</v>
       </c>
       <c r="N37">
-        <v>1.65005841E-4</v>
+        <v>1.58028434E-4</v>
       </c>
       <c r="O37">
-        <v>1.4191521899999999E-4</v>
+        <v>1.3493923300000001E-4</v>
       </c>
       <c r="P37">
-        <v>1.45420176E-4</v>
+        <v>1.3959396800000001E-4</v>
       </c>
       <c r="Q37" s="39">
-        <v>1.24541545E-4</v>
+        <v>1.2172555899999999E-4</v>
       </c>
       <c r="R37">
-        <v>1.39780825E-4</v>
+        <v>1.3726166999999999E-4</v>
       </c>
       <c r="S37" s="39">
-        <v>1.22019287E-4</v>
+        <v>1.20398841E-4</v>
       </c>
       <c r="T37">
-        <v>1.3665202300000001E-4</v>
+        <v>1.34924935E-4</v>
       </c>
       <c r="U37">
-        <v>1.37991423E-4</v>
+        <v>1.3637180800000001E-4</v>
       </c>
       <c r="V37">
-        <v>1.3563041699999999E-4</v>
+        <v>1.3419400899999999E-4</v>
       </c>
       <c r="W37" s="39">
-        <v>1.1441439700000001E-4</v>
+        <v>1.1363082800000001E-4</v>
       </c>
       <c r="X37">
-        <v>1.16616261E-4</v>
+        <v>1.1611837900000001E-4</v>
       </c>
       <c r="Y37">
-        <v>1.2197422800000001E-4</v>
+        <v>1.2162368E-4</v>
       </c>
       <c r="Z37">
-        <v>1.2470353700000001E-4</v>
+        <v>1.24406725E-4</v>
       </c>
       <c r="AA37">
-        <v>1.30834978E-4</v>
+        <v>1.3049046800000001E-4</v>
       </c>
       <c r="AB37">
-        <v>1.3411362499999999E-4</v>
+        <v>1.3370822299999999E-4</v>
       </c>
       <c r="AC37">
-        <v>1.3288879300000001E-4</v>
+        <v>1.32466298E-4</v>
       </c>
       <c r="AD37">
-        <v>1.37290408E-4</v>
+        <v>1.3679012399999999E-4</v>
       </c>
       <c r="AE37">
-        <v>1.4080058300000001E-4</v>
+        <v>1.4022233799999999E-4</v>
       </c>
       <c r="AF37">
-        <v>1.4271983599999999E-4</v>
+        <v>1.4207275200000001E-4</v>
       </c>
       <c r="AG37">
-        <v>1.4681486500000001E-4</v>
+        <v>1.4608111699999999E-4</v>
       </c>
       <c r="AH37">
-        <v>1.5068836299999999E-4</v>
+        <v>1.4984669700000001E-4</v>
       </c>
       <c r="AI37">
-        <v>1.5295408099999999E-4</v>
+        <v>1.52013507E-4</v>
       </c>
       <c r="AJ37">
-        <v>1.56938161E-4</v>
+        <v>1.55897015E-4</v>
       </c>
       <c r="AK37">
-        <v>1.6128444499999999E-4</v>
+        <v>1.6014256599999999E-4</v>
       </c>
       <c r="AL37">
-        <v>1.61868391E-4</v>
+        <v>1.6068208899999999E-4</v>
       </c>
       <c r="AM37">
-        <v>1.67856746E-4</v>
+        <v>1.6658362600000001E-4</v>
       </c>
       <c r="AN37">
-        <v>1.72896968E-4</v>
+        <v>1.71569765E-4</v>
       </c>
       <c r="AO37">
-        <v>1.7779843E-4</v>
+        <v>1.7640553E-4</v>
       </c>
       <c r="AP37">
-        <v>1.8267611799999999E-4</v>
+        <v>1.8120842399999999E-4</v>
       </c>
       <c r="AQ37">
-        <v>1.8753693099999999E-4</v>
+        <v>1.8599459600000001E-4</v>
       </c>
       <c r="AR37">
-        <v>1.9267362099999999E-4</v>
+        <v>1.9104369599999999E-4</v>
       </c>
       <c r="AS37">
-        <v>1.9861117499999999E-4</v>
+        <v>1.9687926E-4</v>
       </c>
       <c r="AT37">
-        <v>2.0473316399999999E-4</v>
+        <v>2.02890109E-4</v>
       </c>
       <c r="AU37">
-        <v>2.10852884E-4</v>
+        <v>2.0890591899999999E-4</v>
       </c>
       <c r="AV37">
-        <v>2.1697015299999999E-4</v>
+        <v>2.1492640400000001E-4</v>
       </c>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
@@ -10174,145 +10174,145 @@
         <v>35</v>
       </c>
       <c r="B38">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C38">
-        <v>7966.4202385211802</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D38">
-        <v>8186.3743000000004</v>
+        <v>8022.1280880000004</v>
       </c>
       <c r="E38">
-        <v>9701.1703209999996</v>
+        <v>9534.2584409999999</v>
       </c>
       <c r="F38">
-        <v>10407.805619999999</v>
+        <v>10282.47286</v>
       </c>
       <c r="G38">
-        <v>10623.29257</v>
+        <v>10539.521699999999</v>
       </c>
       <c r="H38">
-        <v>8737.1823260000001</v>
+        <v>8556.5195359999998</v>
       </c>
       <c r="I38">
-        <v>8818.4625849999902</v>
+        <v>8591.9026649999996</v>
       </c>
       <c r="J38">
-        <v>9940.1322770000006</v>
+        <v>9694.266243</v>
       </c>
       <c r="K38">
-        <v>11282.96738</v>
+        <v>11036.826069999999</v>
       </c>
       <c r="L38">
-        <v>11424.569079999999</v>
+        <v>11182.380649999999</v>
       </c>
       <c r="M38">
-        <v>10506.44162</v>
+        <v>10264.94281</v>
       </c>
       <c r="N38">
-        <v>7837.733682</v>
+        <v>7599.993982</v>
       </c>
       <c r="O38">
-        <v>7159.1341110000003</v>
+        <v>6964.345609</v>
       </c>
       <c r="P38">
-        <v>8568.6068030000006</v>
+        <v>8403.7953550000002</v>
       </c>
       <c r="Q38">
-        <v>13270.076129999999</v>
+        <v>13144.305909999999</v>
       </c>
       <c r="R38">
-        <v>15282.475899999999</v>
+        <v>15161.77334</v>
       </c>
       <c r="S38">
-        <v>18046.88349</v>
+        <v>17946.497889999999</v>
       </c>
       <c r="T38">
-        <v>18829.531660000001</v>
+        <v>18731.853050000002</v>
       </c>
       <c r="U38">
-        <v>19429.48156</v>
+        <v>19341.830549999999</v>
       </c>
       <c r="V38">
-        <v>20279.491099999999</v>
+        <v>20201.412240000001</v>
       </c>
       <c r="W38">
-        <v>23720.276249999999</v>
+        <v>23671.50894</v>
       </c>
       <c r="X38">
-        <v>26689.909650000001</v>
+        <v>26658.756870000001</v>
       </c>
       <c r="Y38">
-        <v>28247.954610000001</v>
+        <v>28231.747480000002</v>
       </c>
       <c r="Z38">
-        <v>28850.194960000001</v>
+        <v>28838.489580000001</v>
       </c>
       <c r="AA38">
-        <v>28864.591349999999</v>
+        <v>28844.901470000001</v>
       </c>
       <c r="AB38">
-        <v>29415.639640000001</v>
+        <v>29375.17958</v>
       </c>
       <c r="AC38">
-        <v>30604.34504</v>
+        <v>30539.323659999998</v>
       </c>
       <c r="AD38">
-        <v>30894.227859999999</v>
+        <v>30808.928349999998</v>
       </c>
       <c r="AE38">
-        <v>30755.587609999999</v>
+        <v>30656.745190000001</v>
       </c>
       <c r="AF38">
-        <v>30705.280340000001</v>
+        <v>30597.126479999999</v>
       </c>
       <c r="AG38">
-        <v>30636.998920000002</v>
+        <v>30516.56769</v>
       </c>
       <c r="AH38">
-        <v>30373.837309999999</v>
+        <v>30239.176869999999</v>
       </c>
       <c r="AI38">
-        <v>30157.484110000001</v>
+        <v>30010.63667</v>
       </c>
       <c r="AJ38">
-        <v>30003.9159</v>
+        <v>29841.224429999998</v>
       </c>
       <c r="AK38">
-        <v>30031.489730000001</v>
+        <v>29851.401290000002</v>
       </c>
       <c r="AL38">
-        <v>31062.437430000002</v>
+        <v>30855.025710000002</v>
       </c>
       <c r="AM38">
-        <v>31924.517660000001</v>
+        <v>31687.6518</v>
       </c>
       <c r="AN38">
-        <v>32189.328130000002</v>
+        <v>31941.42613</v>
       </c>
       <c r="AO38">
-        <v>32259.308069999999</v>
+        <v>32001.414089999998</v>
       </c>
       <c r="AP38">
-        <v>32240.896260000001</v>
+        <v>31971.433939999999</v>
       </c>
       <c r="AQ38">
-        <v>32166.560890000001</v>
+        <v>31884.963589999999</v>
       </c>
       <c r="AR38">
-        <v>32261.434379999999</v>
+        <v>31959.815060000001</v>
       </c>
       <c r="AS38">
-        <v>32982.10353</v>
+        <v>32639.899410000002</v>
       </c>
       <c r="AT38">
-        <v>33868.678979999997</v>
+        <v>33476.382610000001</v>
       </c>
       <c r="AU38">
-        <v>34809.153890000001</v>
+        <v>34363.599699999999</v>
       </c>
       <c r="AV38">
-        <v>35733.996279999999</v>
+        <v>35235.453079999999</v>
       </c>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
@@ -10320,145 +10320,145 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>7686.80183036578</v>
+        <v>7532.5787238302</v>
       </c>
       <c r="C39">
-        <v>7966.4202385211902</v>
+        <v>7806.5870459573798</v>
       </c>
       <c r="D39">
-        <v>8186.3742824293804</v>
+        <v>8022.1280913976798</v>
       </c>
       <c r="E39">
-        <v>9701.1703209695897</v>
+        <v>9534.25844921522</v>
       </c>
       <c r="F39">
-        <v>10407.8056041769</v>
+        <v>10282.4728900873</v>
       </c>
       <c r="G39">
-        <v>10623.2925565719</v>
+        <v>10539.521694347701</v>
       </c>
       <c r="H39">
-        <v>8737.18232133936</v>
+        <v>8556.5195376094707</v>
       </c>
       <c r="I39">
-        <v>8818.4625882105793</v>
+        <v>8591.9026735474708</v>
       </c>
       <c r="J39">
-        <v>9940.1322562618698</v>
+        <v>9694.2662199945498</v>
       </c>
       <c r="K39">
-        <v>11282.9673936618</v>
+        <v>11036.8260767556</v>
       </c>
       <c r="L39">
-        <v>11424.5690587727</v>
+        <v>11182.380641377</v>
       </c>
       <c r="M39">
-        <v>10506.441609973899</v>
+        <v>10264.942820730799</v>
       </c>
       <c r="N39">
-        <v>7837.7336658944196</v>
+        <v>7599.9939644666601</v>
       </c>
       <c r="O39">
-        <v>7159.1341260828003</v>
+        <v>6964.3456031981696</v>
       </c>
       <c r="P39">
-        <v>8568.60678276402</v>
+        <v>8403.7953766794599</v>
       </c>
       <c r="Q39">
-        <v>13270.076152507399</v>
+        <v>13144.3059301741</v>
       </c>
       <c r="R39">
-        <v>15282.475901665601</v>
+        <v>15161.773338679999</v>
       </c>
       <c r="S39">
-        <v>18046.883516481001</v>
+        <v>17946.497893699499</v>
       </c>
       <c r="T39">
-        <v>18829.531698115901</v>
+        <v>18731.853010990701</v>
       </c>
       <c r="U39">
-        <v>19429.481542696099</v>
+        <v>19341.830591113499</v>
       </c>
       <c r="V39">
-        <v>20279.4911359178</v>
+        <v>20201.412245402</v>
       </c>
       <c r="W39">
-        <v>23720.2762898603</v>
+        <v>23671.508891207501</v>
       </c>
       <c r="X39">
-        <v>26689.9096319239</v>
+        <v>26658.756930790401</v>
       </c>
       <c r="Y39">
-        <v>28247.954668273302</v>
+        <v>28231.747443834702</v>
       </c>
       <c r="Z39">
-        <v>28850.194943923601</v>
+        <v>28838.489597973999</v>
       </c>
       <c r="AA39">
-        <v>28864.591277023799</v>
+        <v>28844.901512501601</v>
       </c>
       <c r="AB39">
-        <v>29415.639679608299</v>
+        <v>29375.179601575401</v>
       </c>
       <c r="AC39">
-        <v>30604.345099313599</v>
+        <v>30539.323607374601</v>
       </c>
       <c r="AD39">
-        <v>30894.227822219102</v>
+        <v>30808.928367177599</v>
       </c>
       <c r="AE39">
-        <v>30755.587549267901</v>
+        <v>30656.745237218602</v>
       </c>
       <c r="AF39">
-        <v>30705.2802812521</v>
+        <v>30597.126418643998</v>
       </c>
       <c r="AG39">
-        <v>30636.998974567501</v>
+        <v>30516.567655133698</v>
       </c>
       <c r="AH39">
-        <v>30373.837254224101</v>
+        <v>30239.176811888199</v>
       </c>
       <c r="AI39">
-        <v>30157.484105088701</v>
+        <v>30010.6367037747</v>
       </c>
       <c r="AJ39">
-        <v>30003.915877556701</v>
+        <v>29841.2244475179</v>
       </c>
       <c r="AK39">
-        <v>30031.489738440199</v>
+        <v>29851.401270434799</v>
       </c>
       <c r="AL39">
-        <v>31062.4374267848</v>
+        <v>30855.025684563501</v>
       </c>
       <c r="AM39">
-        <v>31924.517729710198</v>
+        <v>31687.651852025101</v>
       </c>
       <c r="AN39">
-        <v>32189.328183798101</v>
+        <v>31941.426084301202</v>
       </c>
       <c r="AO39">
-        <v>32259.308026529601</v>
+        <v>32001.414107590499</v>
       </c>
       <c r="AP39">
-        <v>32240.896230849099</v>
+        <v>31971.433940615501</v>
       </c>
       <c r="AQ39">
-        <v>32166.560887037202</v>
+        <v>31884.963533194201</v>
       </c>
       <c r="AR39">
-        <v>32261.434398494701</v>
+        <v>31959.815100677199</v>
       </c>
       <c r="AS39">
-        <v>32982.103582211697</v>
+        <v>32639.899448113199</v>
       </c>
       <c r="AT39">
-        <v>33868.678964179198</v>
+        <v>33476.3826588343</v>
       </c>
       <c r="AU39">
-        <v>34809.153897877797</v>
+        <v>34363.599711925403</v>
       </c>
       <c r="AV39">
-        <v>35733.996311364703</v>
+        <v>35235.453062846602</v>
       </c>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
@@ -10514,97 +10514,97 @@
         <v>93114.179950000005</v>
       </c>
       <c r="R40">
-        <v>94895.604689999906</v>
+        <v>94796.557379999998</v>
       </c>
       <c r="S40">
-        <v>97226.709499999997</v>
+        <v>96974.936379999999</v>
       </c>
       <c r="T40">
-        <v>97061.455409999995</v>
+        <v>96791.164690000005</v>
       </c>
       <c r="U40">
-        <v>100282.4745</v>
+        <v>100002.82369999999</v>
       </c>
       <c r="V40">
-        <v>98968.584090000004</v>
+        <v>98647.753949999998</v>
       </c>
       <c r="W40">
-        <v>99599.869890000002</v>
+        <v>99082.267460000003</v>
       </c>
       <c r="X40">
-        <v>99355.759820000007</v>
+        <v>98680.086620000002</v>
       </c>
       <c r="Y40">
-        <v>97357.762480000005</v>
+        <v>96592.211710000003</v>
       </c>
       <c r="Z40">
-        <v>94256.573520000005</v>
+        <v>93454.844630000007</v>
       </c>
       <c r="AA40">
-        <v>89955.959350000005</v>
+        <v>89155.704589999994</v>
       </c>
       <c r="AB40">
-        <v>85994.242509999996</v>
+        <v>85165.772110000005</v>
       </c>
       <c r="AC40">
-        <v>85138.895879999996</v>
+        <v>84258.503259999998</v>
       </c>
       <c r="AD40">
-        <v>83038.368449999994</v>
+        <v>82157.810570000001</v>
       </c>
       <c r="AE40">
-        <v>80471.274239999999</v>
+        <v>79611.326709999994</v>
       </c>
       <c r="AF40">
-        <v>77989.853529999906</v>
+        <v>77149.6201</v>
       </c>
       <c r="AG40">
-        <v>75857.753920000003</v>
+        <v>75039.790179999996</v>
       </c>
       <c r="AH40">
-        <v>73031.851509999906</v>
+        <v>72241.797869999995</v>
       </c>
       <c r="AI40">
-        <v>70060.619600000005</v>
+        <v>69294.933749999997</v>
       </c>
       <c r="AJ40">
-        <v>67565.684330000004</v>
+        <v>66819.02046</v>
       </c>
       <c r="AK40">
-        <v>65176.641250000001</v>
+        <v>64441.307249999998</v>
       </c>
       <c r="AL40">
-        <v>63559.619169999998</v>
+        <v>62785.882180000001</v>
       </c>
       <c r="AM40">
-        <v>62925.64832</v>
+        <v>62132.347470000001</v>
       </c>
       <c r="AN40">
-        <v>61534.393779999999</v>
+        <v>60747.515700000004</v>
       </c>
       <c r="AO40">
-        <v>59973.710379999997</v>
+        <v>59201.534169999999</v>
       </c>
       <c r="AP40">
-        <v>58768.345359999999</v>
+        <v>58014.332470000001</v>
       </c>
       <c r="AQ40">
-        <v>57251.498549999997</v>
+        <v>56514.685619999997</v>
       </c>
       <c r="AR40">
-        <v>55950.486559999998</v>
+        <v>55221.469640000003</v>
       </c>
       <c r="AS40">
-        <v>55333.930500000002</v>
+        <v>54584.364820000003</v>
       </c>
       <c r="AT40">
-        <v>54688.871729999999</v>
+        <v>53909.564879999998</v>
       </c>
       <c r="AU40">
-        <v>54077.8364</v>
+        <v>53265.813459999998</v>
       </c>
       <c r="AV40">
-        <v>54415.55949</v>
+        <v>53581.403109999999</v>
       </c>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
@@ -10660,97 +10660,97 @@
         <v>93114.179950000005</v>
       </c>
       <c r="R41">
-        <v>94895.604689999906</v>
+        <v>94796.557379999998</v>
       </c>
       <c r="S41">
-        <v>97226.709499999997</v>
+        <v>96974.936379999999</v>
       </c>
       <c r="T41">
-        <v>97061.455409999995</v>
+        <v>96791.164690000005</v>
       </c>
       <c r="U41">
-        <v>100282.4745</v>
+        <v>100002.82369999999</v>
       </c>
       <c r="V41">
-        <v>98968.584090000004</v>
+        <v>98647.753949999998</v>
       </c>
       <c r="W41">
-        <v>99599.869890000002</v>
+        <v>99082.267460000003</v>
       </c>
       <c r="X41">
-        <v>99355.759820000007</v>
+        <v>98680.086620000002</v>
       </c>
       <c r="Y41">
-        <v>97357.762480000005</v>
+        <v>96592.211710000003</v>
       </c>
       <c r="Z41">
-        <v>94256.573520000005</v>
+        <v>93454.844630000007</v>
       </c>
       <c r="AA41">
-        <v>89955.959350000005</v>
+        <v>89155.704589999994</v>
       </c>
       <c r="AB41">
-        <v>85994.242509999996</v>
+        <v>85165.772110000005</v>
       </c>
       <c r="AC41">
-        <v>85138.895879999996</v>
+        <v>84258.503259999998</v>
       </c>
       <c r="AD41">
-        <v>83038.368449999994</v>
+        <v>82157.810570000001</v>
       </c>
       <c r="AE41">
-        <v>80471.274239999999</v>
+        <v>79611.326709999994</v>
       </c>
       <c r="AF41">
-        <v>77989.853529999906</v>
+        <v>77149.6201</v>
       </c>
       <c r="AG41">
-        <v>75857.753920000003</v>
+        <v>75039.790179999996</v>
       </c>
       <c r="AH41">
-        <v>73031.851509999906</v>
+        <v>72241.797869999995</v>
       </c>
       <c r="AI41">
-        <v>70060.619600000005</v>
+        <v>69294.933749999997</v>
       </c>
       <c r="AJ41">
-        <v>67565.684330000004</v>
+        <v>66819.02046</v>
       </c>
       <c r="AK41">
-        <v>65176.641250000001</v>
+        <v>64441.307249999998</v>
       </c>
       <c r="AL41">
-        <v>63559.619169999998</v>
+        <v>62785.882180000001</v>
       </c>
       <c r="AM41">
-        <v>62925.64832</v>
+        <v>62132.347470000001</v>
       </c>
       <c r="AN41">
-        <v>61534.393779999999</v>
+        <v>60747.515700000004</v>
       </c>
       <c r="AO41">
-        <v>59973.710379999997</v>
+        <v>59201.534169999999</v>
       </c>
       <c r="AP41">
-        <v>58768.345359999999</v>
+        <v>58014.332470000001</v>
       </c>
       <c r="AQ41">
-        <v>57251.498549999997</v>
+        <v>56514.685619999997</v>
       </c>
       <c r="AR41">
-        <v>55950.486559999998</v>
+        <v>55221.469640000003</v>
       </c>
       <c r="AS41">
-        <v>55333.930500000002</v>
+        <v>54584.364820000003</v>
       </c>
       <c r="AT41">
-        <v>54688.871729999999</v>
+        <v>53909.564879999998</v>
       </c>
       <c r="AU41">
-        <v>54077.8364</v>
+        <v>53265.813459999998</v>
       </c>
       <c r="AV41">
-        <v>54415.55949</v>
+        <v>53581.403109999999</v>
       </c>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
@@ -10764,139 +10764,139 @@
         <v>0.98039215686274495</v>
       </c>
       <c r="D42">
-        <v>0.99102938060000001</v>
+        <v>0.99102560019999997</v>
       </c>
       <c r="E42">
-        <v>0.69050082479999997</v>
+        <v>0.69078412690000002</v>
       </c>
       <c r="F42">
-        <v>0.69826689620000004</v>
+        <v>0.69892559340000004</v>
       </c>
       <c r="G42">
-        <v>0.75048792389999996</v>
+        <v>0.75154929049999997</v>
       </c>
       <c r="H42">
-        <v>0.74196917399999995</v>
+        <v>0.74208622400000002</v>
       </c>
       <c r="I42">
-        <v>0.75691974169999998</v>
+        <v>0.75657658559999996</v>
       </c>
       <c r="J42">
-        <v>0.79354190309999995</v>
+        <v>0.79288026609999995</v>
       </c>
       <c r="K42">
-        <v>0.83577822859999995</v>
+        <v>0.83514108129999998</v>
       </c>
       <c r="L42">
-        <v>0.86124936870000002</v>
+        <v>0.86073636919999996</v>
       </c>
       <c r="M42">
-        <v>0.88263335970000001</v>
+        <v>0.8822819864</v>
       </c>
       <c r="N42">
-        <v>0.94055030360000003</v>
+        <v>0.94015974010000003</v>
       </c>
       <c r="O42">
-        <v>0.94600954900000001</v>
+        <v>0.94605744410000003</v>
       </c>
       <c r="P42">
-        <v>0.977273536</v>
+        <v>0.97746895359999997</v>
       </c>
       <c r="Q42">
-        <v>0.97951600270000005</v>
+        <v>0.98005794950000003</v>
       </c>
       <c r="R42">
-        <v>1.005487636</v>
+        <v>1.0070538339999999</v>
       </c>
       <c r="S42">
-        <v>0.99593213810000003</v>
+        <v>0.99930849889999995</v>
       </c>
       <c r="T42">
-        <v>1.024238953</v>
+        <v>1.027881781</v>
       </c>
       <c r="U42">
-        <v>1.0467123030000001</v>
+        <v>1.0505167120000001</v>
       </c>
       <c r="V42">
-        <v>1.0540249669999999</v>
+        <v>1.0584662199999999</v>
       </c>
       <c r="W42">
-        <v>1.0179504370000001</v>
+        <v>1.0245606709999999</v>
       </c>
       <c r="X42">
-        <v>1.010681154</v>
+        <v>1.019078715</v>
       </c>
       <c r="Y42">
-        <v>1.0141567010000001</v>
+        <v>1.023860674</v>
       </c>
       <c r="Z42">
-        <v>1.020025894</v>
+        <v>1.030574332</v>
       </c>
       <c r="AA42">
-        <v>1.0337931</v>
+        <v>1.0449221769999999</v>
       </c>
       <c r="AB42">
-        <v>1.0388440510000001</v>
+        <v>1.050729134</v>
       </c>
       <c r="AC42">
-        <v>1.043730657</v>
+        <v>1.0562603269999999</v>
       </c>
       <c r="AD42">
-        <v>1.06192208</v>
+        <v>1.074824198</v>
       </c>
       <c r="AE42">
-        <v>1.080180892</v>
+        <v>1.093336753</v>
       </c>
       <c r="AF42">
-        <v>1.094922674</v>
+        <v>1.108343163</v>
       </c>
       <c r="AG42">
-        <v>1.116136459</v>
+        <v>1.1297711969999999</v>
       </c>
       <c r="AH42">
-        <v>1.1351061609999999</v>
+        <v>1.148964087</v>
       </c>
       <c r="AI42">
-        <v>1.1487208840000001</v>
+        <v>1.16286757</v>
       </c>
       <c r="AJ42">
-        <v>1.1673584690000001</v>
+        <v>1.1818158839999999</v>
       </c>
       <c r="AK42">
-        <v>1.1842788280000001</v>
+        <v>1.1991438919999999</v>
       </c>
       <c r="AL42">
-        <v>1.184945608</v>
+        <v>1.200739687</v>
       </c>
       <c r="AM42">
-        <v>1.2079029779999999</v>
+        <v>1.2242684509999999</v>
       </c>
       <c r="AN42">
-        <v>1.2300196809999999</v>
+        <v>1.2469161259999999</v>
       </c>
       <c r="AO42">
-        <v>1.2532021040000001</v>
+        <v>1.2705428169999999</v>
       </c>
       <c r="AP42">
-        <v>1.28136812</v>
+        <v>1.299010022</v>
       </c>
       <c r="AQ42">
-        <v>1.3071169680000001</v>
+        <v>1.3251515540000001</v>
       </c>
       <c r="AR42">
-        <v>1.332972276</v>
+        <v>1.351462816</v>
       </c>
       <c r="AS42">
-        <v>1.358671588</v>
+        <v>1.377822879</v>
       </c>
       <c r="AT42">
-        <v>1.3820178890000001</v>
+        <v>1.401957726</v>
       </c>
       <c r="AU42">
-        <v>1.4048330689999999</v>
+        <v>1.4256295649999999</v>
       </c>
       <c r="AV42">
-        <v>1.441551402</v>
+        <v>1.4629889570000001</v>
       </c>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
@@ -10910,139 +10910,139 @@
         <v>87412.254258101195</v>
       </c>
       <c r="D43">
-        <v>89779.333647315201</v>
+        <v>89778.991173318398</v>
       </c>
       <c r="E43">
-        <v>65354.7058355599</v>
+        <v>65381.519888118703</v>
       </c>
       <c r="F43">
-        <v>66867.940471114707</v>
+        <v>66931.019109666493</v>
       </c>
       <c r="G43">
-        <v>68548.696147868293</v>
+        <v>68645.640141566197</v>
       </c>
       <c r="H43">
-        <v>68886.365404837401</v>
+        <v>68897.232634033993</v>
       </c>
       <c r="I43">
-        <v>70634.4399765407</v>
+        <v>70602.417243333097</v>
       </c>
       <c r="J43">
-        <v>73394.269231097598</v>
+        <v>73333.074776310095</v>
       </c>
       <c r="K43">
-        <v>75887.442260401396</v>
+        <v>75829.590216299795</v>
       </c>
       <c r="L43">
-        <v>77696.839428836596</v>
+        <v>77650.559639002095</v>
       </c>
       <c r="M43">
-        <v>78958.807762078606</v>
+        <v>78927.374532706002</v>
       </c>
       <c r="N43">
-        <v>84605.181421196103</v>
+        <v>84570.049120831594</v>
       </c>
       <c r="O43">
-        <v>85951.091500545197</v>
+        <v>85955.443080428202</v>
       </c>
       <c r="P43">
-        <v>89736.422568822207</v>
+        <v>89754.366446032596</v>
       </c>
       <c r="Q43">
-        <v>91206.829339312404</v>
+        <v>91257.292271170998</v>
       </c>
       <c r="R43">
-        <v>95416.357226538603</v>
+        <v>95465.236559529905</v>
       </c>
       <c r="S43">
-        <v>96831.204672762498</v>
+        <v>96907.878104820702</v>
       </c>
       <c r="T43">
-        <v>99414.123465794502</v>
+        <v>99489.874746621499</v>
       </c>
       <c r="U43">
-        <v>104966.899834433</v>
+        <v>105054.637544039</v>
       </c>
       <c r="V43">
-        <v>104315.35857949901</v>
+        <v>104415.315234946</v>
       </c>
       <c r="W43">
-        <v>101387.731079668</v>
+        <v>101515.79443301899</v>
       </c>
       <c r="X43">
-        <v>100416.99399142399</v>
+        <v>100562.77586879799</v>
       </c>
       <c r="Y43">
-        <v>98736.027213458394</v>
+        <v>98896.966984551298</v>
       </c>
       <c r="Z43">
-        <v>96144.145670114696</v>
+        <v>96312.164076725996</v>
       </c>
       <c r="AA43">
-        <v>92995.850079910495</v>
+        <v>93160.772932151594</v>
       </c>
       <c r="AB43">
-        <v>89334.607251764799</v>
+        <v>89486.157975581606</v>
       </c>
       <c r="AC43">
-        <v>88862.075733086996</v>
+        <v>88998.914205938097</v>
       </c>
       <c r="AD43">
-        <v>88180.276944230296</v>
+        <v>88305.202855336101</v>
       </c>
       <c r="AE43">
-        <v>86923.532788939803</v>
+        <v>87041.989447133499</v>
       </c>
       <c r="AF43">
-        <v>85392.858971935901</v>
+        <v>85508.253965882293</v>
       </c>
       <c r="AG43">
-        <v>84667.604847962095</v>
+        <v>84777.793574287396</v>
       </c>
       <c r="AH43">
-        <v>82898.904598238107</v>
+        <v>83003.231332943004</v>
       </c>
       <c r="AI43">
-        <v>80480.096880499696</v>
+        <v>80580.831223173402</v>
       </c>
       <c r="AJ43">
-        <v>78873.373816406005</v>
+        <v>78967.779732948897</v>
       </c>
       <c r="AK43">
-        <v>77187.316312526396</v>
+        <v>77274.399981332797</v>
       </c>
       <c r="AL43">
-        <v>75314.691581644103</v>
+        <v>75389.500516832006</v>
       </c>
       <c r="AM43">
-        <v>76008.077998308698</v>
+        <v>76066.672794090598</v>
       </c>
       <c r="AN43">
-        <v>75688.515407803905</v>
+        <v>75747.056940768103</v>
       </c>
       <c r="AO43">
-        <v>75159.180032902601</v>
+        <v>75218.083995073495</v>
       </c>
       <c r="AP43">
-        <v>75303.8842094539</v>
+        <v>75361.199298170002</v>
       </c>
       <c r="AQ43">
-        <v>74834.405198132401</v>
+        <v>74890.523473164401</v>
       </c>
       <c r="AR43">
-        <v>74580.447413190603</v>
+        <v>74629.7628633329</v>
       </c>
       <c r="AS43">
-        <v>75180.639222716607</v>
+        <v>75207.586684678696</v>
       </c>
       <c r="AT43">
-        <v>75580.999060086295</v>
+        <v>75578.930988814202</v>
       </c>
       <c r="AU43">
-        <v>75970.3328746919</v>
+        <v>75937.318472350904</v>
       </c>
       <c r="AV43">
-        <v>78442.826073423901</v>
+        <v>78389.001050495397</v>
       </c>
     </row>
   </sheetData>
@@ -11619,175 +11619,175 @@
       </c>
       <c r="F10" s="19">
         <f>result!F24/10^6</f>
-        <v>27.046288920000002</v>
+        <v>27.04652501</v>
       </c>
       <c r="G10" s="19">
         <f>result!G24/10^6</f>
-        <v>27.260657160000001</v>
+        <v>27.26083912</v>
       </c>
       <c r="H10" s="19">
         <f>result!H24/10^6</f>
-        <v>27.476744850000003</v>
+        <v>27.4765823</v>
       </c>
       <c r="I10" s="19">
         <f>result!I24/10^6</f>
-        <v>27.710473059999998</v>
+        <v>27.709685489999998</v>
       </c>
       <c r="J10" s="19">
         <f>result!J24/10^6</f>
-        <v>27.947234129999998</v>
+        <v>27.94554802</v>
       </c>
       <c r="K10" s="19">
         <f>result!K24/10^6</f>
-        <v>28.179281850000002</v>
+        <v>28.176470940000002</v>
       </c>
       <c r="L10" s="19">
         <f>result!L24/10^6</f>
-        <v>28.405732409999999</v>
+        <v>28.401582449999999</v>
       </c>
       <c r="M10" s="19">
         <f>result!M24/10^6</f>
-        <v>28.636629899999999</v>
+        <v>28.630909760000002</v>
       </c>
       <c r="N10" s="19">
         <f>result!N24/10^6</f>
-        <v>32.255275699999999</v>
+        <v>32.247762359999996</v>
       </c>
       <c r="O10" s="19">
         <f>result!O24/10^6</f>
-        <v>32.594526719999998</v>
+        <v>32.584977359999996</v>
       </c>
       <c r="P10" s="19">
         <f>result!P24/10^6</f>
-        <v>32.945817579999996</v>
+        <v>32.933946640000002</v>
       </c>
       <c r="Q10" s="19">
         <f>result!Q24/10^6</f>
-        <v>31.696940440000002</v>
+        <v>31.68265568</v>
       </c>
       <c r="R10" s="19">
         <f>result!R24/10^6</f>
-        <v>31.564343690000001</v>
+        <v>31.54774518</v>
       </c>
       <c r="S10" s="19">
         <f>result!S24/10^6</f>
-        <v>30.961012749999998</v>
+        <v>30.944923840000001</v>
       </c>
       <c r="T10" s="19">
         <f>result!T24/10^6</f>
-        <v>30.701681010000001</v>
+        <v>30.686352600000003</v>
       </c>
       <c r="U10" s="19">
         <f>result!U24/10^6</f>
-        <v>32.586206079999997</v>
+        <v>32.571783539999998</v>
       </c>
       <c r="V10" s="19">
         <f>result!V24/10^6</f>
-        <v>32.585854980000001</v>
+        <v>32.57243021</v>
       </c>
       <c r="W10" s="19">
         <f>result!W24/10^6</f>
-        <v>31.72014132</v>
+        <v>31.70775794</v>
       </c>
       <c r="X10" s="19">
         <f>result!X24/10^6</f>
-        <v>30.954653260000001</v>
+        <v>30.943359699999998</v>
       </c>
       <c r="Y10" s="19">
         <f>result!Y24/10^6</f>
-        <v>30.127535550000001</v>
+        <v>30.117426469999998</v>
       </c>
       <c r="Z10" s="19">
         <f>result!Z24/10^6</f>
-        <v>29.455510870000001</v>
+        <v>29.44672138</v>
       </c>
       <c r="AA10" s="19">
         <f>result!AA24/10^6</f>
-        <v>28.631687750000001</v>
+        <v>28.624395589999999</v>
       </c>
       <c r="AB10" s="19">
         <f>result!AB24/10^6</f>
-        <v>27.740985289999998</v>
+        <v>27.73537786</v>
       </c>
       <c r="AC10" s="19">
         <f>result!AC24/10^6</f>
-        <v>27.634130429999999</v>
+        <v>27.630402800000002</v>
       </c>
       <c r="AD10" s="19">
         <f>result!AD24/10^6</f>
-        <v>27.38713224</v>
+        <v>27.3854863</v>
       </c>
       <c r="AE10" s="19">
         <f>result!AE24/10^6</f>
-        <v>27.087129239999999</v>
+        <v>27.087770300000003</v>
       </c>
       <c r="AF10" s="19">
         <f>result!AF24/10^6</f>
-        <v>26.778406660000002</v>
+        <v>26.781542429999998</v>
       </c>
       <c r="AG10" s="19">
         <f>result!AG24/10^6</f>
-        <v>26.737962149999998</v>
+        <v>26.74379944</v>
       </c>
       <c r="AH10" s="19">
         <f>result!AH24/10^6</f>
-        <v>26.368198460000002</v>
+        <v>26.376943409999999</v>
       </c>
       <c r="AI10" s="19">
         <f>result!AI24/10^6</f>
-        <v>25.847639910000002</v>
+        <v>25.859495629999998</v>
       </c>
       <c r="AJ10" s="19">
         <f>result!AJ24/10^6</f>
-        <v>25.596685319999999</v>
+        <v>25.61185171</v>
       </c>
       <c r="AK10" s="19">
         <f>result!AK24/10^6</f>
-        <v>25.290446210000002</v>
+        <v>25.30911755</v>
       </c>
       <c r="AL10" s="19">
         <f>result!AL24/10^6</f>
-        <v>24.87984398</v>
+        <v>24.902205930000001</v>
       </c>
       <c r="AM10" s="19">
         <f>result!AM24/10^6</f>
-        <v>23.989238350000001</v>
+        <v>24.015468139999999</v>
       </c>
       <c r="AN10" s="19">
         <f>result!AN24/10^6</f>
-        <v>22.884777769999999</v>
+        <v>22.91503647</v>
       </c>
       <c r="AO10" s="19">
         <f>result!AO24/10^6</f>
-        <v>21.756461160000001</v>
+        <v>21.790873569999999</v>
       </c>
       <c r="AP10" s="19">
         <f>result!AP24/10^6</f>
-        <v>20.89831234</v>
+        <v>20.93697354</v>
       </c>
       <c r="AQ10" s="19">
         <f>result!AQ24/10^6</f>
-        <v>19.825835229999999</v>
+        <v>19.868814699999998</v>
       </c>
       <c r="AR10" s="19">
         <f>result!AR24/10^6</f>
-        <v>18.782728840000001</v>
+        <v>18.83006967</v>
       </c>
       <c r="AS10" s="19">
         <f>result!AS24/10^6</f>
-        <v>17.870085700000001</v>
+        <v>17.921799100000001</v>
       </c>
       <c r="AT10" s="19">
         <f>result!AT24/10^6</f>
-        <v>16.841986200000001</v>
+        <v>16.89806102</v>
       </c>
       <c r="AU10" s="19">
         <f>result!AU24/10^6</f>
-        <v>15.79752635</v>
+        <v>15.857929739999999</v>
       </c>
       <c r="AV10" s="19">
         <f>result!AV24/10^6</f>
-        <v>16.21137616</v>
+        <v>16.282524080000002</v>
       </c>
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
@@ -11875,63 +11875,63 @@
       </c>
       <c r="F12" s="27">
         <f t="shared" si="1"/>
-        <v>0.6457277854084652</v>
+        <v>0.64573342203659212</v>
       </c>
       <c r="G12" s="27">
         <f t="shared" si="1"/>
-        <v>0.72481776723222013</v>
+        <v>0.72482260526089093</v>
       </c>
       <c r="H12" s="27">
         <f t="shared" si="1"/>
-        <v>0.78128961754072201</v>
+        <v>0.78128499550022834</v>
       </c>
       <c r="I12" s="27">
         <f t="shared" si="1"/>
-        <v>0.75502125685052235</v>
+        <v>0.75499979810133511</v>
       </c>
       <c r="J12" s="27">
         <f t="shared" si="1"/>
-        <v>0.7916765212528819</v>
+        <v>0.79162875789665721</v>
       </c>
       <c r="K12" s="27">
         <f t="shared" si="1"/>
-        <v>0.84153709114007302</v>
+        <v>0.8414531470197989</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="1"/>
-        <v>0.94193956654322231</v>
+        <v>0.94180195306904213</v>
       </c>
       <c r="M12" s="27">
         <f t="shared" si="1"/>
-        <v>1.0099073519609814</v>
+        <v>1.0097056239133579</v>
       </c>
       <c r="N12" s="27">
         <f t="shared" si="1"/>
-        <v>1.1165295042692913</v>
+        <v>1.1162694269453945</v>
       </c>
       <c r="O12" s="27">
         <f t="shared" si="1"/>
-        <v>1.0260676506188131</v>
+        <v>1.025767039124611</v>
       </c>
       <c r="P12" s="27">
         <f t="shared" si="1"/>
-        <v>1.0011987824849715</v>
+        <v>1.0008380334871334</v>
       </c>
       <c r="Q12" s="27">
         <f t="shared" si="1"/>
-        <v>0.95137952661748637</v>
+        <v>0.95095077141215756</v>
       </c>
       <c r="R12" s="27">
         <f t="shared" si="1"/>
-        <v>1.0266703602414491</v>
+        <v>1.0261304726262164</v>
       </c>
       <c r="S12" s="27">
         <f t="shared" si="1"/>
-        <v>0.92580171477030049</v>
+        <v>0.92532062131941584</v>
       </c>
       <c r="T12" s="27">
         <f t="shared" si="1"/>
-        <v>0.98907410046703004</v>
+        <v>0.98858028602972281</v>
       </c>
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
@@ -12019,63 +12019,63 @@
       </c>
       <c r="F14" s="27">
         <f t="shared" si="2"/>
-        <v>0.82747967180192594</v>
+        <v>0.82748689496205319</v>
       </c>
       <c r="G14" s="27">
         <f t="shared" si="2"/>
-        <v>0.9217485195236238</v>
+        <v>0.9217546720297658</v>
       </c>
       <c r="H14" s="27">
         <f t="shared" si="2"/>
-        <v>0.98761541876188397</v>
+        <v>0.98760957611614131</v>
       </c>
       <c r="I14" s="27">
         <f t="shared" si="2"/>
-        <v>0.95856957501604201</v>
+        <v>0.95854233114190979</v>
       </c>
       <c r="J14" s="27">
         <f t="shared" si="2"/>
-        <v>1.0013240329369679</v>
+        <v>1.0012636211460437</v>
       </c>
       <c r="K14" s="27">
         <f t="shared" si="2"/>
-        <v>1.0632170663139122</v>
+        <v>1.0631110094065792</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="2"/>
-        <v>1.1844042277199733</v>
+        <v>1.1842311911617911</v>
       </c>
       <c r="M14" s="27">
         <f t="shared" si="2"/>
-        <v>1.2671019110534909</v>
+        <v>1.2668488086335903</v>
       </c>
       <c r="N14" s="27">
         <f t="shared" si="2"/>
-        <v>1.4058519071565987</v>
+        <v>1.4055244369013029</v>
       </c>
       <c r="O14" s="27">
         <f t="shared" si="2"/>
-        <v>1.3000286660582894</v>
+        <v>1.2996477910160114</v>
       </c>
       <c r="P14" s="27">
         <f t="shared" si="2"/>
-        <v>1.2690303639132079</v>
+        <v>1.268573110628429</v>
       </c>
       <c r="Q14" s="27">
         <f t="shared" si="2"/>
-        <v>1.208537922204586</v>
+        <v>1.2079932742376231</v>
       </c>
       <c r="R14" s="27">
         <f t="shared" si="2"/>
-        <v>1.3067637947901414</v>
+        <v>1.3060766164940079</v>
       </c>
       <c r="S14" s="27">
         <f t="shared" si="2"/>
-        <v>1.1782086011742123</v>
+        <v>1.1775963443240061</v>
       </c>
       <c r="T14" s="27">
         <f t="shared" si="2"/>
-        <v>1.2551026535995966</v>
+        <v>1.2544760192449438</v>
       </c>
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
@@ -12229,179 +12229,179 @@
       </c>
       <c r="E20" s="26">
         <f>result!E23</f>
-        <v>1.3028745799999999E-3</v>
+        <v>1.3028729499999999E-3</v>
       </c>
       <c r="F20" s="26">
         <f>result!F23</f>
-        <v>1.3155393E-3</v>
+        <v>1.3155347700000001E-3</v>
       </c>
       <c r="G20" s="26">
         <f>result!G23</f>
-        <v>1.3464105499999999E-3</v>
+        <v>1.34640178E-3</v>
       </c>
       <c r="H20" s="26">
         <f>result!H23</f>
-        <v>1.3905160500000001E-3</v>
+        <v>1.3905015600000001E-3</v>
       </c>
       <c r="I20" s="26">
         <f>result!I23</f>
-        <v>1.4271793999999999E-3</v>
+        <v>1.42715892E-3</v>
       </c>
       <c r="J20" s="26">
         <f>result!J23</f>
-        <v>1.46040057E-3</v>
+        <v>1.4603745200000001E-3</v>
       </c>
       <c r="K20" s="26">
         <f>result!K23</f>
-        <v>1.4916140500000001E-3</v>
+        <v>1.49158047E-3</v>
       </c>
       <c r="L20" s="26">
         <f>result!L23</f>
-        <v>1.5395514500000001E-3</v>
+        <v>1.53950871E-3</v>
       </c>
       <c r="M20" s="26">
         <f>result!M23</f>
-        <v>1.60647999E-3</v>
+        <v>1.60642882E-3</v>
       </c>
       <c r="N20" s="26">
         <f>result!N23</f>
-        <v>1.65767489E-3</v>
+        <v>1.65761834E-3</v>
       </c>
       <c r="O20" s="26">
         <f>result!O23</f>
-        <v>1.6920494899999999E-3</v>
+        <v>1.6919922899999999E-3</v>
       </c>
       <c r="P20" s="26">
         <f>result!P23</f>
-        <v>1.72094993E-3</v>
+        <v>1.7208971999999999E-3</v>
       </c>
       <c r="Q20" s="26">
         <f>result!Q23</f>
-        <v>1.7501776999999999E-3</v>
+        <v>1.7501238599999999E-3</v>
       </c>
       <c r="R20" s="26">
         <f>result!R23</f>
-        <v>1.80625362E-3</v>
+        <v>1.8061857999999999E-3</v>
       </c>
       <c r="S20" s="26">
         <f>result!S23</f>
-        <v>1.86407782E-3</v>
+        <v>1.86400184E-3</v>
       </c>
       <c r="T20" s="26">
         <f>result!T23</f>
-        <v>1.9006929100000001E-3</v>
+        <v>1.9006078099999999E-3</v>
       </c>
       <c r="U20" s="26">
         <f>result!U23</f>
-        <v>1.9377242600000001E-3</v>
+        <v>1.93764604E-3</v>
       </c>
       <c r="V20" s="26">
         <f>result!V23</f>
-        <v>1.9754522900000001E-3</v>
+        <v>1.9753656399999998E-3</v>
       </c>
       <c r="W20" s="26">
         <f>result!W23</f>
-        <v>2.0140372099999998E-3</v>
+        <v>2.0139419899999999E-3</v>
       </c>
       <c r="X20" s="26">
         <f>result!X23</f>
-        <v>2.0530272899999999E-3</v>
+        <v>2.0529106399999998E-3</v>
       </c>
       <c r="Y20" s="26">
         <f>result!Y23</f>
-        <v>2.0926577699999999E-3</v>
+        <v>2.0925295400000001E-3</v>
       </c>
       <c r="Z20" s="26">
         <f>result!Z23</f>
-        <v>2.13284596E-3</v>
+        <v>2.13271887E-3</v>
       </c>
       <c r="AA20" s="26">
         <f>result!AA23</f>
-        <v>2.1735626899999998E-3</v>
+        <v>2.1734357500000001E-3</v>
       </c>
       <c r="AB20" s="26">
         <f>result!AB23</f>
-        <v>2.2148148599999999E-3</v>
+        <v>2.2146820299999998E-3</v>
       </c>
       <c r="AC20" s="26">
         <f>result!AC23</f>
-        <v>2.25678823E-3</v>
+        <v>2.2566464500000001E-3</v>
       </c>
       <c r="AD20" s="26">
         <f>result!AD23</f>
-        <v>2.2992333900000001E-3</v>
+        <v>2.2990805299999998E-3</v>
       </c>
       <c r="AE20" s="26">
         <f>result!AE23</f>
-        <v>2.3421989000000001E-3</v>
+        <v>2.3420339599999999E-3</v>
       </c>
       <c r="AF20" s="26">
         <f>result!AF23</f>
-        <v>2.3857233300000002E-3</v>
+        <v>2.3855458900000001E-3</v>
       </c>
       <c r="AG20" s="26">
         <f>result!AG23</f>
-        <v>2.4298093400000002E-3</v>
+        <v>2.4296191699999998E-3</v>
       </c>
       <c r="AH20" s="26">
         <f>result!AH23</f>
-        <v>2.4744738099999998E-3</v>
+        <v>2.4742689099999998E-3</v>
       </c>
       <c r="AI20" s="26">
         <f>result!AI23</f>
-        <v>2.51966933E-3</v>
+        <v>2.5194487199999998E-3</v>
       </c>
       <c r="AJ20" s="26">
         <f>result!AJ23</f>
-        <v>2.56539399E-3</v>
+        <v>2.5651586500000001E-3</v>
       </c>
       <c r="AK20" s="26">
         <f>result!AK23</f>
-        <v>2.6116032699999999E-3</v>
+        <v>2.61135254E-3</v>
       </c>
       <c r="AL20" s="26">
         <f>result!AL23</f>
-        <v>2.6582423600000002E-3</v>
+        <v>2.6579753900000001E-3</v>
       </c>
       <c r="AM20" s="26">
         <f>result!AM23</f>
-        <v>2.70494572E-3</v>
+        <v>2.7046623499999999E-3</v>
       </c>
       <c r="AN20" s="26">
         <f>result!AN23</f>
-        <v>2.7521255199999999E-3</v>
+        <v>2.7518254800000001E-3</v>
       </c>
       <c r="AO20" s="26">
         <f>result!AO23</f>
-        <v>2.7995899899999998E-3</v>
+        <v>2.79927313E-3</v>
       </c>
       <c r="AP20" s="26">
         <f>result!AP23</f>
-        <v>2.8471470800000001E-3</v>
+        <v>2.8468134999999999E-3</v>
       </c>
       <c r="AQ20" s="26">
         <f>result!AQ23</f>
-        <v>2.8946728300000002E-3</v>
+        <v>2.8943218500000001E-3</v>
       </c>
       <c r="AR20" s="26">
         <f>result!AR23</f>
-        <v>2.9421091499999999E-3</v>
+        <v>2.94173847E-3</v>
       </c>
       <c r="AS20" s="26">
         <f>result!AS23</f>
-        <v>2.98933828E-3</v>
+        <v>2.9889469299999999E-3</v>
       </c>
       <c r="AT20" s="26">
         <f>result!AT23</f>
-        <v>3.0362111900000001E-3</v>
+        <v>3.0357977700000002E-3</v>
       </c>
       <c r="AU20" s="26">
         <f>result!AU23</f>
-        <v>3.0825664400000001E-3</v>
+        <v>3.0821303099999998E-3</v>
       </c>
       <c r="AV20" s="26">
         <f>result!AV23</f>
-        <v>3.1438063800000001E-3</v>
+        <v>3.1433496099999999E-3</v>
       </c>
     </row>
     <row r="21" spans="1:48" s="28" customFormat="1" x14ac:dyDescent="0.25">
@@ -12422,179 +12422,179 @@
       </c>
       <c r="E21" s="29">
         <f t="shared" si="3"/>
-        <v>1.0409598130128952</v>
+        <v>1.0409585106891555</v>
       </c>
       <c r="F21" s="29">
         <f t="shared" si="3"/>
-        <v>1.0510785648601073</v>
+        <v>1.0510749455186716</v>
       </c>
       <c r="G21" s="29">
         <f t="shared" si="3"/>
-        <v>1.0757438174644478</v>
+        <v>1.0757368104833462</v>
       </c>
       <c r="H21" s="29">
         <f t="shared" si="3"/>
-        <v>1.1109828602223781</v>
+        <v>1.1109712831236136</v>
       </c>
       <c r="I21" s="29">
         <f t="shared" si="3"/>
-        <v>1.1402758363432464</v>
+        <v>1.1402594734044817</v>
       </c>
       <c r="J21" s="29">
         <f t="shared" si="3"/>
-        <v>1.1668186083353669</v>
+        <v>1.1667977951246824</v>
       </c>
       <c r="K21" s="29">
         <f t="shared" si="3"/>
-        <v>1.1917572929970031</v>
+        <v>1.1917304635300248</v>
       </c>
       <c r="L21" s="29">
         <f t="shared" si="3"/>
-        <v>1.2300579151031803</v>
+        <v>1.2300237670561684</v>
       </c>
       <c r="M21" s="29">
         <f t="shared" si="3"/>
-        <v>1.2835319190887566</v>
+        <v>1.2834910357109937</v>
       </c>
       <c r="N21" s="29">
         <f t="shared" si="3"/>
-        <v>1.3244351912450172</v>
+        <v>1.3243900093999421</v>
       </c>
       <c r="O21" s="29">
         <f t="shared" si="3"/>
-        <v>1.3518995210720623</v>
+        <v>1.3518538198954348</v>
       </c>
       <c r="P21" s="29">
         <f t="shared" si="3"/>
-        <v>1.3749901524192414</v>
+        <v>1.374948022645752</v>
       </c>
       <c r="Q21" s="29">
         <f t="shared" si="3"/>
-        <v>1.3983423111465869</v>
+        <v>1.3982992945146004</v>
       </c>
       <c r="R21" s="29">
         <f t="shared" si="3"/>
-        <v>1.4431453797564038</v>
+        <v>1.4430911935011783</v>
       </c>
       <c r="S21" s="29">
         <f t="shared" si="3"/>
-        <v>1.4893452744689248</v>
+        <v>1.4892845686052856</v>
       </c>
       <c r="T21" s="29">
         <f t="shared" si="3"/>
-        <v>1.5185996922194427</v>
+        <v>1.5185316997346345</v>
       </c>
       <c r="U21" s="29">
         <f t="shared" si="3"/>
-        <v>1.5481866898962375</v>
+        <v>1.5481241943361705</v>
       </c>
       <c r="V21" s="29">
         <f t="shared" si="3"/>
-        <v>1.5783303151208119</v>
+        <v>1.5782610842299938</v>
       </c>
       <c r="W21" s="29">
         <f t="shared" si="3"/>
-        <v>1.6091585711363046</v>
+        <v>1.6090824930587087</v>
       </c>
       <c r="X21" s="29">
         <f t="shared" si="3"/>
-        <v>1.6403105384930994</v>
+        <v>1.6402173384537004</v>
       </c>
       <c r="Y21" s="29">
         <f t="shared" si="3"/>
-        <v>1.671974167274936</v>
+        <v>1.6718717151441849</v>
       </c>
       <c r="Z21" s="29">
         <f t="shared" si="3"/>
-        <v>1.7040833905186092</v>
+        <v>1.7039818492155039</v>
       </c>
       <c r="AA21" s="29">
         <f t="shared" si="3"/>
-        <v>1.7366149022219814</v>
+        <v>1.7365134807646194</v>
       </c>
       <c r="AB21" s="29">
         <f t="shared" si="3"/>
-        <v>1.7695742152892271</v>
+        <v>1.7694680878890268</v>
       </c>
       <c r="AC21" s="29">
         <f t="shared" si="3"/>
-        <v>1.8031097466883594</v>
+        <v>1.8029964684921658</v>
       </c>
       <c r="AD21" s="29">
         <f t="shared" si="3"/>
-        <v>1.8370222249077921</v>
+        <v>1.8369000941060556</v>
       </c>
       <c r="AE21" s="29">
         <f t="shared" si="3"/>
-        <v>1.8713504480093615</v>
+        <v>1.8712186656304632</v>
       </c>
       <c r="AF21" s="29">
         <f t="shared" si="3"/>
-        <v>1.906125232328427</v>
+        <v>1.9059834628042867</v>
       </c>
       <c r="AG21" s="29">
         <f t="shared" si="3"/>
-        <v>1.9413487031294956</v>
+        <v>1.9411967626966407</v>
       </c>
       <c r="AH21" s="29">
         <f t="shared" si="3"/>
-        <v>1.9770343470535023</v>
+        <v>1.9768706377686942</v>
       </c>
       <c r="AI21" s="29">
         <f t="shared" si="3"/>
-        <v>2.0131442848559735</v>
+        <v>2.0129680237270251</v>
       </c>
       <c r="AJ21" s="29">
         <f t="shared" si="3"/>
-        <v>2.0496769905011156</v>
+        <v>2.0494889605202142</v>
       </c>
       <c r="AK21" s="29">
         <f t="shared" si="3"/>
-        <v>2.0865968937724348</v>
+        <v>2.0863965676183112</v>
       </c>
       <c r="AL21" s="29">
         <f t="shared" si="3"/>
-        <v>2.1238602030354734</v>
+        <v>2.1236469015822514</v>
       </c>
       <c r="AM21" s="29">
         <f t="shared" si="3"/>
-        <v>2.1611748622044886</v>
+        <v>2.1609484576167088</v>
       </c>
       <c r="AN21" s="29">
         <f t="shared" si="3"/>
-        <v>2.1988701834118345</v>
+        <v>2.19863045996716</v>
       </c>
       <c r="AO21" s="29">
         <f t="shared" si="3"/>
-        <v>2.236792947870065</v>
+        <v>2.2365397857227531</v>
       </c>
       <c r="AP21" s="29">
         <f t="shared" si="3"/>
-        <v>2.2747897130796813</v>
+        <v>2.2745231921268934</v>
       </c>
       <c r="AQ21" s="29">
         <f t="shared" si="3"/>
-        <v>2.3127614385187467</v>
+        <v>2.3124810154597819</v>
       </c>
       <c r="AR21" s="29">
         <f t="shared" si="3"/>
-        <v>2.3506617119258921</v>
+        <v>2.350365549126026</v>
       </c>
       <c r="AS21" s="29">
         <f t="shared" si="3"/>
-        <v>2.3883964464032212</v>
+        <v>2.3880837688599827</v>
       </c>
       <c r="AT21" s="29">
         <f t="shared" si="3"/>
-        <v>2.4258465712103003</v>
+        <v>2.4255162603634219</v>
       </c>
       <c r="AU21" s="29">
         <f t="shared" si="3"/>
-        <v>2.4628831003688982</v>
+        <v>2.4625346448765439</v>
       </c>
       <c r="AV21" s="29">
         <f t="shared" si="3"/>
-        <v>2.511812074400551</v>
+        <v>2.5114471281339732</v>
       </c>
     </row>
     <row r="22" spans="1:48" s="28" customFormat="1" x14ac:dyDescent="0.25">
@@ -12836,127 +12836,127 @@
       </c>
       <c r="R26" s="14">
         <f>result!R30</f>
-        <v>94895.645269999906</v>
+        <v>94796.611229999995</v>
       </c>
       <c r="S26" s="14">
         <f>result!S30</f>
-        <v>97228.440010000006</v>
+        <v>96976.641740000006</v>
       </c>
       <c r="T26" s="14">
         <f>result!T30</f>
-        <v>97060.425289999999</v>
+        <v>96790.300220000005</v>
       </c>
       <c r="U26" s="14">
         <f>result!U30</f>
-        <v>100371.8621</v>
+        <v>100089.55839999999</v>
       </c>
       <c r="V26" s="14">
         <f>result!V30</f>
-        <v>98103.098870000002</v>
+        <v>97919.652749999994</v>
       </c>
       <c r="W26" s="14">
         <f>result!W30</f>
-        <v>96143.781140000006</v>
+        <v>95994.554470000003</v>
       </c>
       <c r="X26" s="14">
         <f>result!X30</f>
-        <v>91234.063829999999</v>
+        <v>91256.825169999996</v>
       </c>
       <c r="Y26" s="14">
         <f>result!Y30</f>
-        <v>87788.583769999997</v>
+        <v>87867.219490000003</v>
       </c>
       <c r="Z26" s="14">
         <f>result!Z30</f>
-        <v>85421.863200000007</v>
+        <v>85531.58971</v>
       </c>
       <c r="AA26" s="14">
         <f>result!AA30</f>
-        <v>83302.922529999996</v>
+        <v>83428.545870000002</v>
       </c>
       <c r="AB26" s="14">
         <f>result!AB30</f>
-        <v>81363.214080000005</v>
+        <v>81495.670440000002</v>
       </c>
       <c r="AC26" s="14">
         <f>result!AC30</f>
-        <v>80785.516350000005</v>
+        <v>80924.307350000003</v>
       </c>
       <c r="AD26" s="14">
         <f>result!AD30</f>
-        <v>80067.583790000004</v>
+        <v>80209.683650000006</v>
       </c>
       <c r="AE26" s="14">
         <f>result!AE30</f>
-        <v>79340.444159999999</v>
+        <v>79483.797930000001</v>
       </c>
       <c r="AF26" s="14">
         <f>result!AF30</f>
-        <v>78648.782609999995</v>
+        <v>78793.796220000004</v>
       </c>
       <c r="AG26" s="14">
         <f>result!AG30</f>
-        <v>78371.820070000002</v>
+        <v>78518.025829999999</v>
       </c>
       <c r="AH26" s="14">
         <f>result!AH30</f>
-        <v>77596.818100000004</v>
+        <v>77740.589040000006</v>
       </c>
       <c r="AI26" s="14">
         <f>result!AI30</f>
-        <v>76612.548250000007</v>
+        <v>76750.739270000005</v>
       </c>
       <c r="AJ26" s="14">
         <f>result!AJ30</f>
-        <v>76058.902969999996</v>
+        <v>76191.302750000003</v>
       </c>
       <c r="AK26" s="14">
         <f>result!AK30</f>
-        <v>75451.399579999998</v>
+        <v>75575.536309999996</v>
       </c>
       <c r="AL26" s="14">
         <f>result!AL30</f>
-        <v>74704.634229999996</v>
+        <v>74818.172120000003</v>
       </c>
       <c r="AM26" s="14">
         <f>result!AM30</f>
-        <v>73276.459319999994</v>
+        <v>73373.536240000001</v>
       </c>
       <c r="AN26" s="14">
         <f>result!AN30</f>
-        <v>71644.952229999995</v>
+        <v>71718.321559999997</v>
       </c>
       <c r="AO26" s="14">
         <f>result!AO30</f>
-        <v>70035.33094</v>
+        <v>70081.498399999997</v>
       </c>
       <c r="AP26" s="14">
         <f>result!AP30</f>
-        <v>68868.939809999996</v>
+        <v>68887.414999999906</v>
       </c>
       <c r="AQ26" s="14">
         <f>result!AQ30</f>
-        <v>67374.600380000003</v>
+        <v>67363.900420000005</v>
       </c>
       <c r="AR26" s="14">
         <f>result!AR30</f>
-        <v>65929.165729999906</v>
+        <v>65889.627739999996</v>
       </c>
       <c r="AS26" s="14">
         <f>result!AS30</f>
-        <v>64713.467409999997</v>
+        <v>64642.703520000003</v>
       </c>
       <c r="AT26" s="14">
         <f>result!AT30</f>
-        <v>63326.491549999999</v>
+        <v>63222.283519999997</v>
       </c>
       <c r="AU26" s="14">
         <f>result!AU30</f>
-        <v>61890.662960000001</v>
+        <v>61752.993399999999</v>
       </c>
       <c r="AV26" s="14">
         <f>result!AV30</f>
-        <v>62666.98128</v>
+        <v>62514.370239999997</v>
       </c>
     </row>
     <row r="27" spans="1:48" x14ac:dyDescent="0.25">
@@ -12974,183 +12974,183 @@
       </c>
       <c r="D27" s="19">
         <f>result!D31</f>
-        <v>0.99102938060000001</v>
+        <v>0.99102560019999997</v>
       </c>
       <c r="E27" s="19">
         <f>result!E31</f>
-        <v>0.69050082479999997</v>
+        <v>0.69078412690000002</v>
       </c>
       <c r="F27" s="19">
         <f>result!F31</f>
-        <v>0.69826689620000004</v>
+        <v>0.69892559340000004</v>
       </c>
       <c r="G27" s="19">
         <f>result!G31</f>
-        <v>0.75048792389999996</v>
+        <v>0.75154929049999997</v>
       </c>
       <c r="H27" s="19">
         <f>result!H31</f>
-        <v>0.74196917399999995</v>
+        <v>0.74208622400000002</v>
       </c>
       <c r="I27" s="19">
         <f>result!I31</f>
-        <v>0.75691974169999998</v>
+        <v>0.75657658559999996</v>
       </c>
       <c r="J27" s="19">
         <f>result!J31</f>
-        <v>0.79354190309999995</v>
+        <v>0.79288026609999995</v>
       </c>
       <c r="K27" s="19">
         <f>result!K31</f>
-        <v>0.83577822859999995</v>
+        <v>0.83514108129999998</v>
       </c>
       <c r="L27" s="19">
         <f>result!L31</f>
-        <v>0.86124936870000002</v>
+        <v>0.86073636919999996</v>
       </c>
       <c r="M27" s="19">
         <f>result!M31</f>
-        <v>0.88263335970000001</v>
+        <v>0.8822819864</v>
       </c>
       <c r="N27" s="19">
         <f>result!N31</f>
-        <v>0.94055030360000003</v>
+        <v>0.94015974010000003</v>
       </c>
       <c r="O27" s="19">
         <f>result!O31</f>
-        <v>0.94600954900000001</v>
+        <v>0.94605744410000003</v>
       </c>
       <c r="P27" s="19">
         <f>result!P31</f>
-        <v>0.977273536</v>
+        <v>0.97746895359999997</v>
       </c>
       <c r="Q27" s="31">
         <f>result!Q31</f>
-        <v>0.97951600270000005</v>
+        <v>0.98005794950000003</v>
       </c>
       <c r="R27" s="31">
         <f>result!R31</f>
-        <v>1.0054763529999999</v>
+        <v>1.0070424200000001</v>
       </c>
       <c r="S27" s="19">
         <f>result!S31</f>
-        <v>0.99588708189999997</v>
+        <v>0.99926356699999996</v>
       </c>
       <c r="T27" s="19">
         <f>result!T31</f>
-        <v>1.024166669</v>
+        <v>1.0278075840000001</v>
       </c>
       <c r="U27" s="19">
         <f>result!U31</f>
-        <v>1.046295988</v>
+        <v>1.0501284310000001</v>
       </c>
       <c r="V27" s="19">
         <f>result!V31</f>
-        <v>1.1003200980000001</v>
+        <v>1.103139154</v>
       </c>
       <c r="W27" s="19">
         <f>result!W31</f>
-        <v>1.1184047290000001</v>
+        <v>1.121119451</v>
       </c>
       <c r="X27" s="19">
         <f>result!X31</f>
-        <v>1.189038646</v>
+        <v>1.1896875739999999</v>
       </c>
       <c r="Y27" s="19">
         <f>result!Y31</f>
-        <v>1.21609576</v>
+        <v>1.215700614</v>
       </c>
       <c r="Z27" s="19">
         <f>result!Z31</f>
-        <v>1.2422566180000001</v>
+        <v>1.2412101179999999</v>
       </c>
       <c r="AA27" s="19">
         <f>result!AA31</f>
-        <v>1.2659353520000001</v>
+        <v>1.2645214309999999</v>
       </c>
       <c r="AB27" s="19">
         <f>result!AB31</f>
-        <v>1.288197644</v>
+        <v>1.286596058</v>
       </c>
       <c r="AC27" s="19">
         <f>result!AC31</f>
-        <v>1.312294372</v>
+        <v>1.310557059</v>
       </c>
       <c r="AD27" s="19">
         <f>result!AD31</f>
-        <v>1.336047811</v>
+        <v>1.3342317610000001</v>
       </c>
       <c r="AE27" s="19">
         <f>result!AE31</f>
-        <v>1.359690176</v>
+        <v>1.3578438260000001</v>
       </c>
       <c r="AF27" s="19">
         <f>result!AF31</f>
-        <v>1.3834758540000001</v>
+        <v>1.3816194230000001</v>
       </c>
       <c r="AG27" s="19">
         <f>result!AG31</f>
-        <v>1.4086093340000001</v>
+        <v>1.406737141</v>
       </c>
       <c r="AH27" s="19">
         <f>result!AH31</f>
-        <v>1.433065773</v>
+        <v>1.4312195190000001</v>
       </c>
       <c r="AI27" s="19">
         <f>result!AI31</f>
-        <v>1.457255988</v>
+        <v>1.4554796350000001</v>
       </c>
       <c r="AJ27" s="19">
         <f>result!AJ31</f>
-        <v>1.4826721940000001</v>
+        <v>1.4809754550000001</v>
       </c>
       <c r="AK27" s="19">
         <f>result!AK31</f>
-        <v>1.5079763610000001</v>
+        <v>1.5064149250000001</v>
       </c>
       <c r="AL27" s="19">
         <f>result!AL31</f>
-        <v>1.532990232</v>
+        <v>1.531619407</v>
       </c>
       <c r="AM27" s="19">
         <f>result!AM31</f>
-        <v>1.5556991760000001</v>
+        <v>1.554652836</v>
       </c>
       <c r="AN27" s="19">
         <f>result!AN31</f>
-        <v>1.5768145259999999</v>
+        <v>1.5762818030000001</v>
       </c>
       <c r="AO27" s="19">
         <f>result!AO31</f>
-        <v>1.597250244</v>
+        <v>1.5973554400000001</v>
       </c>
       <c r="AP27" s="19">
         <f>result!AP31</f>
-        <v>1.61855478</v>
+        <v>1.6193542869999999</v>
       </c>
       <c r="AQ27" s="19">
         <f>result!AQ31</f>
-        <v>1.638451471</v>
+        <v>1.6400456919999999</v>
       </c>
       <c r="AR27" s="19">
         <f>result!AR31</f>
-        <v>1.658135664</v>
+        <v>1.6605913240000001</v>
       </c>
       <c r="AS27" s="19">
         <f>result!AS31</f>
-        <v>1.678096703</v>
+        <v>1.681494654</v>
       </c>
       <c r="AT27" s="19">
         <f>result!AT31</f>
-        <v>1.6969332420000001</v>
+        <v>1.701385484</v>
       </c>
       <c r="AU27" s="19">
         <f>result!AU31</f>
-        <v>1.7155968290000001</v>
+        <v>1.7211622680000001</v>
       </c>
       <c r="AV27" s="19">
         <f>result!AV31</f>
-        <v>1.748859795</v>
+        <v>1.755212668</v>
       </c>
     </row>
     <row r="28" spans="1:48" x14ac:dyDescent="0.25">
@@ -13168,183 +13168,183 @@
       </c>
       <c r="D28" s="14">
         <f>result!D32</f>
-        <v>89779.333647315201</v>
+        <v>89778.991173318398</v>
       </c>
       <c r="E28" s="14">
         <f>result!E32</f>
-        <v>65354.7058355599</v>
+        <v>65381.519888118703</v>
       </c>
       <c r="F28" s="14">
         <f>result!F32</f>
-        <v>66867.940471114707</v>
+        <v>66931.019109666493</v>
       </c>
       <c r="G28" s="14">
         <f>result!G32</f>
-        <v>68548.696147868293</v>
+        <v>68645.640141566197</v>
       </c>
       <c r="H28" s="14">
         <f>result!H32</f>
-        <v>68886.365404837401</v>
+        <v>68897.232634033993</v>
       </c>
       <c r="I28" s="14">
         <f>result!I32</f>
-        <v>70634.4399765407</v>
+        <v>70602.417243333097</v>
       </c>
       <c r="J28" s="14">
         <f>result!J32</f>
-        <v>73394.269231097598</v>
+        <v>73333.074776310095</v>
       </c>
       <c r="K28" s="14">
         <f>result!K32</f>
-        <v>75887.442260401396</v>
+        <v>75829.590216299795</v>
       </c>
       <c r="L28" s="14">
         <f>result!L32</f>
-        <v>77696.839428836596</v>
+        <v>77650.559639002095</v>
       </c>
       <c r="M28" s="14">
         <f>result!M32</f>
-        <v>78958.807762078606</v>
+        <v>78927.374532706002</v>
       </c>
       <c r="N28" s="14">
         <f>result!N32</f>
-        <v>84605.181421196103</v>
+        <v>84570.049120831594</v>
       </c>
       <c r="O28" s="14">
         <f>result!O32</f>
-        <v>85951.091500545197</v>
+        <v>85955.443080428202</v>
       </c>
       <c r="P28" s="14">
         <f>result!P32</f>
-        <v>89736.422568822207</v>
+        <v>89754.366446032596</v>
       </c>
       <c r="Q28" s="14">
         <f>result!Q32</f>
-        <v>91206.829339312404</v>
+        <v>91257.292271170998</v>
       </c>
       <c r="R28" s="14">
         <f>result!R32</f>
-        <v>95415.3273216612</v>
+        <v>95464.208780858302</v>
       </c>
       <c r="S28" s="14">
         <f>result!S32</f>
-        <v>96828.547399248098</v>
+        <v>96905.2249407934</v>
       </c>
       <c r="T28" s="14">
         <f>result!T32</f>
-        <v>99406.052460982595</v>
+        <v>99481.804623752803</v>
       </c>
       <c r="U28" s="14">
         <f>result!U32</f>
-        <v>105018.676623319</v>
+        <v>105106.890922074</v>
       </c>
       <c r="V28" s="14">
         <f>result!V32</f>
-        <v>107944.811362742</v>
+        <v>108019.002894608</v>
       </c>
       <c r="W28" s="14">
         <f>result!W32</f>
-        <v>107527.65949091699</v>
+        <v>107621.36220639601</v>
       </c>
       <c r="X28" s="14">
         <f>result!X32</f>
-        <v>108480.8277255</v>
+        <v>108567.110947439</v>
       </c>
       <c r="Y28" s="14">
         <f>result!Y32</f>
-        <v>106759.324499101</v>
+        <v>106820.23268446499</v>
       </c>
       <c r="Z28" s="14">
         <f>result!Z32</f>
-        <v>106115.87488208999</v>
+        <v>106162.67455667599</v>
       </c>
       <c r="AA28" s="14">
         <f>result!AA32</f>
-        <v>105456.114555644</v>
+        <v>105497.184209781</v>
       </c>
       <c r="AB28" s="14">
         <f>result!AB32</f>
-        <v>104811.900686123</v>
+        <v>104852.008332171</v>
       </c>
       <c r="AC28" s="14">
         <f>result!AC32</f>
-        <v>106014.378445219</v>
+        <v>106055.922242228</v>
       </c>
       <c r="AD28" s="14">
         <f>result!AD32</f>
-        <v>106974.120054688</v>
+        <v>107018.30746559201</v>
       </c>
       <c r="AE28" s="14">
         <f>result!AE32</f>
-        <v>107878.42248382801</v>
+        <v>107926.584286282</v>
       </c>
       <c r="AF28" s="14">
         <f>result!AF32</f>
-        <v>108808.69168742999</v>
+        <v>108863.039269456</v>
       </c>
       <c r="AG28" s="14">
         <f>result!AG32</f>
-        <v>110395.27727317</v>
+        <v>110454.223173058</v>
       </c>
       <c r="AH28" s="14">
         <f>result!AH32</f>
-        <v>111201.344112816</v>
+        <v>111263.848452605</v>
       </c>
       <c r="AI28" s="14">
         <f>result!AI32</f>
-        <v>111644.094693251</v>
+        <v>111709.13797867901</v>
       </c>
       <c r="AJ28" s="14">
         <f>result!AJ32</f>
-        <v>112770.420539763</v>
+        <v>112837.449257224</v>
       </c>
       <c r="AK28" s="14">
         <f>result!AK32</f>
-        <v>113778.926971005</v>
+        <v>113848.115862263</v>
       </c>
       <c r="AL28" s="14">
         <f>result!AL32</f>
-        <v>114521.474559722</v>
+        <v>114592.964415258</v>
       </c>
       <c r="AM28" s="14">
         <f>result!AM32</f>
-        <v>113996.12738432099</v>
+        <v>114070.376202864</v>
       </c>
       <c r="AN28" s="14">
         <f>result!AN32</f>
-        <v>112970.80139084</v>
+        <v>113048.28521673</v>
       </c>
       <c r="AO28" s="14">
         <f>result!AO32</f>
-        <v>111863.949432535</v>
+        <v>111945.062712591</v>
       </c>
       <c r="AP28" s="14">
         <f>result!AP32</f>
-        <v>111468.151723007</v>
+        <v>111553.130800598</v>
       </c>
       <c r="AQ28" s="14">
         <f>result!AQ32</f>
-        <v>110390.01310064799</v>
+        <v>110479.874680138</v>
       </c>
       <c r="AR28" s="14">
         <f>result!AR32</f>
-        <v>109319.50099467899</v>
+        <v>109415.744166633</v>
       </c>
       <c r="AS28" s="14">
         <f>result!AS32</f>
-        <v>108595.45630041799</v>
+        <v>108696.360388987</v>
       </c>
       <c r="AT28" s="14">
         <f>result!AT32</f>
-        <v>107460.82861042699</v>
+        <v>107565.47544626</v>
       </c>
       <c r="AU28" s="14">
         <f>result!AU32</f>
-        <v>106179.42511888299</v>
+        <v>106286.922176133</v>
       </c>
       <c r="AV28" s="14">
         <f>result!AV32</f>
-        <v>109595.764034609</v>
+        <v>109726.01457729</v>
       </c>
     </row>
     <row r="30" spans="1:48" x14ac:dyDescent="0.25">
@@ -13999,127 +13999,127 @@
       </c>
       <c r="R36" s="32">
         <f>result!R29</f>
-        <v>94895.645269999906</v>
+        <v>94796.611229999995</v>
       </c>
       <c r="S36">
         <f>result!S29</f>
-        <v>97228.440010000006</v>
+        <v>96976.641740000006</v>
       </c>
       <c r="T36">
         <f>result!T29</f>
-        <v>97060.425289999999</v>
+        <v>96790.300220000005</v>
       </c>
       <c r="U36">
         <f>result!U29</f>
-        <v>100371.8621</v>
+        <v>100089.55839999999</v>
       </c>
       <c r="V36">
         <f>result!V29</f>
-        <v>98103.098870000002</v>
+        <v>97919.652749999994</v>
       </c>
       <c r="W36">
         <f>result!W29</f>
-        <v>96143.781140000006</v>
+        <v>95994.554470000003</v>
       </c>
       <c r="X36">
         <f>result!X29</f>
-        <v>91234.063829999999</v>
+        <v>91256.825169999996</v>
       </c>
       <c r="Y36">
         <f>result!Y29</f>
-        <v>87788.583769999997</v>
+        <v>87867.219490000003</v>
       </c>
       <c r="Z36">
         <f>result!Z29</f>
-        <v>85421.863200000007</v>
+        <v>85531.58971</v>
       </c>
       <c r="AA36">
         <f>result!AA29</f>
-        <v>83302.922529999996</v>
+        <v>83428.545870000002</v>
       </c>
       <c r="AB36">
         <f>result!AB29</f>
-        <v>81363.214080000005</v>
+        <v>81495.670440000002</v>
       </c>
       <c r="AC36">
         <f>result!AC29</f>
-        <v>80785.516350000005</v>
+        <v>80924.307350000003</v>
       </c>
       <c r="AD36">
         <f>result!AD29</f>
-        <v>80067.583790000004</v>
+        <v>80209.683650000006</v>
       </c>
       <c r="AE36">
         <f>result!AE29</f>
-        <v>79340.444159999999</v>
+        <v>79483.797930000001</v>
       </c>
       <c r="AF36">
         <f>result!AF29</f>
-        <v>78648.782609999995</v>
+        <v>78793.796220000004</v>
       </c>
       <c r="AG36">
         <f>result!AG29</f>
-        <v>78371.820070000002</v>
+        <v>78518.025829999999</v>
       </c>
       <c r="AH36">
         <f>result!AH29</f>
-        <v>77596.818100000004</v>
+        <v>77740.589040000006</v>
       </c>
       <c r="AI36">
         <f>result!AI29</f>
-        <v>76612.548250000007</v>
+        <v>76750.739270000005</v>
       </c>
       <c r="AJ36">
         <f>result!AJ29</f>
-        <v>76058.902969999996</v>
+        <v>76191.302750000003</v>
       </c>
       <c r="AK36">
         <f>result!AK29</f>
-        <v>75451.399579999998</v>
+        <v>75575.536309999996</v>
       </c>
       <c r="AL36">
         <f>result!AL29</f>
-        <v>74704.634229999996</v>
+        <v>74818.172120000003</v>
       </c>
       <c r="AM36">
         <f>result!AM29</f>
-        <v>73276.459319999994</v>
+        <v>73373.536240000001</v>
       </c>
       <c r="AN36">
         <f>result!AN29</f>
-        <v>71644.952229999995</v>
+        <v>71718.321559999997</v>
       </c>
       <c r="AO36">
         <f>result!AO29</f>
-        <v>70035.33094</v>
+        <v>70081.498399999997</v>
       </c>
       <c r="AP36">
         <f>result!AP29</f>
-        <v>68868.939809999996</v>
+        <v>68887.414999999906</v>
       </c>
       <c r="AQ36">
         <f>result!AQ29</f>
-        <v>67374.600380000003</v>
+        <v>67363.900420000005</v>
       </c>
       <c r="AR36">
         <f>result!AR29</f>
-        <v>65929.165729999906</v>
+        <v>65889.627739999996</v>
       </c>
       <c r="AS36">
         <f>result!AS29</f>
-        <v>64713.467409999997</v>
+        <v>64642.703520000003</v>
       </c>
       <c r="AT36">
         <f>result!AT29</f>
-        <v>63326.491549999999</v>
+        <v>63222.283519999997</v>
       </c>
       <c r="AU36">
         <f>result!AU29</f>
-        <v>61890.662960000001</v>
+        <v>61752.993399999999</v>
       </c>
       <c r="AV36">
         <f>result!AV29</f>
-        <v>62666.98128</v>
+        <v>62514.370239999997</v>
       </c>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
@@ -14610,71 +14610,71 @@
       </c>
       <c r="D50" s="34">
         <f t="shared" si="9"/>
-        <v>89779.333647315201</v>
+        <v>89778.991173318398</v>
       </c>
       <c r="E50" s="34">
         <f t="shared" si="9"/>
-        <v>65354.7058355599</v>
+        <v>65381.519888118703</v>
       </c>
       <c r="F50" s="34">
         <f t="shared" si="9"/>
-        <v>66867.940471114707</v>
+        <v>66931.019109666493</v>
       </c>
       <c r="G50" s="34">
         <f t="shared" si="9"/>
-        <v>68548.696147868293</v>
+        <v>68645.640141566197</v>
       </c>
       <c r="H50" s="34">
         <f t="shared" si="9"/>
-        <v>68886.365404837401</v>
+        <v>68897.232634033993</v>
       </c>
       <c r="I50" s="34">
         <f t="shared" si="9"/>
-        <v>70634.4399765407</v>
+        <v>70602.417243333097</v>
       </c>
       <c r="J50" s="34">
         <f t="shared" si="9"/>
-        <v>73394.269231097598</v>
+        <v>73333.074776310095</v>
       </c>
       <c r="K50" s="34">
         <f t="shared" si="9"/>
-        <v>75887.442260401396</v>
+        <v>75829.590216299795</v>
       </c>
       <c r="L50" s="34">
         <f t="shared" si="9"/>
-        <v>77696.839428836596</v>
+        <v>77650.559639002095</v>
       </c>
       <c r="M50" s="34">
         <f t="shared" si="9"/>
-        <v>78958.807762078606</v>
+        <v>78927.374532706002</v>
       </c>
       <c r="N50" s="34">
         <f t="shared" si="9"/>
-        <v>84605.181421196103</v>
+        <v>84570.049120831594</v>
       </c>
       <c r="O50" s="34">
         <f t="shared" si="9"/>
-        <v>85951.091500545197</v>
+        <v>85955.443080428202</v>
       </c>
       <c r="P50" s="34">
         <f t="shared" si="9"/>
-        <v>89736.422568822207</v>
+        <v>89754.366446032596</v>
       </c>
       <c r="Q50" s="34">
         <f t="shared" si="9"/>
-        <v>91206.829339312404</v>
+        <v>91257.292271170998</v>
       </c>
       <c r="R50" s="34">
         <f t="shared" si="9"/>
-        <v>95415.3273216612</v>
+        <v>95464.208780858302</v>
       </c>
       <c r="S50" s="34">
         <f t="shared" si="9"/>
-        <v>96828.547399248098</v>
+        <v>96905.2249407934</v>
       </c>
       <c r="T50" s="34">
         <f t="shared" si="9"/>
-        <v>99406.052460982595</v>
+        <v>99481.804623752803</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -20661,11 +20661,11 @@
       </c>
       <c r="I3" s="41">
         <f>result!R11/result!$R$4</f>
-        <v>9.4433779213816977E-3</v>
+        <v>1.0738327829237906E-2</v>
       </c>
       <c r="J3" s="23">
         <f>I3-H3</f>
-        <v>-1.0556622078618303E-2</v>
+        <v>-9.261672170762094E-3</v>
       </c>
       <c r="K3" s="11"/>
       <c r="L3" s="13">
@@ -20674,18 +20674,18 @@
       </c>
       <c r="M3" s="14">
         <f>SUM(result!N3:R3)/5</f>
-        <v>523761.0647000001</v>
+        <v>530075.2322999998</v>
       </c>
       <c r="N3" s="15">
         <f>L3-M3</f>
-        <v>-76409.178563727066</v>
+        <v>-82723.346163726761</v>
       </c>
       <c r="O3" s="11">
         <v>14000</v>
       </c>
       <c r="P3" s="19">
         <f>SUM(result!R2:S2)/2</f>
-        <v>16664.34851</v>
+        <v>16553.80344</v>
       </c>
       <c r="R3" s="12"/>
     </row>
@@ -20702,11 +20702,11 @@
       </c>
       <c r="I4" s="41">
         <f>result!R10/result!$R$4</f>
-        <v>4.9867428906788351E-2</v>
+        <v>5.4934817726399347E-2</v>
       </c>
       <c r="J4" s="23">
         <f t="shared" ref="J4:J9" si="0">I4-H4</f>
-        <v>1.4867428906788348E-2</v>
+        <v>1.9934817726399344E-2</v>
       </c>
       <c r="K4" s="11"/>
       <c r="N4" s="12"/>
@@ -20726,11 +20726,11 @@
       </c>
       <c r="I5" s="41">
         <f>result!R9/result!$R$4</f>
-        <v>0.21371213265621286</v>
+        <v>0.23333606550825939</v>
       </c>
       <c r="J5" s="23">
         <f t="shared" si="0"/>
-        <v>-2.1287867343787126E-2</v>
+        <v>-1.6639344917405985E-3</v>
       </c>
       <c r="K5" s="11"/>
       <c r="L5" t="s">
@@ -20763,36 +20763,36 @@
       </c>
       <c r="I6" s="41">
         <f>result!R8/result!$R$4</f>
-        <v>0.34871528906019389</v>
+        <v>0.31508176392545656</v>
       </c>
       <c r="J6" s="23">
         <f t="shared" si="0"/>
-        <v>2.8715289060193883E-2</v>
+        <v>-4.9182360745434472E-3</v>
       </c>
       <c r="K6" s="16"/>
       <c r="L6" s="17">
         <f>SUM(result!U3:AB3)/7</f>
-        <v>844598.51511428563</v>
+        <v>854872.25952857139</v>
       </c>
       <c r="M6" s="17">
         <f>SUM(result!U13:AB13)/7</f>
-        <v>1449761.7594428572</v>
+        <v>1454112.9161285716</v>
       </c>
       <c r="N6" s="18">
         <f>M6-L6</f>
-        <v>605163.2443285716</v>
+        <v>599240.65660000022</v>
       </c>
       <c r="O6" s="16">
         <f>SUM(result!U2:AB2)/7</f>
-        <v>17966.547032857143</v>
+        <v>17839.580597142856</v>
       </c>
       <c r="P6" s="20">
         <f>SUM(result!U12:AB12)/7</f>
-        <v>29356.791302857142</v>
+        <v>29309.118101428576</v>
       </c>
       <c r="Q6" s="17">
         <f>P6-O6</f>
-        <v>11390.244269999999</v>
+        <v>11469.537504285719</v>
       </c>
       <c r="R6" s="21"/>
     </row>
@@ -20809,11 +20809,11 @@
       </c>
       <c r="I7" s="41">
         <f>result!R7/result!$R$4</f>
-        <v>0.20195684024110336</v>
+        <v>0.21264127283360726</v>
       </c>
       <c r="J7" s="23">
         <f t="shared" si="0"/>
-        <v>-1.8043159758896643E-2</v>
+        <v>-7.3587271663927423E-3</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -20829,11 +20829,11 @@
       </c>
       <c r="I8" s="41">
         <f>result!R6/result!$R$4</f>
-        <v>9.8955651376382042E-2</v>
+        <v>0.10406030936528178</v>
       </c>
       <c r="J8" s="23">
         <f t="shared" si="0"/>
-        <v>-1.0443486236179633E-3</v>
+        <v>4.0603093652817751E-3</v>
       </c>
       <c r="N8" s="38"/>
     </row>
@@ -20850,11 +20850,11 @@
       </c>
       <c r="I9" s="41">
         <f>result!R5/result!$R$4</f>
-        <v>7.7349279719025374E-2</v>
+        <v>6.9207442653207857E-2</v>
       </c>
       <c r="J9" s="23">
         <f t="shared" si="0"/>
-        <v>7.3492797190253673E-3</v>
+        <v>-7.9255734679214984E-4</v>
       </c>
       <c r="L9" s="22" t="s">
         <v>0</v>
@@ -20866,7 +20866,7 @@
         <v>0.02</v>
       </c>
       <c r="O9" s="25">
-        <v>1.229473511239425E-2</v>
+        <v>9.8657493049371069E-3</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -20880,7 +20880,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="O10" s="25">
-        <v>5.1746726829430954E-2</v>
+        <v>5.3291814306341313E-2</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -20909,7 +20909,7 @@
         <v>0.23499999999999999</v>
       </c>
       <c r="O11" s="24">
-        <v>0.22814435970265176</v>
+        <v>0.23557189507050164</v>
       </c>
       <c r="P11" s="24"/>
     </row>
@@ -20939,7 +20939,7 @@
         <v>0.32</v>
       </c>
       <c r="O12" s="24">
-        <v>0.33195392205833041</v>
+        <v>0.31523578905274563</v>
       </c>
       <c r="P12" s="24"/>
     </row>
@@ -20969,7 +20969,7 @@
         <v>0.22</v>
       </c>
       <c r="O13" s="24">
-        <v>0.20077604736669283</v>
+        <v>0.21277031860607376</v>
       </c>
       <c r="P13" s="24"/>
     </row>
@@ -20999,7 +20999,7 @@
         <v>0.1</v>
       </c>
       <c r="O14" s="24">
-        <v>9.7869394053386058E-2</v>
+        <v>0.10405988192919496</v>
       </c>
       <c r="P14" s="24"/>
     </row>
@@ -21033,7 +21033,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O15" s="24">
-        <v>7.7214814747391072E-2</v>
+        <v>6.9204551568052275E-2</v>
       </c>
       <c r="P15" s="24"/>
     </row>

--- a/data/calibrations/recalage parc immobilier_new2.xlsx
+++ b/data/calibrations/recalage parc immobilier_new2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\ThreeME\data\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C48172D-4BE4-4AD8-AEA9-FE5107050659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7EE5A5-09EE-4B70-8E2B-795CA0E8AD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{F3B8202A-200E-4C94-BB50-F6C7EC74A6D2}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{F3B8202A-200E-4C94-BB50-F6C7EC74A6D2}"/>
   </bookViews>
   <sheets>
     <sheet name="result" sheetId="1" r:id="rId1"/>
@@ -4384,7 +4384,13 @@
       <sheetData sheetId="21" refreshError="1"/>
       <sheetData sheetId="22" refreshError="1"/>
       <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="24">
+        <row r="2">
+          <cell r="C2">
+            <v>0.99172610111270254</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="25">
         <row r="112">
           <cell r="C112">
